--- a/Case_test/Inf_stage_demand/Inf_enmpc_felement=1.xlsx
+++ b/Case_test/Inf_stage_demand/Inf_enmpc_felement=1.xlsx
@@ -475,13 +475,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.939390404544829e-06</v>
+        <v>4.939400855208401e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.694114096875121e-06</v>
+        <v>2.694122792567683e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.021529324961749e-06</v>
+        <v>4.021534364853784e-06</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01778699086131106</v>
+        <v>0.01782624339494395</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01395284958129348</v>
+        <v>0.0139501753835496</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003865535338763994</v>
+        <v>0.003907486664976432</v>
       </c>
     </row>
     <row r="5">
@@ -503,13 +503,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02927626212541221</v>
+        <v>0.0292532529667745</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02034935163880069</v>
+        <v>0.02034992858999947</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008960957482693353</v>
+        <v>0.008937370263023858</v>
       </c>
     </row>
     <row r="6">
@@ -517,13 +517,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02859503957782529</v>
+        <v>0.0285769686128675</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01613455903054562</v>
+        <v>0.01613618630112499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01249483618848425</v>
+        <v>0.01247513662821509</v>
       </c>
     </row>
     <row r="7">
@@ -531,13 +531,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02907593044662832</v>
+        <v>0.02907759109239278</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01654202620397262</v>
+        <v>0.01654194907887202</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01256812363082904</v>
+        <v>0.01256986179707925</v>
       </c>
     </row>
     <row r="8">
@@ -545,13 +545,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03667132200721429</v>
+        <v>0.03667138003628176</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02034298373196265</v>
+        <v>0.02034298771036722</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01636165970684607</v>
+        <v>0.01636176424886828</v>
       </c>
     </row>
     <row r="9">
@@ -559,13 +559,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04402461884957459</v>
+        <v>0.04402461690801041</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02376076944605917</v>
+        <v>0.02376076904636129</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0202966025700521</v>
+        <v>0.02029660102758298</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.04301632957049411</v>
+        <v>0.04301632778669995</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02329062306033072</v>
+        <v>0.02329062322721109</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01975844059671498</v>
+        <v>0.01975843868299873</v>
       </c>
     </row>
     <row r="11">
@@ -587,13 +587,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0348661870747413</v>
+        <v>0.03486618784407179</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01947211558476554</v>
+        <v>0.01947211556224638</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01542740235017137</v>
+        <v>0.01542740314217674</v>
       </c>
     </row>
     <row r="12">
@@ -601,13 +601,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02824710680655373</v>
+        <v>0.02824710674168528</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01614400517107075</v>
+        <v>0.01614400517291095</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01213734314013723</v>
+        <v>0.01213734307341489</v>
       </c>
     </row>
     <row r="13">
@@ -615,13 +615,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02906166876252227</v>
+        <v>0.02906168510907547</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01654279345854873</v>
+        <v>0.01654279132075939</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01255309176120534</v>
+        <v>0.01255311017391241</v>
       </c>
     </row>
     <row r="14">
@@ -629,13 +629,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03667063897345863</v>
+        <v>0.03667062225155579</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02034308555091776</v>
+        <v>0.02034308742224072</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01636087470857647</v>
+        <v>0.01636085611108981</v>
       </c>
     </row>
     <row r="15">
@@ -643,13 +643,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04402467025310886</v>
+        <v>0.0440246706715061</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02376076841171825</v>
+        <v>0.02376076845072252</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02029665502678506</v>
+        <v>0.02029665540605467</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +657,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04301633386566216</v>
+        <v>0.04301633399013501</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02329062262261434</v>
+        <v>0.02329062261055726</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01975844536885616</v>
+        <v>0.01975844550543399</v>
       </c>
     </row>
     <row r="17">
@@ -671,13 +671,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03486618764543253</v>
+        <v>0.03486618764151404</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01947211557363496</v>
+        <v>0.01947211557386132</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01542740293208706</v>
+        <v>0.01542740292794057</v>
       </c>
     </row>
     <row r="18">
@@ -685,13 +685,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02824710674308569</v>
+        <v>0.02824710674312599</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01614400517286052</v>
+        <v>0.01614400517285865</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01213734307486613</v>
+        <v>0.0121373430749081</v>
       </c>
     </row>
     <row r="19">
@@ -699,13 +699,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02906166871843148</v>
+        <v>0.02906168510907872</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01654279346442132</v>
+        <v>0.01654279132075881</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0125530917114338</v>
+        <v>0.0125531101739157</v>
       </c>
     </row>
     <row r="20">
@@ -713,13 +713,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03667063901969993</v>
+        <v>0.03667062225167252</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0203430855457423</v>
+        <v>0.02034308742222165</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01636087476000452</v>
+        <v>0.01636085611122597</v>
       </c>
     </row>
     <row r="21">
@@ -727,13 +727,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.04402467025198716</v>
+        <v>0.04402467067137451</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0237607684116052</v>
+        <v>0.02376076845074116</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02029665502577803</v>
+        <v>0.02029665540590363</v>
       </c>
     </row>
     <row r="22">
@@ -741,13 +741,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.04301633386528039</v>
+        <v>0.04301633399015023</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02329062262265172</v>
+        <v>0.02329062261055579</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01975844536843704</v>
+        <v>0.01975844550544987</v>
       </c>
     </row>
     <row r="23">
@@ -755,13 +755,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.03486618764544717</v>
+        <v>0.03486618764150994</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0194721155736342</v>
+        <v>0.01947211557386179</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01542740293210229</v>
+        <v>0.01542740292793579</v>
       </c>
     </row>
     <row r="24">
@@ -769,13 +769,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02824710674308549</v>
+        <v>0.02824710674312825</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01614400517286038</v>
+        <v>0.01614400517285853</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0121373430748661</v>
+        <v>0.01213734307491051</v>
       </c>
     </row>
     <row r="25">
@@ -783,13 +783,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02906166894263119</v>
+        <v>0.02906168510908101</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01654279343510584</v>
+        <v>0.01654279132075865</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01255309196399439</v>
+        <v>0.01255311017391845</v>
       </c>
     </row>
     <row r="26">
@@ -797,13 +797,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03667063879031907</v>
+        <v>0.03667062225174106</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02034308557141217</v>
+        <v>0.02034308742221036</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01636087450489566</v>
+        <v>0.01636085611130633</v>
       </c>
     </row>
   </sheetData>
@@ -830,9 +830,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>controller_1_lyapunov</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>118166.5321219524</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107192.604394083</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100533.8339551765</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>95636.64913582048</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>94986.56383750282</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91157.92317556044</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87801.69847488271</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84771.53716838772</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>82029.70766033765</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79559.08325498675</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>77313.45137201132</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>75010.4840989674</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>73062.00093162405</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>71205.77097091815</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>69446.18490116032</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>67793.50747332913</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>66239.88850735745</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>64763.9507526187</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>63344.30956067113</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>61970.57693939324</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>60647.86528718892</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>59385.71217463879</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58182.54597154722</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57026.74865105037</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -863,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4018254429101944</v>
+        <v>0.5813748380169272</v>
       </c>
     </row>
     <row r="3">
@@ -871,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9163357010111213</v>
+        <v>0.9663050062954426</v>
       </c>
     </row>
     <row r="4">
@@ -879,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7038679020479321</v>
+        <v>0.7209113463759422</v>
       </c>
     </row>
     <row r="5">
@@ -887,7 +1087,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.793026776984334</v>
+        <v>0.9389876835048199</v>
       </c>
     </row>
     <row r="6">
@@ -895,7 +1095,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.219468554481864</v>
+        <v>0.8679094547405839</v>
       </c>
     </row>
     <row r="7">
@@ -903,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.016489646397531</v>
+        <v>0.7579735545441508</v>
       </c>
     </row>
     <row r="8">
@@ -911,7 +1111,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.423277638852596</v>
+        <v>0.9203162845224142</v>
       </c>
     </row>
     <row r="9">
@@ -919,7 +1119,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.9026277596130967</v>
+        <v>1.87995117623359</v>
       </c>
     </row>
     <row r="10">
@@ -927,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8204880077391863</v>
+        <v>0.8286430733278394</v>
       </c>
     </row>
     <row r="11">
@@ -935,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.8165108393877745</v>
+        <v>0.9461590917780995</v>
       </c>
     </row>
     <row r="12">
@@ -943,7 +1143,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.414836697280407</v>
+        <v>2.068875886499882</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +1151,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.625255743972957</v>
+        <v>0.7687814338132739</v>
       </c>
     </row>
     <row r="14">
@@ -959,7 +1159,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.17946445941925</v>
+        <v>0.8457668870687485</v>
       </c>
     </row>
     <row r="15">
@@ -967,7 +1167,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7207207707688212</v>
+        <v>0.8223119927570224</v>
       </c>
     </row>
     <row r="16">
@@ -975,7 +1175,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8837792593985796</v>
+        <v>0.7812387645244598</v>
       </c>
     </row>
     <row r="17">
@@ -983,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8138515688478947</v>
+        <v>0.8863522615283728</v>
       </c>
     </row>
     <row r="18">
@@ -991,7 +1191,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.383196674287319</v>
+        <v>5.475935145281255</v>
       </c>
     </row>
     <row r="19">
@@ -999,7 +1199,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.31914605665952</v>
+        <v>0.6925724791362882</v>
       </c>
     </row>
     <row r="20">
@@ -1007,7 +1207,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.180510755628347</v>
+        <v>0.8549786824733019</v>
       </c>
     </row>
     <row r="21">
@@ -1015,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7177500892430544</v>
+        <v>2.239589654840529</v>
       </c>
     </row>
     <row r="22">
@@ -1023,7 +1223,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.9997352175414562</v>
+        <v>0.67268808465451</v>
       </c>
     </row>
     <row r="23">
@@ -1031,7 +1231,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.8438110081478953</v>
+        <v>0.9418226107954979</v>
       </c>
     </row>
     <row r="24">
@@ -1039,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1.396666845306754</v>
+        <v>1.554223558865488</v>
       </c>
     </row>
     <row r="25">
@@ -1047,7 +1247,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1.411481938324869</v>
+        <v>0.8701225994154811</v>
       </c>
     </row>
     <row r="26">
@@ -1057,7 +1257,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40.60918879508972</v>
+        <v>41.20404577255249</v>
       </c>
     </row>
   </sheetData>
@@ -1110,13 +1310,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.082506899357989</v>
+        <v>1.082506901217855</v>
       </c>
       <c r="C3" t="n">
-        <v>1.108714765536125</v>
+        <v>1.108714763646543</v>
       </c>
       <c r="D3" t="n">
-        <v>1.116647951341172</v>
+        <v>1.116647949430622</v>
       </c>
     </row>
     <row r="4">
@@ -1124,13 +1324,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.085155920588716</v>
+        <v>1.085172428532646</v>
       </c>
       <c r="C4" t="n">
-        <v>1.083541618317136</v>
+        <v>1.083525137789854</v>
       </c>
       <c r="D4" t="n">
-        <v>1.092370868895471</v>
+        <v>1.092446770289794</v>
       </c>
     </row>
     <row r="5">
@@ -1138,13 +1338,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.084896726285521</v>
+        <v>1.084894281094971</v>
       </c>
       <c r="C5" t="n">
-        <v>1.083519142020685</v>
+        <v>1.083521583961463</v>
       </c>
       <c r="D5" t="n">
-        <v>1.088560113696773</v>
+        <v>1.088555325814936</v>
       </c>
     </row>
     <row r="6">
@@ -1152,13 +1352,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.085788681950332</v>
+        <v>1.085780207383593</v>
       </c>
       <c r="C6" t="n">
-        <v>1.08140123030728</v>
+        <v>1.081409670694627</v>
       </c>
       <c r="D6" t="n">
-        <v>1.092487165108793</v>
+        <v>1.092462611383728</v>
       </c>
     </row>
     <row r="7">
@@ -1166,13 +1366,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.085843807352191</v>
+        <v>1.085844199019021</v>
       </c>
       <c r="C7" t="n">
-        <v>1.081372453153084</v>
+        <v>1.081372063100127</v>
       </c>
       <c r="D7" t="n">
-        <v>1.092816350625413</v>
+        <v>1.092817004458691</v>
       </c>
     </row>
     <row r="8">
@@ -1180,13 +1380,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.087581641035745</v>
+        <v>1.087581624665223</v>
       </c>
       <c r="C8" t="n">
-        <v>1.080896431802753</v>
+        <v>1.080896448070517</v>
       </c>
       <c r="D8" t="n">
-        <v>1.097838597634867</v>
+        <v>1.097838798674772</v>
       </c>
     </row>
     <row r="9">
@@ -1194,13 +1394,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.08956197254733</v>
+        <v>1.089561973952372</v>
       </c>
       <c r="C9" t="n">
-        <v>1.080393750413608</v>
+        <v>1.08039374902051</v>
       </c>
       <c r="D9" t="n">
-        <v>1.103557869009941</v>
+        <v>1.103557876746293</v>
       </c>
     </row>
     <row r="10">
@@ -1208,13 +1408,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.089446739410079</v>
+        <v>1.089446738510624</v>
       </c>
       <c r="C10" t="n">
-        <v>1.080463211103141</v>
+        <v>1.080463211875158</v>
       </c>
       <c r="D10" t="n">
-        <v>1.103203366996099</v>
+        <v>1.10320336477201</v>
       </c>
     </row>
     <row r="11">
@@ -1222,13 +1422,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.087382870688302</v>
+        <v>1.087382871015311</v>
       </c>
       <c r="C11" t="n">
-        <v>1.081024364607592</v>
+        <v>1.081024364288227</v>
       </c>
       <c r="D11" t="n">
-        <v>1.097228971747625</v>
+        <v>1.097228972669168</v>
       </c>
     </row>
     <row r="12">
@@ -1236,13 +1436,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.085751058803235</v>
+        <v>1.085751058786831</v>
       </c>
       <c r="C12" t="n">
-        <v>1.081438774602633</v>
+        <v>1.081438774618908</v>
       </c>
       <c r="D12" t="n">
-        <v>1.092536870006026</v>
+        <v>1.092536869974566</v>
       </c>
     </row>
     <row r="13">
@@ -1250,13 +1450,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.085839884715513</v>
+        <v>1.085839895625834</v>
       </c>
       <c r="C13" t="n">
-        <v>1.081376359509471</v>
+        <v>1.081376348661052</v>
       </c>
       <c r="D13" t="n">
-        <v>1.092808378917528</v>
+        <v>1.092808414456462</v>
       </c>
     </row>
     <row r="14">
@@ -1264,13 +1464,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.087581222306387</v>
+        <v>1.087581214578248</v>
       </c>
       <c r="C14" t="n">
-        <v>1.080896847959328</v>
+        <v>1.080896855639131</v>
       </c>
       <c r="D14" t="n">
-        <v>1.097837274776257</v>
+        <v>1.097837253224714</v>
       </c>
     </row>
     <row r="15">
@@ -1278,13 +1478,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.089561976174524</v>
+        <v>1.089561976037969</v>
       </c>
       <c r="C15" t="n">
-        <v>1.080393746817104</v>
+        <v>1.080393746952347</v>
       </c>
       <c r="D15" t="n">
-        <v>1.103557844108743</v>
+        <v>1.103557843173295</v>
       </c>
     </row>
     <row r="16">
@@ -1292,13 +1492,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.089446740675063</v>
+        <v>1.089446740718507</v>
       </c>
       <c r="C16" t="n">
-        <v>1.08046320972856</v>
+        <v>1.080463209685483</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10320336944272</v>
+        <v>1.103203369534604</v>
       </c>
     </row>
     <row r="17">
@@ -1306,13 +1506,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.087382870966316</v>
+        <v>1.087382870965333</v>
       </c>
       <c r="C17" t="n">
-        <v>1.081024364336935</v>
+        <v>1.081024364337912</v>
       </c>
       <c r="D17" t="n">
-        <v>1.097228972598588</v>
+        <v>1.097228972597122</v>
       </c>
     </row>
     <row r="18">
@@ -1320,13 +1520,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.085751058787094</v>
+        <v>1.085751058787103</v>
       </c>
       <c r="C18" t="n">
-        <v>1.081438774618647</v>
+        <v>1.081438774618638</v>
       </c>
       <c r="D18" t="n">
-        <v>1.092536869974833</v>
+        <v>1.092536869974847</v>
       </c>
     </row>
     <row r="19">
@@ -1334,13 +1534,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.085839884685582</v>
+        <v>1.085839895625836</v>
       </c>
       <c r="C19" t="n">
-        <v>1.081376359539232</v>
+        <v>1.081376348661049</v>
       </c>
       <c r="D19" t="n">
-        <v>1.092808378819548</v>
+        <v>1.092808414456468</v>
       </c>
     </row>
     <row r="20">
@@ -1348,13 +1548,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.08758122232776</v>
+        <v>1.087581214578326</v>
       </c>
       <c r="C20" t="n">
-        <v>1.080896847938089</v>
+        <v>1.080896855639052</v>
       </c>
       <c r="D20" t="n">
-        <v>1.097837274835859</v>
+        <v>1.097837253224971</v>
       </c>
     </row>
     <row r="21">
@@ -1362,13 +1562,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.089561976174924</v>
+        <v>1.089561976037903</v>
       </c>
       <c r="C21" t="n">
-        <v>1.08039374681671</v>
+        <v>1.080393746952411</v>
       </c>
       <c r="D21" t="n">
-        <v>1.103557844111407</v>
+        <v>1.103557843173107</v>
       </c>
     </row>
     <row r="22">
@@ -1376,13 +1576,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.089446740674924</v>
+        <v>1.089446740718513</v>
       </c>
       <c r="C22" t="n">
-        <v>1.080463209728697</v>
+        <v>1.080463209685477</v>
       </c>
       <c r="D22" t="n">
-        <v>1.103203369442414</v>
+        <v>1.103203369534613</v>
       </c>
     </row>
     <row r="23">
@@ -1390,13 +1590,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1.08738287096632</v>
+        <v>1.087382870965331</v>
       </c>
       <c r="C23" t="n">
-        <v>1.081024364336931</v>
+        <v>1.081024364337914</v>
       </c>
       <c r="D23" t="n">
-        <v>1.097228972598594</v>
+        <v>1.097228972597113</v>
       </c>
     </row>
     <row r="24">
@@ -1404,13 +1604,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1.085751058787094</v>
+        <v>1.085751058787104</v>
       </c>
       <c r="C24" t="n">
-        <v>1.081438774618647</v>
+        <v>1.081438774618637</v>
       </c>
       <c r="D24" t="n">
-        <v>1.092536869974833</v>
+        <v>1.092536869974849</v>
       </c>
     </row>
     <row r="25">
@@ -1418,13 +1618,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1.085839884835195</v>
+        <v>1.085839895625837</v>
       </c>
       <c r="C25" t="n">
-        <v>1.081376359390468</v>
+        <v>1.081376348661048</v>
       </c>
       <c r="D25" t="n">
-        <v>1.092808379307082</v>
+        <v>1.092808414456473</v>
       </c>
     </row>
     <row r="26">
@@ -1432,13 +1632,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1.087581222221749</v>
+        <v>1.087581214578372</v>
       </c>
       <c r="C26" t="n">
-        <v>1.080896848043437</v>
+        <v>1.080896855639007</v>
       </c>
       <c r="D26" t="n">
-        <v>1.097837274540226</v>
+        <v>1.097837253225124</v>
       </c>
     </row>
   </sheetData>
@@ -2048,19 +2248,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>42.00577081031001</v>
+        <v>42.00577081088423</v>
       </c>
       <c r="C3" t="n">
-        <v>41.91135576102806</v>
+        <v>41.91135576159457</v>
       </c>
       <c r="D3" t="n">
-        <v>41.95935348559801</v>
+        <v>41.95935348617113</v>
       </c>
       <c r="E3" t="n">
-        <v>42.30342051718402</v>
+        <v>42.30342051743694</v>
       </c>
       <c r="F3" t="n">
-        <v>42.30178083959822</v>
+        <v>42.30178083985014</v>
       </c>
     </row>
     <row r="4">
@@ -2068,19 +2268,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.12981973544962</v>
+        <v>41.1298198478313</v>
       </c>
       <c r="C4" t="n">
-        <v>41.01331593238662</v>
+        <v>41.01331604301953</v>
       </c>
       <c r="D4" t="n">
-        <v>41.0787121354473</v>
+        <v>41.0787122476073</v>
       </c>
       <c r="E4" t="n">
-        <v>41.41727058482651</v>
+        <v>41.4196300062613</v>
       </c>
       <c r="F4" t="n">
-        <v>41.41493803714216</v>
+        <v>41.41728895209967</v>
       </c>
     </row>
     <row r="5">
@@ -2088,19 +2288,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.11032497442375</v>
+        <v>41.11032497234608</v>
       </c>
       <c r="C5" t="n">
-        <v>41.01329245812688</v>
+        <v>41.01329245800957</v>
       </c>
       <c r="D5" t="n">
-        <v>41.07122015265739</v>
+        <v>41.07122015090437</v>
       </c>
       <c r="E5" t="n">
-        <v>41.03216790131585</v>
+        <v>41.0332076338772</v>
       </c>
       <c r="F5" t="n">
-        <v>41.02900095319362</v>
+        <v>41.03004840510501</v>
       </c>
     </row>
     <row r="6">
@@ -2108,19 +2308,19 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.07935584233569</v>
+        <v>41.07935584222917</v>
       </c>
       <c r="C6" t="n">
-        <v>41.01330469303805</v>
+        <v>41.01330469292704</v>
       </c>
       <c r="D6" t="n">
-        <v>41.05274877113042</v>
+        <v>41.05274877101983</v>
       </c>
       <c r="E6" t="n">
-        <v>41.01757397986028</v>
+        <v>41.01756522469758</v>
       </c>
       <c r="F6" t="n">
-        <v>41.01333097529621</v>
+        <v>41.01333150885741</v>
       </c>
     </row>
     <row r="7">
@@ -2128,19 +2328,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.07951643023659</v>
+        <v>41.07951643026905</v>
       </c>
       <c r="C7" t="n">
-        <v>41.01330628941068</v>
+        <v>41.01330628944115</v>
       </c>
       <c r="D7" t="n">
-        <v>41.05285510248594</v>
+        <v>41.05285510251809</v>
       </c>
       <c r="E7" t="n">
-        <v>41.01875449933468</v>
+        <v>41.01874893047633</v>
       </c>
       <c r="F7" t="n">
-        <v>41.01435940369352</v>
+        <v>41.01435387686005</v>
       </c>
     </row>
     <row r="8">
@@ -2148,19 +2348,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41.1107040603574</v>
+        <v>41.11070406027971</v>
       </c>
       <c r="C8" t="n">
-        <v>41.01329538952446</v>
+        <v>41.01329538944848</v>
       </c>
       <c r="D8" t="n">
-        <v>41.07149821164629</v>
+        <v>41.07149821156884</v>
       </c>
       <c r="E8" t="n">
-        <v>41.02059812969578</v>
+        <v>41.02059774185243</v>
       </c>
       <c r="F8" t="n">
-        <v>41.01416547354272</v>
+        <v>41.01416502940393</v>
       </c>
     </row>
     <row r="9">
@@ -2168,19 +2368,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41.1476849250687</v>
+        <v>41.14768492507029</v>
       </c>
       <c r="C9" t="n">
-        <v>41.01328659544365</v>
+        <v>41.01328659544366</v>
       </c>
       <c r="D9" t="n">
-        <v>41.09360217422134</v>
+        <v>41.09360217422266</v>
       </c>
       <c r="E9" t="n">
-        <v>41.02216683789604</v>
+        <v>41.02216684353032</v>
       </c>
       <c r="F9" t="n">
-        <v>41.01330718342805</v>
+        <v>41.01330718340842</v>
       </c>
     </row>
     <row r="10">
@@ -2188,19 +2388,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41.14741387909959</v>
+        <v>41.14741387467972</v>
       </c>
       <c r="C10" t="n">
-        <v>41.0132857853983</v>
+        <v>41.01328578105444</v>
       </c>
       <c r="D10" t="n">
-        <v>41.09342353118775</v>
+        <v>41.09342352677695</v>
       </c>
       <c r="E10" t="n">
-        <v>41.02214147287589</v>
+        <v>41.02214144322139</v>
       </c>
       <c r="F10" t="n">
-        <v>41.01328208916999</v>
+        <v>41.01328205989962</v>
       </c>
     </row>
     <row r="11">
@@ -2208,19 +2408,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41.11027915589319</v>
+        <v>41.11027915596995</v>
       </c>
       <c r="C11" t="n">
-        <v>41.01329314634565</v>
+        <v>41.01329314634554</v>
       </c>
       <c r="D11" t="n">
-        <v>41.07121768360647</v>
+        <v>41.07121768367048</v>
       </c>
       <c r="E11" t="n">
-        <v>41.01970633961107</v>
+        <v>41.01970633992908</v>
       </c>
       <c r="F11" t="n">
-        <v>41.01328868154879</v>
+        <v>41.01328868154356</v>
       </c>
     </row>
     <row r="12">
@@ -2228,19 +2428,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>41.07935584812463</v>
+        <v>41.07935584812449</v>
       </c>
       <c r="C12" t="n">
-        <v>41.01330468456636</v>
+        <v>41.01330468456637</v>
       </c>
       <c r="D12" t="n">
-        <v>41.05274875626218</v>
+        <v>41.0527487562622</v>
       </c>
       <c r="E12" t="n">
-        <v>41.01771599669642</v>
+        <v>41.01771599669743</v>
       </c>
       <c r="F12" t="n">
-        <v>41.01333644771763</v>
+        <v>41.01333644771902</v>
       </c>
     </row>
     <row r="13">
@@ -2248,19 +2448,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41.07951642956036</v>
+        <v>41.07951643019253</v>
       </c>
       <c r="C13" t="n">
-        <v>41.01330628859894</v>
+        <v>41.01330628922302</v>
       </c>
       <c r="D13" t="n">
-        <v>41.0528551017791</v>
+        <v>41.05285510241018</v>
       </c>
       <c r="E13" t="n">
-        <v>41.0188073734929</v>
+        <v>41.01880816433339</v>
       </c>
       <c r="F13" t="n">
-        <v>41.01441204317918</v>
+        <v>41.01441282695558</v>
       </c>
     </row>
     <row r="14">
@@ -2268,19 +2468,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>41.11070406036653</v>
+        <v>41.1107040603554</v>
       </c>
       <c r="C14" t="n">
-        <v>41.01329538951959</v>
+        <v>41.01329538951955</v>
       </c>
       <c r="D14" t="n">
-        <v>41.07149821165338</v>
+        <v>41.07149821164409</v>
       </c>
       <c r="E14" t="n">
-        <v>41.02060047065594</v>
+        <v>41.0206005213104</v>
       </c>
       <c r="F14" t="n">
-        <v>41.01416836505349</v>
+        <v>41.01416842373731</v>
       </c>
     </row>
     <row r="15">
@@ -2288,19 +2488,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41.14768492507529</v>
+        <v>41.14768492506882</v>
       </c>
       <c r="C15" t="n">
-        <v>41.01328659545007</v>
+        <v>41.01328659544368</v>
       </c>
       <c r="D15" t="n">
-        <v>41.09360217422793</v>
+        <v>41.09360217422145</v>
       </c>
       <c r="E15" t="n">
-        <v>41.02216680120461</v>
+        <v>41.0221668003448</v>
       </c>
       <c r="F15" t="n">
-        <v>41.01330718319748</v>
+        <v>41.01330718308503</v>
       </c>
     </row>
     <row r="16">
@@ -2308,19 +2508,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41.14741387467964</v>
+        <v>41.14741387467976</v>
       </c>
       <c r="C16" t="n">
-        <v>41.01328578105449</v>
+        <v>41.01328578105448</v>
       </c>
       <c r="D16" t="n">
-        <v>41.09342352677687</v>
+        <v>41.09342352677697</v>
       </c>
       <c r="E16" t="n">
-        <v>41.02214144328173</v>
+        <v>41.02214144328415</v>
       </c>
       <c r="F16" t="n">
-        <v>41.01328205987518</v>
+        <v>41.01328205987468</v>
       </c>
     </row>
     <row r="17">
@@ -2328,19 +2528,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>41.11027915596992</v>
+        <v>41.11027915596994</v>
       </c>
       <c r="C17" t="n">
         <v>41.01329314634553</v>
       </c>
       <c r="D17" t="n">
-        <v>41.07121768367045</v>
+        <v>41.07121768367048</v>
       </c>
       <c r="E17" t="n">
-        <v>41.01970633993066</v>
+        <v>41.01970633993006</v>
       </c>
       <c r="F17" t="n">
-        <v>41.0132886815449</v>
+        <v>41.01328868154429</v>
       </c>
     </row>
     <row r="18">
@@ -2348,19 +2548,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41.07935584812448</v>
+        <v>41.07935584812449</v>
       </c>
       <c r="C18" t="n">
         <v>41.01330468456636</v>
       </c>
       <c r="D18" t="n">
-        <v>41.05274875626218</v>
+        <v>41.05274875626219</v>
       </c>
       <c r="E18" t="n">
-        <v>41.01771599669751</v>
+        <v>41.01771599669734</v>
       </c>
       <c r="F18" t="n">
-        <v>41.01333644771911</v>
+        <v>41.01333644771893</v>
       </c>
     </row>
     <row r="19">
@@ -2368,19 +2568,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41.07951642955862</v>
+        <v>41.07951643019253</v>
       </c>
       <c r="C19" t="n">
-        <v>41.01330628859722</v>
+        <v>41.01330628922302</v>
       </c>
       <c r="D19" t="n">
-        <v>41.05285510177736</v>
+        <v>41.05285510241018</v>
       </c>
       <c r="E19" t="n">
-        <v>41.01880737130583</v>
+        <v>41.01880816433347</v>
       </c>
       <c r="F19" t="n">
-        <v>41.01441204101165</v>
+        <v>41.01441282695566</v>
       </c>
     </row>
     <row r="20">
@@ -2388,19 +2588,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>41.11070406036657</v>
+        <v>41.11070406035539</v>
       </c>
       <c r="C20" t="n">
-        <v>41.0132953895196</v>
+        <v>41.01329538951955</v>
       </c>
       <c r="D20" t="n">
-        <v>41.07149821165341</v>
+        <v>41.07149821164409</v>
       </c>
       <c r="E20" t="n">
-        <v>41.0206004705159</v>
+        <v>41.02060052131556</v>
       </c>
       <c r="F20" t="n">
-        <v>41.01416836489125</v>
+        <v>41.0141684237424</v>
       </c>
     </row>
     <row r="21">
@@ -2408,19 +2608,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>41.14768492507539</v>
+        <v>41.14768492506882</v>
       </c>
       <c r="C21" t="n">
-        <v>41.01328659545017</v>
+        <v>41.01328659544367</v>
       </c>
       <c r="D21" t="n">
-        <v>41.09360217422802</v>
+        <v>41.09360217422145</v>
       </c>
       <c r="E21" t="n">
-        <v>41.0221668012084</v>
+        <v>41.02216680034475</v>
       </c>
       <c r="F21" t="n">
-        <v>41.01330718319917</v>
+        <v>41.01330718308504</v>
       </c>
     </row>
     <row r="22">
@@ -2428,19 +2628,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>41.14741387467963</v>
+        <v>41.14741387467976</v>
       </c>
       <c r="C22" t="n">
         <v>41.01328578105448</v>
       </c>
       <c r="D22" t="n">
-        <v>41.09342352677687</v>
+        <v>41.09342352677698</v>
       </c>
       <c r="E22" t="n">
-        <v>41.02214144328171</v>
+        <v>41.02214144328416</v>
       </c>
       <c r="F22" t="n">
-        <v>41.01328205987518</v>
+        <v>41.01328205987469</v>
       </c>
     </row>
     <row r="23">
@@ -2448,19 +2648,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>41.11027915596993</v>
+        <v>41.11027915596994</v>
       </c>
       <c r="C23" t="n">
-        <v>41.01329314634554</v>
+        <v>41.01329314634553</v>
       </c>
       <c r="D23" t="n">
-        <v>41.07121768367046</v>
+        <v>41.07121768367048</v>
       </c>
       <c r="E23" t="n">
-        <v>41.01970633993066</v>
+        <v>41.0197063399299</v>
       </c>
       <c r="F23" t="n">
-        <v>41.01328868154489</v>
+        <v>41.01328868154413</v>
       </c>
     </row>
     <row r="24">
@@ -2471,16 +2671,16 @@
         <v>41.07935584812449</v>
       </c>
       <c r="C24" t="n">
-        <v>41.01330468456636</v>
+        <v>41.01330468456637</v>
       </c>
       <c r="D24" t="n">
-        <v>41.05274875626218</v>
+        <v>41.0527487562622</v>
       </c>
       <c r="E24" t="n">
-        <v>41.01771599669751</v>
+        <v>41.01771599669728</v>
       </c>
       <c r="F24" t="n">
-        <v>41.01333644771911</v>
+        <v>41.01333644771887</v>
       </c>
     </row>
     <row r="25">
@@ -2488,19 +2688,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>41.07951642956731</v>
+        <v>41.07951643019254</v>
       </c>
       <c r="C25" t="n">
-        <v>41.0133062886058</v>
+        <v>41.01330628922302</v>
       </c>
       <c r="D25" t="n">
-        <v>41.05285510178602</v>
+        <v>41.05285510241019</v>
       </c>
       <c r="E25" t="n">
-        <v>41.01880738215395</v>
+        <v>41.01880816433355</v>
       </c>
       <c r="F25" t="n">
-        <v>41.01441205176288</v>
+        <v>41.01441282695573</v>
       </c>
     </row>
     <row r="26">
@@ -2508,19 +2708,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>41.11070406036641</v>
+        <v>41.1107040603554</v>
       </c>
       <c r="C26" t="n">
-        <v>41.01329538951959</v>
+        <v>41.01329538951954</v>
       </c>
       <c r="D26" t="n">
-        <v>41.0714982116533</v>
+        <v>41.07149821164409</v>
       </c>
       <c r="E26" t="n">
-        <v>41.02060047121062</v>
+        <v>41.02060052131865</v>
       </c>
       <c r="F26" t="n">
-        <v>41.01416836569609</v>
+        <v>41.01416842374546</v>
       </c>
     </row>
   </sheetData>
@@ -2629,34 +2829,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>37.25055141180063</v>
+        <v>37.25055143791961</v>
       </c>
       <c r="C3" t="n">
-        <v>74.25037183998857</v>
+        <v>74.25037185571284</v>
       </c>
       <c r="D3" t="n">
-        <v>34.30632890306791</v>
+        <v>34.30632890561256</v>
       </c>
       <c r="E3" t="n">
-        <v>38.88529911075283</v>
+        <v>38.88529911202312</v>
       </c>
       <c r="F3" t="n">
-        <v>39.7624919110204</v>
+        <v>39.76249191205618</v>
       </c>
       <c r="G3" t="n">
-        <v>41.6169478452691</v>
+        <v>41.6169478457869</v>
       </c>
       <c r="H3" t="n">
-        <v>7.462855554843103</v>
+        <v>7.462855573430432</v>
       </c>
       <c r="I3" t="n">
-        <v>13.83019947872867</v>
+        <v>13.83019949601609</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.693304788444678</v>
+        <v>-1.693304777724028</v>
       </c>
       <c r="K3" t="n">
-        <v>20.90526651349445</v>
+        <v>20.90526651885144</v>
       </c>
     </row>
     <row r="4">
@@ -2664,34 +2864,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>90.73470696138538</v>
+        <v>90.73471205061495</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3216281499675</v>
+        <v>106.3216312105566</v>
       </c>
       <c r="D4" t="n">
-        <v>39.46045058479255</v>
+        <v>39.46045107921293</v>
       </c>
       <c r="E4" t="n">
-        <v>41.46137898213255</v>
+        <v>41.46137922892487</v>
       </c>
       <c r="F4" t="n">
-        <v>41.88477181327753</v>
+        <v>41.88477201494423</v>
       </c>
       <c r="G4" t="n">
-        <v>42.67934442369047</v>
+        <v>42.67934452450825</v>
       </c>
       <c r="H4" t="n">
-        <v>22.64640931278673</v>
+        <v>22.82152747052476</v>
       </c>
       <c r="I4" t="n">
-        <v>26.46403581971435</v>
+        <v>26.62577622512355</v>
       </c>
       <c r="J4" t="n">
-        <v>5.765392384146708</v>
+        <v>5.865451095280497</v>
       </c>
       <c r="K4" t="n">
-        <v>24.61727913728969</v>
+        <v>24.66726867384637</v>
       </c>
     </row>
     <row r="5">
@@ -2699,34 +2899,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>110.1315041775737</v>
+        <v>110.1314989559164</v>
       </c>
       <c r="C5" t="n">
-        <v>110.4914200233448</v>
+        <v>110.4914168971747</v>
       </c>
       <c r="D5" t="n">
-        <v>36.95360646311656</v>
+        <v>36.95360596465075</v>
       </c>
       <c r="E5" t="n">
-        <v>36.98610866332658</v>
+        <v>36.98610841500082</v>
       </c>
       <c r="F5" t="n">
-        <v>36.97807826621605</v>
+        <v>36.97807806028067</v>
       </c>
       <c r="G5" t="n">
-        <v>36.99098749926247</v>
+        <v>36.99098739634297</v>
       </c>
       <c r="H5" t="n">
-        <v>46.58156021313761</v>
+        <v>46.47880173806641</v>
       </c>
       <c r="I5" t="n">
-        <v>47.81293079297477</v>
+        <v>47.72161888530924</v>
       </c>
       <c r="J5" t="n">
-        <v>20.5772846519119</v>
+        <v>20.52171863764992</v>
       </c>
       <c r="K5" t="n">
-        <v>28.78486821414802</v>
+        <v>28.75715175508025</v>
       </c>
     </row>
     <row r="6">
@@ -2734,34 +2934,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>90.10301022158355</v>
+        <v>90.1030103232589</v>
       </c>
       <c r="C6" t="n">
-        <v>90.80009351922341</v>
+        <v>90.80009356614275</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47864266153505</v>
+        <v>30.47864266253792</v>
       </c>
       <c r="E6" t="n">
-        <v>30.51341244550536</v>
+        <v>30.51341244551946</v>
       </c>
       <c r="F6" t="n">
-        <v>30.48408947334183</v>
+        <v>30.48408947637567</v>
       </c>
       <c r="G6" t="n">
-        <v>30.5064266769749</v>
+        <v>30.5064266784589</v>
       </c>
       <c r="H6" t="n">
-        <v>60.4479905345278</v>
+        <v>60.37189164392185</v>
       </c>
       <c r="I6" t="n">
-        <v>60.10836461522513</v>
+        <v>60.03690118564934</v>
       </c>
       <c r="J6" t="n">
-        <v>29.84685620220289</v>
+        <v>29.8023417217814</v>
       </c>
       <c r="K6" t="n">
-        <v>30.18455687710813</v>
+        <v>30.16229514003503</v>
       </c>
     </row>
     <row r="7">
@@ -2769,34 +2969,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91.58544320750396</v>
+        <v>91.58544321362238</v>
       </c>
       <c r="C7" t="n">
-        <v>91.57882606925968</v>
+        <v>91.57882607308026</v>
       </c>
       <c r="D7" t="n">
-        <v>30.52504472346119</v>
+        <v>30.52504472409668</v>
       </c>
       <c r="E7" t="n">
-        <v>30.52500358039824</v>
+        <v>30.52500358071557</v>
       </c>
       <c r="F7" t="n">
-        <v>30.52520195416616</v>
+        <v>30.52520195442339</v>
       </c>
       <c r="G7" t="n">
-        <v>30.52509608012794</v>
+        <v>30.52509608025694</v>
       </c>
       <c r="H7" t="n">
-        <v>61.18296518921964</v>
+        <v>61.18631241131764</v>
       </c>
       <c r="I7" t="n">
-        <v>61.13758251659195</v>
+        <v>61.13823618412264</v>
       </c>
       <c r="J7" t="n">
-        <v>30.56946499104941</v>
+        <v>30.56925145962059</v>
       </c>
       <c r="K7" t="n">
-        <v>30.54686874662373</v>
+        <v>30.54673987694646</v>
       </c>
     </row>
     <row r="8">
@@ -2804,34 +3004,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112.4849285808197</v>
+        <v>112.4849285757944</v>
       </c>
       <c r="C8" t="n">
-        <v>111.7800974068036</v>
+        <v>111.7800974037958</v>
       </c>
       <c r="D8" t="n">
-        <v>37.04642580945036</v>
+        <v>37.04642580897113</v>
       </c>
       <c r="E8" t="n">
-        <v>37.01159054791068</v>
+        <v>37.01159054767197</v>
       </c>
       <c r="F8" t="n">
-        <v>37.04122864330689</v>
+        <v>37.04122864310875</v>
       </c>
       <c r="G8" t="n">
-        <v>37.01872848197155</v>
+        <v>37.01872848187251</v>
       </c>
       <c r="H8" t="n">
-        <v>74.81398235371347</v>
+        <v>74.81436497211885</v>
       </c>
       <c r="I8" t="n">
-        <v>74.24669490158161</v>
+        <v>74.24705226833126</v>
       </c>
       <c r="J8" t="n">
-        <v>37.02065710917223</v>
+        <v>37.02087379024079</v>
       </c>
       <c r="K8" t="n">
-        <v>37.00311181382018</v>
+        <v>37.00321989353031</v>
       </c>
     </row>
     <row r="9">
@@ -2839,34 +3039,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132.1828816397248</v>
+        <v>132.1828816433474</v>
       </c>
       <c r="C9" t="n">
-        <v>131.3502063638099</v>
+        <v>131.3502063659727</v>
       </c>
       <c r="D9" t="n">
-        <v>43.53028168002225</v>
+        <v>43.53028168036469</v>
       </c>
       <c r="E9" t="n">
-        <v>43.4888189831541</v>
+        <v>43.48881898332452</v>
       </c>
       <c r="F9" t="n">
-        <v>43.52390821424404</v>
+        <v>43.52390821438647</v>
       </c>
       <c r="G9" t="n">
-        <v>43.49721428525695</v>
+        <v>43.49721428532813</v>
       </c>
       <c r="H9" t="n">
-        <v>87.86489751861214</v>
+        <v>87.86490892293523</v>
       </c>
       <c r="I9" t="n">
-        <v>87.20034956625695</v>
+        <v>87.2003740828346</v>
       </c>
       <c r="J9" t="n">
-        <v>43.47295468917262</v>
+        <v>43.47297333869658</v>
       </c>
       <c r="K9" t="n">
-        <v>43.46537243293862</v>
+        <v>43.46538187671602</v>
       </c>
     </row>
     <row r="10">
@@ -2874,34 +3074,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>130.4072931691489</v>
+        <v>130.4072929677857</v>
       </c>
       <c r="C10" t="n">
-        <v>130.418549812998</v>
+        <v>130.4185496920055</v>
       </c>
       <c r="D10" t="n">
-        <v>43.47493264258224</v>
+        <v>43.47493262306737</v>
       </c>
       <c r="E10" t="n">
-        <v>43.47499818370492</v>
+        <v>43.47499817396505</v>
       </c>
       <c r="F10" t="n">
-        <v>43.47466052873749</v>
+        <v>43.47466052076354</v>
       </c>
       <c r="G10" t="n">
-        <v>43.47483859752345</v>
+        <v>43.47483859353713</v>
       </c>
       <c r="H10" t="n">
-        <v>86.93814413879666</v>
+        <v>86.93813977440415</v>
       </c>
       <c r="I10" t="n">
-        <v>86.94789391986238</v>
+        <v>86.94789123994893</v>
       </c>
       <c r="J10" t="n">
-        <v>43.47395900159292</v>
+        <v>43.47395772871176</v>
       </c>
       <c r="K10" t="n">
-        <v>43.47446639941604</v>
+        <v>43.47446577743224</v>
       </c>
     </row>
     <row r="11">
@@ -2909,34 +3109,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>109.2321277224402</v>
+        <v>109.2321279276741</v>
       </c>
       <c r="C11" t="n">
-        <v>110.0711280791177</v>
+        <v>110.0711282018977</v>
       </c>
       <c r="D11" t="n">
-        <v>36.94467583985877</v>
+        <v>36.94467585941053</v>
       </c>
       <c r="E11" t="n">
-        <v>36.98617780269848</v>
+        <v>36.98617781243808</v>
       </c>
       <c r="F11" t="n">
-        <v>36.9508982609282</v>
+        <v>36.95089826901793</v>
       </c>
       <c r="G11" t="n">
-        <v>36.97769364724526</v>
+        <v>36.97769365128823</v>
       </c>
       <c r="H11" t="n">
-        <v>73.01145857445852</v>
+        <v>73.01146101532713</v>
       </c>
       <c r="I11" t="n">
-        <v>73.68959608380278</v>
+        <v>73.68959816410531</v>
       </c>
       <c r="J11" t="n">
-        <v>36.96577055956991</v>
+        <v>36.96577180741791</v>
       </c>
       <c r="K11" t="n">
-        <v>36.99151700831349</v>
+        <v>36.99151763060286</v>
       </c>
     </row>
     <row r="12">
@@ -2944,34 +3144,34 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>90.1073308021639</v>
+        <v>90.10733079819606</v>
       </c>
       <c r="C12" t="n">
-        <v>90.80119241551621</v>
+        <v>90.80119241368692</v>
       </c>
       <c r="D12" t="n">
-        <v>30.47863926157178</v>
+        <v>30.4786392615341</v>
       </c>
       <c r="E12" t="n">
-        <v>30.51341088313296</v>
+        <v>30.51341088313324</v>
       </c>
       <c r="F12" t="n">
-        <v>30.48410237291587</v>
+        <v>30.48410237279765</v>
       </c>
       <c r="G12" t="n">
-        <v>30.50642889444001</v>
+        <v>30.5064288943822</v>
       </c>
       <c r="H12" t="n">
-        <v>60.23445139657579</v>
+        <v>60.23445126363148</v>
       </c>
       <c r="I12" t="n">
-        <v>60.79359637596934</v>
+        <v>60.79359633928522</v>
       </c>
       <c r="J12" t="n">
-        <v>30.49809787452232</v>
+        <v>30.4980978732809</v>
       </c>
       <c r="K12" t="n">
-        <v>30.51877996576181</v>
+        <v>30.51877996590295</v>
       </c>
     </row>
     <row r="13">
@@ -2979,34 +3179,34 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>91.58543805398166</v>
+        <v>91.5854380827646</v>
       </c>
       <c r="C13" t="n">
-        <v>91.57882590270221</v>
+        <v>91.57882592001691</v>
       </c>
       <c r="D13" t="n">
-        <v>30.52504476293008</v>
+        <v>30.52504476573318</v>
       </c>
       <c r="E13" t="n">
-        <v>30.52500359757829</v>
+        <v>30.52500359897793</v>
       </c>
       <c r="F13" t="n">
-        <v>30.52520197859699</v>
+        <v>30.52520197973765</v>
       </c>
       <c r="G13" t="n">
-        <v>30.52509609292408</v>
+        <v>30.52509609349431</v>
       </c>
       <c r="H13" t="n">
-        <v>61.14060101782795</v>
+        <v>61.14066094014781</v>
       </c>
       <c r="I13" t="n">
-        <v>61.12547595326606</v>
+        <v>61.12553028694049</v>
       </c>
       <c r="J13" t="n">
-        <v>30.57080143178487</v>
+        <v>30.57083479765598</v>
       </c>
       <c r="K13" t="n">
-        <v>30.5478717183235</v>
+        <v>30.54788838470175</v>
       </c>
     </row>
     <row r="14">
@@ -3014,34 +3214,34 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>112.4849286130253</v>
+        <v>112.4849285836827</v>
       </c>
       <c r="C14" t="n">
-        <v>111.7800974260559</v>
+        <v>111.7800974084793</v>
       </c>
       <c r="D14" t="n">
-        <v>37.04642581302014</v>
+        <v>37.04642581021124</v>
       </c>
       <c r="E14" t="n">
-        <v>37.01159054972034</v>
+        <v>37.01159054832053</v>
       </c>
       <c r="F14" t="n">
-        <v>37.04122864459066</v>
+        <v>37.04122864343285</v>
       </c>
       <c r="G14" t="n">
-        <v>37.01872848261665</v>
+        <v>37.01872848203801</v>
       </c>
       <c r="H14" t="n">
-        <v>74.81043387951833</v>
+        <v>74.81037494371277</v>
       </c>
       <c r="I14" t="n">
-        <v>74.24322250219136</v>
+        <v>74.24317125602458</v>
       </c>
       <c r="J14" t="n">
-        <v>37.018536819834</v>
+        <v>37.01850591178878</v>
       </c>
       <c r="K14" t="n">
-        <v>37.00205396051131</v>
+        <v>37.0020385419595</v>
       </c>
     </row>
     <row r="15">
@@ -3049,34 +3249,34 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>132.1828816395393</v>
+        <v>132.1828816398197</v>
       </c>
       <c r="C15" t="n">
-        <v>131.3502063637905</v>
+        <v>131.3502063638784</v>
       </c>
       <c r="D15" t="n">
-        <v>43.53028168006586</v>
+        <v>43.53028168004283</v>
       </c>
       <c r="E15" t="n">
-        <v>43.48881898317941</v>
+        <v>43.48881898316516</v>
       </c>
       <c r="F15" t="n">
-        <v>43.52390821424271</v>
+        <v>43.52390821424815</v>
       </c>
       <c r="G15" t="n">
-        <v>43.4972142852565</v>
+        <v>43.49721428525903</v>
       </c>
       <c r="H15" t="n">
-        <v>87.86489848697467</v>
+        <v>87.86489722380651</v>
       </c>
       <c r="I15" t="n">
-        <v>87.20021106539453</v>
+        <v>87.20020788599021</v>
       </c>
       <c r="J15" t="n">
-        <v>43.4728341259924</v>
+        <v>43.47283165972882</v>
       </c>
       <c r="K15" t="n">
-        <v>43.46531094277089</v>
+        <v>43.46530969252393</v>
       </c>
     </row>
     <row r="16">
@@ -3084,34 +3284,34 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>130.4072929675653</v>
+        <v>130.4072929678643</v>
       </c>
       <c r="C16" t="n">
-        <v>130.4185496918616</v>
+        <v>130.4185496920412</v>
       </c>
       <c r="D16" t="n">
-        <v>43.47493262303952</v>
+        <v>43.47493262306819</v>
       </c>
       <c r="E16" t="n">
-        <v>43.47499817395081</v>
+        <v>43.47499817396507</v>
       </c>
       <c r="F16" t="n">
-        <v>43.47466052075394</v>
+        <v>43.47466052076583</v>
       </c>
       <c r="G16" t="n">
-        <v>43.4748385935323</v>
+        <v>43.47483859353824</v>
       </c>
       <c r="H16" t="n">
-        <v>86.93815453821071</v>
+        <v>86.93815482003079</v>
       </c>
       <c r="I16" t="n">
-        <v>86.94789599024271</v>
+        <v>86.94789608253464</v>
       </c>
       <c r="J16" t="n">
-        <v>43.4739579407215</v>
+        <v>43.47395794908545</v>
       </c>
       <c r="K16" t="n">
-        <v>43.47446578139862</v>
+        <v>43.47446578377902</v>
       </c>
     </row>
     <row r="17">
@@ -3119,34 +3319,34 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>109.2321279276778</v>
+        <v>109.2321279276721</v>
       </c>
       <c r="C17" t="n">
-        <v>110.0711282018993</v>
+        <v>110.0711282018968</v>
       </c>
       <c r="D17" t="n">
-        <v>36.94467585941025</v>
+        <v>36.94467585941036</v>
       </c>
       <c r="E17" t="n">
-        <v>36.9861778124379</v>
+        <v>36.98617781243799</v>
       </c>
       <c r="F17" t="n">
-        <v>36.950898269018</v>
+        <v>36.95089826901788</v>
       </c>
       <c r="G17" t="n">
-        <v>36.97769365128826</v>
+        <v>36.97769365128821</v>
       </c>
       <c r="H17" t="n">
-        <v>73.01146081253391</v>
+        <v>73.0114608083026</v>
       </c>
       <c r="I17" t="n">
-        <v>73.68959814975123</v>
+        <v>73.68959814929649</v>
       </c>
       <c r="J17" t="n">
-        <v>36.96577180850408</v>
+        <v>36.96577180849236</v>
       </c>
       <c r="K17" t="n">
-        <v>36.99151763115115</v>
+        <v>36.99151763114872</v>
       </c>
     </row>
     <row r="18">
@@ -3154,34 +3354,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>90.10733079819629</v>
+        <v>90.10733079819603</v>
       </c>
       <c r="C18" t="n">
-        <v>90.80119241368703</v>
+        <v>90.80119241368685</v>
       </c>
       <c r="D18" t="n">
-        <v>30.47863926153416</v>
+        <v>30.47863926153414</v>
       </c>
       <c r="E18" t="n">
-        <v>30.51341088313326</v>
+        <v>30.51341088313327</v>
       </c>
       <c r="F18" t="n">
-        <v>30.48410237279766</v>
+        <v>30.48410237279764</v>
       </c>
       <c r="G18" t="n">
         <v>30.5064288943822</v>
       </c>
       <c r="H18" t="n">
-        <v>60.23445126394039</v>
+        <v>60.23445126398868</v>
       </c>
       <c r="I18" t="n">
-        <v>60.79359633917553</v>
+        <v>60.79359633920603</v>
       </c>
       <c r="J18" t="n">
-        <v>30.49809787322601</v>
+        <v>30.49809787324413</v>
       </c>
       <c r="K18" t="n">
-        <v>30.51877996587595</v>
+        <v>30.51877996588505</v>
       </c>
     </row>
     <row r="19">
@@ -3189,34 +3389,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>91.5854380539175</v>
+        <v>91.5854380827644</v>
       </c>
       <c r="C19" t="n">
-        <v>91.57882590265818</v>
+        <v>91.57882592001707</v>
       </c>
       <c r="D19" t="n">
-        <v>30.52504476292235</v>
+        <v>30.52504476573321</v>
       </c>
       <c r="E19" t="n">
-        <v>30.52500359757443</v>
+        <v>30.52500359897795</v>
       </c>
       <c r="F19" t="n">
-        <v>30.52520197859388</v>
+        <v>30.52520197973767</v>
       </c>
       <c r="G19" t="n">
-        <v>30.52509609292251</v>
+        <v>30.52509609349433</v>
       </c>
       <c r="H19" t="n">
-        <v>61.14060085310588</v>
+        <v>61.14066094016476</v>
       </c>
       <c r="I19" t="n">
-        <v>61.12547580298295</v>
+        <v>61.1255302869534</v>
       </c>
       <c r="J19" t="n">
-        <v>30.57080133944853</v>
+        <v>30.57083479766369</v>
       </c>
       <c r="K19" t="n">
-        <v>30.54787167220113</v>
+        <v>30.54788838470552</v>
       </c>
     </row>
     <row r="20">
@@ -3224,34 +3424,34 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>112.4849286131056</v>
+        <v>112.4849285836829</v>
       </c>
       <c r="C20" t="n">
-        <v>111.7800974261043</v>
+        <v>111.7800974084794</v>
       </c>
       <c r="D20" t="n">
-        <v>37.04642581302786</v>
+        <v>37.04642581021123</v>
       </c>
       <c r="E20" t="n">
-        <v>37.0115905497242</v>
+        <v>37.01159054832053</v>
       </c>
       <c r="F20" t="n">
-        <v>37.04122864459386</v>
+        <v>37.04122864343283</v>
       </c>
       <c r="G20" t="n">
-        <v>37.01872848261824</v>
+        <v>37.018728482038</v>
       </c>
       <c r="H20" t="n">
-        <v>74.81043404251204</v>
+        <v>74.81037494410079</v>
       </c>
       <c r="I20" t="n">
-        <v>74.24322264391715</v>
+        <v>74.2431712563744</v>
       </c>
       <c r="J20" t="n">
-        <v>37.01853690531226</v>
+        <v>37.01850591200297</v>
       </c>
       <c r="K20" t="n">
-        <v>37.00205400315237</v>
+        <v>37.00203854206641</v>
       </c>
     </row>
     <row r="21">
@@ -3259,34 +3459,34 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>132.1828816395418</v>
+        <v>132.18288163982</v>
       </c>
       <c r="C21" t="n">
-        <v>131.3502063637922</v>
+        <v>131.3502063638785</v>
       </c>
       <c r="D21" t="n">
-        <v>43.5302816800663</v>
+        <v>43.53028168004288</v>
       </c>
       <c r="E21" t="n">
-        <v>43.48881898317961</v>
+        <v>43.48881898316519</v>
       </c>
       <c r="F21" t="n">
-        <v>43.52390821424282</v>
+        <v>43.52390821424816</v>
       </c>
       <c r="G21" t="n">
-        <v>43.49721428525655</v>
+        <v>43.49721428525903</v>
       </c>
       <c r="H21" t="n">
-        <v>87.86489849057303</v>
+        <v>87.86489722338598</v>
       </c>
       <c r="I21" t="n">
-        <v>87.20021107428136</v>
+        <v>87.2002078856281</v>
       </c>
       <c r="J21" t="n">
-        <v>43.47283413287014</v>
+        <v>43.4728316595114</v>
       </c>
       <c r="K21" t="n">
-        <v>43.46531094625711</v>
+        <v>43.46530969241564</v>
       </c>
     </row>
     <row r="22">
@@ -3294,34 +3494,34 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>130.4072929675606</v>
+        <v>130.4072929678649</v>
       </c>
       <c r="C22" t="n">
-        <v>130.4185496918587</v>
+        <v>130.4185496920417</v>
       </c>
       <c r="D22" t="n">
-        <v>43.47493262303902</v>
+        <v>43.47493262306822</v>
       </c>
       <c r="E22" t="n">
-        <v>43.47499817395057</v>
+        <v>43.47499817396508</v>
       </c>
       <c r="F22" t="n">
-        <v>43.47466052075377</v>
+        <v>43.47466052076583</v>
       </c>
       <c r="G22" t="n">
-        <v>43.47483859353223</v>
+        <v>43.47483859353824</v>
       </c>
       <c r="H22" t="n">
-        <v>86.93815453731578</v>
+        <v>86.93815482005829</v>
       </c>
       <c r="I22" t="n">
-        <v>86.94789598988856</v>
+        <v>86.94789608254229</v>
       </c>
       <c r="J22" t="n">
-        <v>43.47395794063911</v>
+        <v>43.47395794908573</v>
       </c>
       <c r="K22" t="n">
-        <v>43.47446578136248</v>
+        <v>43.47446578377855</v>
       </c>
     </row>
     <row r="23">
@@ -3329,34 +3529,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>109.2321279276785</v>
+        <v>109.2321279276718</v>
       </c>
       <c r="C23" t="n">
-        <v>110.0711282018997</v>
+        <v>110.0711282018966</v>
       </c>
       <c r="D23" t="n">
-        <v>36.94467585941032</v>
+        <v>36.94467585941035</v>
       </c>
       <c r="E23" t="n">
-        <v>36.98617781243794</v>
+        <v>36.98617781243799</v>
       </c>
       <c r="F23" t="n">
-        <v>36.95089826901801</v>
+        <v>36.95089826901788</v>
       </c>
       <c r="G23" t="n">
-        <v>36.97769365128827</v>
+        <v>36.97769365128821</v>
       </c>
       <c r="H23" t="n">
-        <v>73.01146081255231</v>
+        <v>73.01146080828981</v>
       </c>
       <c r="I23" t="n">
-        <v>73.68959814975376</v>
+        <v>73.6895981492853</v>
       </c>
       <c r="J23" t="n">
-        <v>36.96577180850366</v>
+        <v>36.96577180848564</v>
       </c>
       <c r="K23" t="n">
-        <v>36.99151763115087</v>
+        <v>36.9915176311453</v>
       </c>
     </row>
     <row r="24">
@@ -3364,34 +3564,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>90.10733079819586</v>
+        <v>90.10733079819597</v>
       </c>
       <c r="C24" t="n">
-        <v>90.80119241368686</v>
+        <v>90.80119241368692</v>
       </c>
       <c r="D24" t="n">
-        <v>30.47863926153414</v>
+        <v>30.47863926153412</v>
       </c>
       <c r="E24" t="n">
         <v>30.51341088313325</v>
       </c>
       <c r="F24" t="n">
-        <v>30.48410237279766</v>
+        <v>30.48410237279764</v>
       </c>
       <c r="G24" t="n">
         <v>30.5064288943822</v>
       </c>
       <c r="H24" t="n">
-        <v>60.23445126394068</v>
+        <v>60.23445126399749</v>
       </c>
       <c r="I24" t="n">
-        <v>60.79359633917595</v>
+        <v>60.79359633921353</v>
       </c>
       <c r="J24" t="n">
-        <v>30.49809787322609</v>
+        <v>30.49809787324859</v>
       </c>
       <c r="K24" t="n">
-        <v>30.51877996587607</v>
+        <v>30.51877996588719</v>
       </c>
     </row>
     <row r="25">
@@ -3399,34 +3599,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>91.58543805431191</v>
+        <v>91.5854380827646</v>
       </c>
       <c r="C25" t="n">
-        <v>91.57882590289546</v>
+        <v>91.57882592001718</v>
       </c>
       <c r="D25" t="n">
-        <v>30.52504476296082</v>
+        <v>30.52504476573323</v>
       </c>
       <c r="E25" t="n">
-        <v>30.52500359759363</v>
+        <v>30.52500359897796</v>
       </c>
       <c r="F25" t="n">
-        <v>30.52520197860951</v>
+        <v>30.52520197973768</v>
       </c>
       <c r="G25" t="n">
-        <v>30.52509609293033</v>
+        <v>30.52509609349433</v>
       </c>
       <c r="H25" t="n">
-        <v>61.14060167505896</v>
+        <v>61.14066094017428</v>
       </c>
       <c r="I25" t="n">
-        <v>61.12547654828932</v>
+        <v>61.12553028696226</v>
       </c>
       <c r="J25" t="n">
-        <v>30.57080179713588</v>
+        <v>30.57083479766919</v>
       </c>
       <c r="K25" t="n">
-        <v>30.54787190081772</v>
+        <v>30.54788838470837</v>
       </c>
     </row>
     <row r="26">
@@ -3434,34 +3634,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>112.4849286127031</v>
+        <v>112.4849285836829</v>
       </c>
       <c r="C26" t="n">
-        <v>111.780097425863</v>
+        <v>111.7800974084793</v>
       </c>
       <c r="D26" t="n">
-        <v>37.04642581298933</v>
+        <v>37.04642581021124</v>
       </c>
       <c r="E26" t="n">
-        <v>37.01159054970498</v>
+        <v>37.01159054832053</v>
       </c>
       <c r="F26" t="n">
-        <v>37.04122864457799</v>
+        <v>37.04122864343284</v>
       </c>
       <c r="G26" t="n">
-        <v>37.01872848261032</v>
+        <v>37.01872848203801</v>
       </c>
       <c r="H26" t="n">
-        <v>74.81043323406807</v>
+        <v>74.81037494432928</v>
       </c>
       <c r="I26" t="n">
-        <v>74.24322194095453</v>
+        <v>74.24317125658042</v>
       </c>
       <c r="J26" t="n">
-        <v>37.01853648133473</v>
+        <v>37.01850591212927</v>
       </c>
       <c r="K26" t="n">
-        <v>37.00205379165008</v>
+        <v>37.00203854212946</v>
       </c>
     </row>
   </sheetData>
@@ -3610,49 +3810,49 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>42.02260091659777</v>
+        <v>42.02260091717802</v>
       </c>
       <c r="C3" t="n">
-        <v>42.02080732090534</v>
+        <v>42.02080732148311</v>
       </c>
       <c r="D3" t="n">
-        <v>42.01371083695089</v>
+        <v>42.01371083752576</v>
       </c>
       <c r="E3" t="n">
-        <v>41.99554578831657</v>
+        <v>41.99554578888829</v>
       </c>
       <c r="F3" t="n">
-        <v>41.96829553637234</v>
+        <v>41.96829553694039</v>
       </c>
       <c r="G3" t="n">
-        <v>41.93326599501875</v>
+        <v>41.93326599558497</v>
       </c>
       <c r="H3" t="n">
-        <v>41.99907081211217</v>
+        <v>41.99907081268591</v>
       </c>
       <c r="I3" t="n">
-        <v>41.98432761072864</v>
+        <v>41.98432761130181</v>
       </c>
       <c r="J3" t="n">
-        <v>41.96817191392476</v>
+        <v>41.96817191449776</v>
       </c>
       <c r="K3" t="n">
-        <v>42.32328486399309</v>
+        <v>42.32328486429486</v>
       </c>
       <c r="L3" t="n">
-        <v>42.3206977071931</v>
+        <v>42.3206977074821</v>
       </c>
       <c r="M3" t="n">
-        <v>42.31186756793534</v>
+        <v>42.31186756820239</v>
       </c>
       <c r="N3" t="n">
-        <v>42.30387333848677</v>
+        <v>42.30387333873909</v>
       </c>
       <c r="O3" t="n">
-        <v>42.30388442719547</v>
+        <v>42.30388442744771</v>
       </c>
       <c r="P3" t="n">
-        <v>42.30321298697667</v>
+        <v>42.30321298722858</v>
       </c>
     </row>
     <row r="4">
@@ -3660,49 +3860,49 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.1652608619613</v>
+        <v>41.16526097647309</v>
       </c>
       <c r="C4" t="n">
-        <v>41.15444888309323</v>
+        <v>41.1544489964277</v>
       </c>
       <c r="D4" t="n">
-        <v>41.1396029563505</v>
+        <v>41.13960306887309</v>
       </c>
       <c r="E4" t="n">
-        <v>41.11321526083668</v>
+        <v>41.11321537260552</v>
       </c>
       <c r="F4" t="n">
-        <v>41.0763923654446</v>
+        <v>41.07639247639154</v>
       </c>
       <c r="G4" t="n">
-        <v>41.03570515612505</v>
+        <v>41.03570526669764</v>
       </c>
       <c r="H4" t="n">
-        <v>41.12178081498743</v>
+        <v>41.12178092727272</v>
       </c>
       <c r="I4" t="n">
-        <v>41.10507351295812</v>
+        <v>41.10507362512818</v>
       </c>
       <c r="J4" t="n">
-        <v>41.08771943328798</v>
+        <v>41.0877195454234</v>
       </c>
       <c r="K4" t="n">
-        <v>41.49603270812396</v>
+        <v>41.49937891474011</v>
       </c>
       <c r="L4" t="n">
-        <v>41.47192638293463</v>
+        <v>41.47490065337267</v>
       </c>
       <c r="M4" t="n">
-        <v>41.43899667703982</v>
+        <v>41.44156986720108</v>
       </c>
       <c r="N4" t="n">
-        <v>41.41740830759928</v>
+        <v>41.41976470791139</v>
       </c>
       <c r="O4" t="n">
-        <v>41.41734639355845</v>
+        <v>41.41970097126793</v>
       </c>
       <c r="P4" t="n">
-        <v>41.41640059565378</v>
+        <v>41.41875142826649</v>
       </c>
     </row>
     <row r="5">
@@ -3710,49 +3910,49 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.15037370292936</v>
+        <v>41.15037369828381</v>
       </c>
       <c r="C5" t="n">
-        <v>41.13444389775241</v>
+        <v>41.13444389461469</v>
       </c>
       <c r="D5" t="n">
-        <v>41.11840366662875</v>
+        <v>41.11840366439692</v>
       </c>
       <c r="E5" t="n">
-        <v>41.09421390952946</v>
+        <v>41.09421390810758</v>
       </c>
       <c r="F5" t="n">
-        <v>41.06190468289285</v>
+        <v>41.06190468234119</v>
       </c>
       <c r="G5" t="n">
-        <v>41.02951316682451</v>
+        <v>41.02951316670723</v>
       </c>
       <c r="H5" t="n">
-        <v>41.10381730693035</v>
+        <v>41.1038173049612</v>
       </c>
       <c r="I5" t="n">
-        <v>41.09078847983918</v>
+        <v>41.09078847801447</v>
       </c>
       <c r="J5" t="n">
-        <v>41.07774642628928</v>
+        <v>41.07774642453654</v>
       </c>
       <c r="K5" t="n">
-        <v>41.30055630669342</v>
+        <v>41.30053453047054</v>
       </c>
       <c r="L5" t="n">
-        <v>41.1981562705874</v>
+        <v>41.19858563042261</v>
       </c>
       <c r="M5" t="n">
-        <v>41.09000400518831</v>
+        <v>41.09084710036698</v>
       </c>
       <c r="N5" t="n">
-        <v>41.03204291895418</v>
+        <v>41.03308425993443</v>
       </c>
       <c r="O5" t="n">
-        <v>41.03137256041079</v>
+        <v>41.03241747133608</v>
       </c>
       <c r="P5" t="n">
-        <v>41.03007179605583</v>
+        <v>41.03111922092781</v>
       </c>
     </row>
     <row r="6">
@@ -3760,49 +3960,49 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.10637567653424</v>
+        <v>41.10637567646409</v>
       </c>
       <c r="C6" t="n">
-        <v>41.09569833732637</v>
+        <v>41.09569833723211</v>
       </c>
       <c r="D6" t="n">
-        <v>41.08485248986547</v>
+        <v>41.08485248976</v>
       </c>
       <c r="E6" t="n">
-        <v>41.06840240603421</v>
+        <v>41.06840240592481</v>
       </c>
       <c r="F6" t="n">
-        <v>41.04640623696304</v>
+        <v>41.04640623685212</v>
       </c>
       <c r="G6" t="n">
-        <v>41.0243480761542</v>
+        <v>41.0243480760432</v>
       </c>
       <c r="H6" t="n">
-        <v>41.07493283002334</v>
+        <v>41.07493282991543</v>
       </c>
       <c r="I6" t="n">
-        <v>41.06607069121959</v>
+        <v>41.06607069110989</v>
       </c>
       <c r="J6" t="n">
-        <v>41.05719365343376</v>
+        <v>41.05719365332317</v>
       </c>
       <c r="K6" t="n">
-        <v>41.44548615215744</v>
+        <v>41.44445688003366</v>
       </c>
       <c r="L6" t="n">
-        <v>41.27366516092959</v>
+        <v>41.27306392062883</v>
       </c>
       <c r="M6" t="n">
-        <v>41.10306215523605</v>
+        <v>41.10286380503776</v>
       </c>
       <c r="N6" t="n">
-        <v>41.01688981410489</v>
+        <v>41.01688412404769</v>
       </c>
       <c r="O6" t="n">
-        <v>41.01549168354108</v>
+        <v>41.01549012608951</v>
       </c>
       <c r="P6" t="n">
-        <v>41.0140619514877</v>
+        <v>41.01406248503955</v>
       </c>
     </row>
     <row r="7">
@@ -3810,49 +4010,49 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.10709718265666</v>
+        <v>41.10709718269138</v>
       </c>
       <c r="C7" t="n">
-        <v>41.0960661337297</v>
+        <v>41.09606613376317</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08503372209596</v>
+        <v>41.08503372212858</v>
       </c>
       <c r="E7" t="n">
-        <v>41.06848769257927</v>
+        <v>41.06848769261106</v>
       </c>
       <c r="F7" t="n">
-        <v>41.04642457626411</v>
+        <v>41.04642457629501</v>
       </c>
       <c r="G7" t="n">
-        <v>41.02434967209764</v>
+        <v>41.0243496721281</v>
       </c>
       <c r="H7" t="n">
-        <v>41.07507386503337</v>
+        <v>41.07507386506571</v>
       </c>
       <c r="I7" t="n">
-        <v>41.06618784877162</v>
+        <v>41.06618784880381</v>
       </c>
       <c r="J7" t="n">
-        <v>41.05729997329064</v>
+        <v>41.05729997332278</v>
       </c>
       <c r="K7" t="n">
-        <v>41.4597187740103</v>
+        <v>41.45973557064465</v>
       </c>
       <c r="L7" t="n">
-        <v>41.28375507178774</v>
+        <v>41.28375268836124</v>
       </c>
       <c r="M7" t="n">
-        <v>41.10730357649875</v>
+        <v>41.10729741030674</v>
       </c>
       <c r="N7" t="n">
-        <v>41.01802034719609</v>
+        <v>41.01801478827524</v>
       </c>
       <c r="O7" t="n">
-        <v>41.01655430556735</v>
+        <v>41.0165487667709</v>
       </c>
       <c r="P7" t="n">
-        <v>41.01509036184704</v>
+        <v>41.01508483511049</v>
       </c>
     </row>
     <row r="8">
@@ -3860,49 +4060,49 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41.15185920707731</v>
+        <v>41.15185920699719</v>
       </c>
       <c r="C8" t="n">
-        <v>41.13524233969455</v>
+        <v>41.13524233961589</v>
       </c>
       <c r="D8" t="n">
-        <v>41.11882631818642</v>
+        <v>41.1188263181086</v>
       </c>
       <c r="E8" t="n">
-        <v>41.09442372465705</v>
+        <v>41.09442372457995</v>
       </c>
       <c r="F8" t="n">
-        <v>41.06195220847156</v>
+        <v>41.06195220839525</v>
       </c>
       <c r="G8" t="n">
-        <v>41.0295160970672</v>
+        <v>41.02951609699125</v>
       </c>
       <c r="H8" t="n">
-        <v>41.10415920409493</v>
+        <v>41.10415920401734</v>
       </c>
       <c r="I8" t="n">
-        <v>41.09108596229244</v>
+        <v>41.09108596221496</v>
       </c>
       <c r="J8" t="n">
-        <v>41.07802444114002</v>
+        <v>41.07802444106258</v>
       </c>
       <c r="K8" t="n">
-        <v>41.67163509308721</v>
+        <v>41.67164096412463</v>
       </c>
       <c r="L8" t="n">
-        <v>41.40987985667893</v>
+        <v>41.40988308744262</v>
       </c>
       <c r="M8" t="n">
-        <v>41.15044952327887</v>
+        <v>41.15045027709211</v>
       </c>
       <c r="N8" t="n">
-        <v>41.01952400936734</v>
+        <v>41.01952360270126</v>
       </c>
       <c r="O8" t="n">
-        <v>41.01737939919563</v>
+        <v>41.01737896753971</v>
       </c>
       <c r="P8" t="n">
-        <v>41.01523669952354</v>
+        <v>41.01523625539623</v>
       </c>
     </row>
     <row r="9">
@@ -3910,49 +4110,49 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41.20443761021141</v>
+        <v>41.20443761021514</v>
       </c>
       <c r="C9" t="n">
-        <v>41.18152442725491</v>
+        <v>41.18152442725738</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15888631219113</v>
+        <v>41.15888631219285</v>
       </c>
       <c r="E9" t="n">
-        <v>41.12522867889107</v>
+        <v>41.12522867889214</v>
       </c>
       <c r="F9" t="n">
-        <v>41.0804339846616</v>
+        <v>41.08043398466196</v>
       </c>
       <c r="G9" t="n">
         <v>41.03567583517204</v>
       </c>
       <c r="H9" t="n">
-        <v>41.13865758916669</v>
+        <v>41.1386575891682</v>
       </c>
       <c r="I9" t="n">
-        <v>41.12062479378486</v>
+        <v>41.12062479378625</v>
       </c>
       <c r="J9" t="n">
-        <v>41.10260621137127</v>
+        <v>41.10260621137259</v>
       </c>
       <c r="K9" t="n">
-        <v>41.91655508959566</v>
+        <v>41.91655549481484</v>
       </c>
       <c r="L9" t="n">
-        <v>41.55762852840736</v>
+        <v>41.5576288439289</v>
       </c>
       <c r="M9" t="n">
-        <v>41.20105753823199</v>
+        <v>41.20105765597157</v>
       </c>
       <c r="N9" t="n">
-        <v>41.02068879836246</v>
+        <v>41.02068880214372</v>
       </c>
       <c r="O9" t="n">
-        <v>41.01773596608043</v>
+        <v>41.01773596733844</v>
       </c>
       <c r="P9" t="n">
-        <v>41.01478394885284</v>
+        <v>41.01478394883323</v>
       </c>
     </row>
     <row r="10">
@@ -3960,49 +4160,49 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41.20320142952155</v>
+        <v>41.20320142499043</v>
       </c>
       <c r="C10" t="n">
-        <v>41.18089875601027</v>
+        <v>41.18089875154555</v>
       </c>
       <c r="D10" t="n">
-        <v>41.15858016376909</v>
+        <v>41.15858015934335</v>
       </c>
       <c r="E10" t="n">
-        <v>41.12508580667178</v>
+        <v>41.12508580227966</v>
       </c>
       <c r="F10" t="n">
-        <v>41.08040477005541</v>
+        <v>41.08040476569862</v>
       </c>
       <c r="G10" t="n">
-        <v>41.03567502556819</v>
+        <v>41.03567502122669</v>
       </c>
       <c r="H10" t="n">
-        <v>41.13841987134081</v>
+        <v>41.13841986692493</v>
       </c>
       <c r="I10" t="n">
-        <v>41.12042774733789</v>
+        <v>41.12042774292667</v>
       </c>
       <c r="J10" t="n">
-        <v>41.10242760744379</v>
+        <v>41.10242760303393</v>
       </c>
       <c r="K10" t="n">
-        <v>41.90693692842827</v>
+        <v>41.90693683493755</v>
       </c>
       <c r="L10" t="n">
-        <v>41.55546086361056</v>
+        <v>41.55546080462258</v>
       </c>
       <c r="M10" t="n">
-        <v>41.20093289815916</v>
+        <v>41.20093286052121</v>
       </c>
       <c r="N10" t="n">
-        <v>41.02066507480377</v>
+        <v>41.02066504528221</v>
       </c>
       <c r="O10" t="n">
-        <v>41.01771210494259</v>
+        <v>41.01771207559118</v>
       </c>
       <c r="P10" t="n">
-        <v>41.01475885549117</v>
+        <v>41.01475882622184</v>
       </c>
     </row>
     <row r="11">
@@ -4010,49 +4210,49 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41.14993612252368</v>
+        <v>41.14993612270071</v>
       </c>
       <c r="C11" t="n">
-        <v>41.13426510530141</v>
+        <v>41.13426510541967</v>
       </c>
       <c r="D11" t="n">
-        <v>41.11834652680496</v>
+        <v>41.11834652688777</v>
       </c>
       <c r="E11" t="n">
-        <v>41.09419912036532</v>
+        <v>41.09419912041638</v>
       </c>
       <c r="F11" t="n">
-        <v>41.06190549126779</v>
+        <v>41.06190549128472</v>
       </c>
       <c r="G11" t="n">
-        <v>41.02951385477427</v>
+        <v>41.02951385477415</v>
       </c>
       <c r="H11" t="n">
-        <v>41.10378634306361</v>
+        <v>41.1037863431361</v>
       </c>
       <c r="I11" t="n">
-        <v>41.09077664571185</v>
+        <v>41.09077664577867</v>
       </c>
       <c r="J11" t="n">
-        <v>41.07774395763143</v>
+        <v>41.07774395769543</v>
       </c>
       <c r="K11" t="n">
-        <v>41.65409092169462</v>
+        <v>41.65409095931995</v>
       </c>
       <c r="L11" t="n">
-        <v>41.40469083129049</v>
+        <v>41.40469085246701</v>
       </c>
       <c r="M11" t="n">
-        <v>41.14910672668475</v>
+        <v>41.14910673356265</v>
       </c>
       <c r="N11" t="n">
-        <v>41.0186396756064</v>
+        <v>41.0186396758164</v>
       </c>
       <c r="O11" t="n">
-        <v>41.01650133986951</v>
+        <v>41.01650133993594</v>
       </c>
       <c r="P11" t="n">
-        <v>41.01435993018107</v>
+        <v>41.01435993017582</v>
       </c>
     </row>
     <row r="12">
@@ -4060,49 +4260,49 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>41.10637697574715</v>
+        <v>41.1063769757456</v>
       </c>
       <c r="C12" t="n">
-        <v>41.09569861380968</v>
+        <v>41.09569861380906</v>
       </c>
       <c r="D12" t="n">
-        <v>41.08485250413839</v>
+        <v>41.08485250413821</v>
       </c>
       <c r="E12" t="n">
-        <v>41.06840239041627</v>
+        <v>41.06840239041623</v>
       </c>
       <c r="F12" t="n">
-        <v>41.04640622624164</v>
+        <v>41.04640622624165</v>
       </c>
       <c r="G12" t="n">
-        <v>41.02434806768478</v>
+        <v>41.0243480676848</v>
       </c>
       <c r="H12" t="n">
-        <v>41.07493282394719</v>
+        <v>41.07493282394712</v>
       </c>
       <c r="I12" t="n">
-        <v>41.06607067764575</v>
+        <v>41.06607067764573</v>
       </c>
       <c r="J12" t="n">
-        <v>41.05719363856712</v>
+        <v>41.05719363856714</v>
       </c>
       <c r="K12" t="n">
-        <v>41.45096316326097</v>
+        <v>41.4509631622871</v>
       </c>
       <c r="L12" t="n">
-        <v>41.28037635899962</v>
+        <v>41.28037635877465</v>
       </c>
       <c r="M12" t="n">
-        <v>41.10589033242723</v>
+        <v>41.10589033241186</v>
       </c>
       <c r="N12" t="n">
-        <v>41.01698802833783</v>
+        <v>41.01698802833911</v>
       </c>
       <c r="O12" t="n">
-        <v>41.01552873374584</v>
+        <v>41.01552873374725</v>
       </c>
       <c r="P12" t="n">
-        <v>41.01406742381314</v>
+        <v>41.01406742381453</v>
       </c>
     </row>
     <row r="13">
@@ -4110,49 +4310,49 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41.10709718071141</v>
+        <v>41.10709718135497</v>
       </c>
       <c r="C13" t="n">
-        <v>41.09606613302555</v>
+        <v>41.09606613366236</v>
       </c>
       <c r="D13" t="n">
-        <v>41.0850337214321</v>
+        <v>41.08503372206491</v>
       </c>
       <c r="E13" t="n">
-        <v>41.06848769185035</v>
+        <v>41.06848769247966</v>
       </c>
       <c r="F13" t="n">
-        <v>41.04642457547785</v>
+        <v>41.04642457610344</v>
       </c>
       <c r="G13" t="n">
-        <v>41.02434967128613</v>
+        <v>41.02434967191004</v>
       </c>
       <c r="H13" t="n">
-        <v>41.07507386434855</v>
+        <v>41.0750738649803</v>
       </c>
       <c r="I13" t="n">
-        <v>41.06618784807244</v>
+        <v>41.06618784870365</v>
       </c>
       <c r="J13" t="n">
-        <v>41.05729997258387</v>
+        <v>41.0572999732149</v>
       </c>
       <c r="K13" t="n">
-        <v>41.45946033960605</v>
+        <v>41.45946191960276</v>
       </c>
       <c r="L13" t="n">
-        <v>41.28373910835563</v>
+        <v>41.2837403506519</v>
       </c>
       <c r="M13" t="n">
-        <v>41.10735741207048</v>
+        <v>41.107358346146</v>
       </c>
       <c r="N13" t="n">
-        <v>41.01807320458536</v>
+        <v>41.01807399305268</v>
       </c>
       <c r="O13" t="n">
-        <v>41.01660703764986</v>
+        <v>41.01660782296977</v>
       </c>
       <c r="P13" t="n">
-        <v>41.01514300040947</v>
+        <v>41.01514378417211</v>
       </c>
     </row>
     <row r="14">
@@ -4160,49 +4360,49 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>41.15185920710262</v>
+        <v>41.15185920707681</v>
       </c>
       <c r="C14" t="n">
-        <v>41.13524233971037</v>
+        <v>41.13524233969321</v>
       </c>
       <c r="D14" t="n">
-        <v>41.1188263181966</v>
+        <v>41.11882631818459</v>
       </c>
       <c r="E14" t="n">
-        <v>41.0944237246616</v>
+        <v>41.09442372465419</v>
       </c>
       <c r="F14" t="n">
-        <v>41.06195220846987</v>
+        <v>41.06195220846736</v>
       </c>
       <c r="G14" t="n">
-        <v>41.02951609706234</v>
+        <v>41.0295160970623</v>
       </c>
       <c r="H14" t="n">
-        <v>41.10415920410338</v>
+        <v>41.10415920409287</v>
       </c>
       <c r="I14" t="n">
-        <v>41.0910859623</v>
+        <v>41.09108596229031</v>
       </c>
       <c r="J14" t="n">
-        <v>41.07802444114711</v>
+        <v>41.07802444113783</v>
       </c>
       <c r="K14" t="n">
-        <v>41.67157774838643</v>
+        <v>41.67157687418999</v>
       </c>
       <c r="L14" t="n">
-        <v>41.40984697956689</v>
+        <v>41.40984651222894</v>
       </c>
       <c r="M14" t="n">
-        <v>41.15044070386382</v>
+        <v>41.15044059167649</v>
       </c>
       <c r="N14" t="n">
-        <v>41.0195265343641</v>
+        <v>41.01952658770337</v>
       </c>
       <c r="O14" t="n">
-        <v>41.01738216864253</v>
+        <v>41.01738222554596</v>
       </c>
       <c r="P14" t="n">
-        <v>41.01523959095962</v>
+        <v>41.01523964964191</v>
       </c>
     </row>
     <row r="15">
@@ -4210,49 +4410,49 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41.20443761021794</v>
+        <v>41.20443761021159</v>
       </c>
       <c r="C15" t="n">
-        <v>41.18152442726149</v>
+        <v>41.18152442725505</v>
       </c>
       <c r="D15" t="n">
-        <v>41.15888631219772</v>
+        <v>41.15888631219126</v>
       </c>
       <c r="E15" t="n">
-        <v>41.12522867889762</v>
+        <v>41.12522867889115</v>
       </c>
       <c r="F15" t="n">
-        <v>41.08043398466805</v>
+        <v>41.08043398466164</v>
       </c>
       <c r="G15" t="n">
-        <v>41.03567583517845</v>
+        <v>41.03567583517206</v>
       </c>
       <c r="H15" t="n">
-        <v>41.13865758917328</v>
+        <v>41.1386575891668</v>
       </c>
       <c r="I15" t="n">
-        <v>41.12062479379146</v>
+        <v>41.12062479378498</v>
       </c>
       <c r="J15" t="n">
-        <v>41.10260621137786</v>
+        <v>41.10260621137138</v>
       </c>
       <c r="K15" t="n">
-        <v>41.91655324432844</v>
+        <v>41.91655319314531</v>
       </c>
       <c r="L15" t="n">
-        <v>41.55762665943048</v>
+        <v>41.55762661812852</v>
       </c>
       <c r="M15" t="n">
-        <v>41.20105678583646</v>
+        <v>41.20105677018029</v>
       </c>
       <c r="N15" t="n">
-        <v>41.02068877350123</v>
+        <v>41.020688772886</v>
       </c>
       <c r="O15" t="n">
-        <v>41.01773595753099</v>
+        <v>41.01773595724944</v>
       </c>
       <c r="P15" t="n">
-        <v>41.01478394862227</v>
+        <v>41.01478394850984</v>
       </c>
     </row>
     <row r="16">
@@ -4260,49 +4460,49 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41.2032014249902</v>
+        <v>41.2032014249905</v>
       </c>
       <c r="C16" t="n">
-        <v>41.18089875154541</v>
+        <v>41.1808987515456</v>
       </c>
       <c r="D16" t="n">
-        <v>41.15858015934324</v>
+        <v>41.15858015934338</v>
       </c>
       <c r="E16" t="n">
-        <v>41.12508580227962</v>
+        <v>41.12508580227969</v>
       </c>
       <c r="F16" t="n">
         <v>41.08040476569865</v>
       </c>
       <c r="G16" t="n">
-        <v>41.03567502122675</v>
+        <v>41.03567502122672</v>
       </c>
       <c r="H16" t="n">
-        <v>41.13841986692485</v>
+        <v>41.13841986692496</v>
       </c>
       <c r="I16" t="n">
-        <v>41.12042774292661</v>
+        <v>41.12042774292671</v>
       </c>
       <c r="J16" t="n">
-        <v>41.10242760303387</v>
+        <v>41.10242760303396</v>
       </c>
       <c r="K16" t="n">
-        <v>41.90693699476626</v>
+        <v>41.90693699785469</v>
       </c>
       <c r="L16" t="n">
-        <v>41.55546084642431</v>
+        <v>41.55546084726008</v>
       </c>
       <c r="M16" t="n">
-        <v>41.20093286394363</v>
+        <v>41.20093286403394</v>
       </c>
       <c r="N16" t="n">
-        <v>41.02066504528702</v>
+        <v>41.02066504528798</v>
       </c>
       <c r="O16" t="n">
-        <v>41.01771207556729</v>
+        <v>41.01771207556712</v>
       </c>
       <c r="P16" t="n">
-        <v>41.01475882619741</v>
+        <v>41.01475882619692</v>
       </c>
     </row>
     <row r="17">
@@ -4310,49 +4510,49 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>41.14993612270069</v>
+        <v>41.14993612270071</v>
       </c>
       <c r="C17" t="n">
-        <v>41.13426510541964</v>
+        <v>41.13426510541966</v>
       </c>
       <c r="D17" t="n">
-        <v>41.11834652688775</v>
+        <v>41.11834652688776</v>
       </c>
       <c r="E17" t="n">
-        <v>41.09419912041636</v>
+        <v>41.09419912041638</v>
       </c>
       <c r="F17" t="n">
-        <v>41.0619054912847</v>
+        <v>41.06190549128471</v>
       </c>
       <c r="G17" t="n">
-        <v>41.02951385477413</v>
+        <v>41.02951385477414</v>
       </c>
       <c r="H17" t="n">
-        <v>41.10378634313609</v>
+        <v>41.1037863431361</v>
       </c>
       <c r="I17" t="n">
-        <v>41.09077664577866</v>
+        <v>41.09077664577869</v>
       </c>
       <c r="J17" t="n">
-        <v>41.0777439576954</v>
+        <v>41.07774395769543</v>
       </c>
       <c r="K17" t="n">
-        <v>41.65409095784958</v>
+        <v>41.65409095781698</v>
       </c>
       <c r="L17" t="n">
-        <v>41.40469085237315</v>
+        <v>41.40469085236927</v>
       </c>
       <c r="M17" t="n">
-        <v>41.14910673356778</v>
+        <v>41.14910673356702</v>
       </c>
       <c r="N17" t="n">
-        <v>41.01863967581792</v>
+        <v>41.01863967581731</v>
       </c>
       <c r="O17" t="n">
-        <v>41.01650133993733</v>
+        <v>41.01650133993673</v>
       </c>
       <c r="P17" t="n">
-        <v>41.01435993017717</v>
+        <v>41.01435993017657</v>
       </c>
     </row>
     <row r="18">
@@ -4360,49 +4560,49 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41.10637697574559</v>
+        <v>41.1063769757456</v>
       </c>
       <c r="C18" t="n">
         <v>41.09569861380906</v>
       </c>
       <c r="D18" t="n">
-        <v>41.0848525041382</v>
+        <v>41.08485250413821</v>
       </c>
       <c r="E18" t="n">
-        <v>41.06840239041621</v>
+        <v>41.06840239041622</v>
       </c>
       <c r="F18" t="n">
-        <v>41.04640622624164</v>
+        <v>41.04640622624165</v>
       </c>
       <c r="G18" t="n">
-        <v>41.02434806768478</v>
+        <v>41.02434806768479</v>
       </c>
       <c r="H18" t="n">
-        <v>41.07493282394709</v>
+        <v>41.0749328239471</v>
       </c>
       <c r="I18" t="n">
-        <v>41.06607067764572</v>
+        <v>41.06607067764573</v>
       </c>
       <c r="J18" t="n">
         <v>41.05719363856713</v>
       </c>
       <c r="K18" t="n">
-        <v>41.45096316228805</v>
+        <v>41.4509631622884</v>
       </c>
       <c r="L18" t="n">
-        <v>41.28037635877386</v>
+        <v>41.28037635877394</v>
       </c>
       <c r="M18" t="n">
-        <v>41.10589033241169</v>
+        <v>41.10589033241159</v>
       </c>
       <c r="N18" t="n">
-        <v>41.01698802833919</v>
+        <v>41.01698802833902</v>
       </c>
       <c r="O18" t="n">
-        <v>41.01552873374732</v>
+        <v>41.01552873374715</v>
       </c>
       <c r="P18" t="n">
-        <v>41.01406742381462</v>
+        <v>41.01406742381443</v>
       </c>
     </row>
     <row r="19">
@@ -4410,49 +4610,49 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41.10709718070964</v>
+        <v>41.10709718135496</v>
       </c>
       <c r="C19" t="n">
-        <v>41.0960661330238</v>
+        <v>41.09606613366235</v>
       </c>
       <c r="D19" t="n">
-        <v>41.08503372143036</v>
+        <v>41.08503372206491</v>
       </c>
       <c r="E19" t="n">
-        <v>41.06848769184862</v>
+        <v>41.06848769247966</v>
       </c>
       <c r="F19" t="n">
-        <v>41.04642457547613</v>
+        <v>41.04642457610344</v>
       </c>
       <c r="G19" t="n">
-        <v>41.0243496712844</v>
+        <v>41.02434967191003</v>
       </c>
       <c r="H19" t="n">
-        <v>41.07507386434681</v>
+        <v>41.0750738649803</v>
       </c>
       <c r="I19" t="n">
-        <v>41.0661878480707</v>
+        <v>41.06618784870365</v>
       </c>
       <c r="J19" t="n">
-        <v>41.05729997258214</v>
+        <v>41.0572999732149</v>
       </c>
       <c r="K19" t="n">
-        <v>41.45946033524186</v>
+        <v>41.45946191960304</v>
       </c>
       <c r="L19" t="n">
-        <v>41.28373910491966</v>
+        <v>41.28374035065208</v>
       </c>
       <c r="M19" t="n">
-        <v>41.10735740948703</v>
+        <v>41.10735834614611</v>
       </c>
       <c r="N19" t="n">
-        <v>41.01807320240484</v>
+        <v>41.01807399305275</v>
       </c>
       <c r="O19" t="n">
-        <v>41.01660703547805</v>
+        <v>41.01660782296985</v>
       </c>
       <c r="P19" t="n">
-        <v>41.01514299824197</v>
+        <v>41.01514378417219</v>
       </c>
     </row>
     <row r="20">
@@ -4460,49 +4660,49 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>41.1518592071027</v>
+        <v>41.1518592070768</v>
       </c>
       <c r="C20" t="n">
-        <v>41.13524233971042</v>
+        <v>41.13524233969321</v>
       </c>
       <c r="D20" t="n">
-        <v>41.11882631819663</v>
+        <v>41.11882631818459</v>
       </c>
       <c r="E20" t="n">
-        <v>41.09442372466162</v>
+        <v>41.09442372465418</v>
       </c>
       <c r="F20" t="n">
-        <v>41.06195220846987</v>
+        <v>41.06195220846736</v>
       </c>
       <c r="G20" t="n">
-        <v>41.02951609706234</v>
+        <v>41.02951609706228</v>
       </c>
       <c r="H20" t="n">
-        <v>41.10415920410342</v>
+        <v>41.10415920409287</v>
       </c>
       <c r="I20" t="n">
-        <v>41.09108596230003</v>
+        <v>41.09108596229029</v>
       </c>
       <c r="J20" t="n">
-        <v>41.07802444114714</v>
+        <v>41.07802444113782</v>
       </c>
       <c r="K20" t="n">
-        <v>41.67157775080415</v>
+        <v>41.67157687420129</v>
       </c>
       <c r="L20" t="n">
-        <v>41.4098469808594</v>
+        <v>41.40984651223761</v>
       </c>
       <c r="M20" t="n">
-        <v>41.15044070417413</v>
+        <v>41.15044059168276</v>
       </c>
       <c r="N20" t="n">
-        <v>41.01952653421664</v>
+        <v>41.01952658770852</v>
       </c>
       <c r="O20" t="n">
-        <v>41.01738216848521</v>
+        <v>41.01738222555107</v>
       </c>
       <c r="P20" t="n">
-        <v>41.01523959079738</v>
+        <v>41.01523964964702</v>
       </c>
     </row>
     <row r="21">
@@ -4510,49 +4710,49 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>41.20443761021803</v>
+        <v>41.20443761021159</v>
       </c>
       <c r="C21" t="n">
-        <v>41.18152442726158</v>
+        <v>41.18152442725505</v>
       </c>
       <c r="D21" t="n">
-        <v>41.15888631219782</v>
+        <v>41.15888631219125</v>
       </c>
       <c r="E21" t="n">
-        <v>41.12522867889771</v>
+        <v>41.12522867889115</v>
       </c>
       <c r="F21" t="n">
-        <v>41.08043398466816</v>
+        <v>41.08043398466164</v>
       </c>
       <c r="G21" t="n">
-        <v>41.03567583517854</v>
+        <v>41.03567583517206</v>
       </c>
       <c r="H21" t="n">
-        <v>41.13865758917337</v>
+        <v>41.1386575891668</v>
       </c>
       <c r="I21" t="n">
-        <v>41.12062479379156</v>
+        <v>41.12062479378498</v>
       </c>
       <c r="J21" t="n">
-        <v>41.10260621137795</v>
+        <v>41.10260621137138</v>
       </c>
       <c r="K21" t="n">
-        <v>41.91655324447332</v>
+        <v>41.91655319313763</v>
       </c>
       <c r="L21" t="n">
-        <v>41.55762665954721</v>
+        <v>41.5576266181242</v>
       </c>
       <c r="M21" t="n">
-        <v>41.20105678588152</v>
+        <v>41.2010567701789</v>
       </c>
       <c r="N21" t="n">
-        <v>41.02068877350434</v>
+        <v>41.02068877288596</v>
       </c>
       <c r="O21" t="n">
-        <v>41.01773595753317</v>
+        <v>41.01773595724941</v>
       </c>
       <c r="P21" t="n">
-        <v>41.01478394862397</v>
+        <v>41.01478394850985</v>
       </c>
     </row>
     <row r="22">
@@ -4560,49 +4760,49 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>41.2032014249902</v>
+        <v>41.20320142499051</v>
       </c>
       <c r="C22" t="n">
-        <v>41.1808987515454</v>
+        <v>41.18089875154561</v>
       </c>
       <c r="D22" t="n">
-        <v>41.15858015934324</v>
+        <v>41.15858015934339</v>
       </c>
       <c r="E22" t="n">
-        <v>41.12508580227961</v>
+        <v>41.12508580227969</v>
       </c>
       <c r="F22" t="n">
-        <v>41.08040476569863</v>
+        <v>41.08040476569866</v>
       </c>
       <c r="G22" t="n">
-        <v>41.03567502122674</v>
+        <v>41.03567502122673</v>
       </c>
       <c r="H22" t="n">
-        <v>41.13841986692485</v>
+        <v>41.13841986692496</v>
       </c>
       <c r="I22" t="n">
-        <v>41.12042774292661</v>
+        <v>41.12042774292671</v>
       </c>
       <c r="J22" t="n">
-        <v>41.10242760303387</v>
+        <v>41.10242760303396</v>
       </c>
       <c r="K22" t="n">
-        <v>41.90693699475562</v>
+        <v>41.90693699785498</v>
       </c>
       <c r="L22" t="n">
-        <v>41.55546084642081</v>
+        <v>41.55546084726016</v>
       </c>
       <c r="M22" t="n">
-        <v>41.20093286394301</v>
+        <v>41.20093286403396</v>
       </c>
       <c r="N22" t="n">
-        <v>41.020665045287</v>
+        <v>41.02066504528798</v>
       </c>
       <c r="O22" t="n">
-        <v>41.01771207556728</v>
+        <v>41.01771207556712</v>
       </c>
       <c r="P22" t="n">
-        <v>41.01475882619741</v>
+        <v>41.01475882619692</v>
       </c>
     </row>
     <row r="23">
@@ -4619,10 +4819,10 @@
         <v>41.11834652688776</v>
       </c>
       <c r="E23" t="n">
-        <v>41.09419912041637</v>
+        <v>41.09419912041638</v>
       </c>
       <c r="F23" t="n">
-        <v>41.0619054912847</v>
+        <v>41.06190549128471</v>
       </c>
       <c r="G23" t="n">
         <v>41.02951385477414</v>
@@ -4631,28 +4831,28 @@
         <v>41.1037863431361</v>
       </c>
       <c r="I23" t="n">
-        <v>41.09077664577867</v>
+        <v>41.09077664577869</v>
       </c>
       <c r="J23" t="n">
-        <v>41.07774395769541</v>
+        <v>41.07774395769543</v>
       </c>
       <c r="K23" t="n">
-        <v>41.65409095784971</v>
+        <v>41.65409095781661</v>
       </c>
       <c r="L23" t="n">
-        <v>41.40469085237318</v>
+        <v>41.40469085236899</v>
       </c>
       <c r="M23" t="n">
-        <v>41.14910673356778</v>
+        <v>41.14910673356682</v>
       </c>
       <c r="N23" t="n">
-        <v>41.01863967581792</v>
+        <v>41.01863967581715</v>
       </c>
       <c r="O23" t="n">
-        <v>41.01650133993733</v>
+        <v>41.01650133993657</v>
       </c>
       <c r="P23" t="n">
-        <v>41.01435993017716</v>
+        <v>41.01435993017641</v>
       </c>
     </row>
     <row r="24">
@@ -4660,7 +4860,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>41.10637697574559</v>
+        <v>41.1063769757456</v>
       </c>
       <c r="C24" t="n">
         <v>41.09569861380906</v>
@@ -4678,7 +4878,7 @@
         <v>41.02434806768479</v>
       </c>
       <c r="H24" t="n">
-        <v>41.07493282394709</v>
+        <v>41.07493282394711</v>
       </c>
       <c r="I24" t="n">
         <v>41.06607067764573</v>
@@ -4687,22 +4887,22 @@
         <v>41.05719363856713</v>
       </c>
       <c r="K24" t="n">
-        <v>41.45096316228805</v>
+        <v>41.45096316228846</v>
       </c>
       <c r="L24" t="n">
-        <v>41.28037635877386</v>
+        <v>41.28037635877394</v>
       </c>
       <c r="M24" t="n">
-        <v>41.1058903324117</v>
+        <v>41.10589033241156</v>
       </c>
       <c r="N24" t="n">
-        <v>41.0169880283392</v>
+        <v>41.01698802833896</v>
       </c>
       <c r="O24" t="n">
-        <v>41.01552873374732</v>
+        <v>41.0155287337471</v>
       </c>
       <c r="P24" t="n">
-        <v>41.01406742381462</v>
+        <v>41.01406742381437</v>
       </c>
     </row>
     <row r="25">
@@ -4710,49 +4910,49 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>41.10709718071848</v>
+        <v>41.10709718135497</v>
       </c>
       <c r="C25" t="n">
-        <v>41.09606613303254</v>
+        <v>41.09606613366235</v>
       </c>
       <c r="D25" t="n">
-        <v>41.08503372143905</v>
+        <v>41.08503372206491</v>
       </c>
       <c r="E25" t="n">
-        <v>41.06848769185726</v>
+        <v>41.06848769247966</v>
       </c>
       <c r="F25" t="n">
-        <v>41.04642457548471</v>
+        <v>41.04642457610345</v>
       </c>
       <c r="G25" t="n">
-        <v>41.02434967129298</v>
+        <v>41.02434967191004</v>
       </c>
       <c r="H25" t="n">
-        <v>41.07507386435549</v>
+        <v>41.0750738649803</v>
       </c>
       <c r="I25" t="n">
-        <v>41.06618784807936</v>
+        <v>41.06618784870365</v>
       </c>
       <c r="J25" t="n">
-        <v>41.05729997259079</v>
+        <v>41.0572999732149</v>
       </c>
       <c r="K25" t="n">
-        <v>41.4594603569149</v>
+        <v>41.45946191960325</v>
       </c>
       <c r="L25" t="n">
-        <v>41.28373912196049</v>
+        <v>41.28374035065223</v>
       </c>
       <c r="M25" t="n">
-        <v>41.10735742229993</v>
+        <v>41.10735834614622</v>
       </c>
       <c r="N25" t="n">
-        <v>41.01807321322041</v>
+        <v>41.01807399305283</v>
       </c>
       <c r="O25" t="n">
-        <v>41.01660704625045</v>
+        <v>41.01660782296992</v>
       </c>
       <c r="P25" t="n">
-        <v>41.01514300899301</v>
+        <v>41.01514378417227</v>
       </c>
     </row>
     <row r="26">
@@ -4760,49 +4960,49 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>41.15185920710234</v>
+        <v>41.15185920707682</v>
       </c>
       <c r="C26" t="n">
-        <v>41.13524233971018</v>
+        <v>41.13524233969321</v>
       </c>
       <c r="D26" t="n">
-        <v>41.11882631819646</v>
+        <v>41.11882631818459</v>
       </c>
       <c r="E26" t="n">
-        <v>41.09442372466153</v>
+        <v>41.09442372465418</v>
       </c>
       <c r="F26" t="n">
-        <v>41.06195220846984</v>
+        <v>41.06195220846737</v>
       </c>
       <c r="G26" t="n">
-        <v>41.02951609706234</v>
+        <v>41.02951609706229</v>
       </c>
       <c r="H26" t="n">
-        <v>41.10415920410328</v>
+        <v>41.10415920409287</v>
       </c>
       <c r="I26" t="n">
-        <v>41.0910859622999</v>
+        <v>41.09108596229029</v>
       </c>
       <c r="J26" t="n">
-        <v>41.07802444114702</v>
+        <v>41.07802444113783</v>
       </c>
       <c r="K26" t="n">
-        <v>41.67157773881233</v>
+        <v>41.67157687420799</v>
       </c>
       <c r="L26" t="n">
-        <v>41.40984697444861</v>
+        <v>41.40984651224276</v>
       </c>
       <c r="M26" t="n">
-        <v>41.15044070263509</v>
+        <v>41.1504405916865</v>
       </c>
       <c r="N26" t="n">
-        <v>41.01952653494818</v>
+        <v>41.01952658771159</v>
       </c>
       <c r="O26" t="n">
-        <v>41.01738216926564</v>
+        <v>41.01738222555412</v>
       </c>
       <c r="P26" t="n">
-        <v>41.01523959160221</v>
+        <v>41.01523964965006</v>
       </c>
     </row>
   </sheetData>
@@ -4839,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02698517072451379</v>
+        <v>0.02698522722773939</v>
       </c>
     </row>
     <row r="4">
@@ -4847,7 +5047,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>94.23561057963762</v>
+        <v>94.42578653320632</v>
       </c>
     </row>
     <row r="5">
@@ -4855,7 +5055,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>155.5660059129541</v>
+        <v>155.4480914685664</v>
       </c>
     </row>
     <row r="6">
@@ -4863,7 +5063,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>150.4112880870227</v>
+        <v>150.3306578382298</v>
       </c>
     </row>
     <row r="7">
@@ -4871,7 +5071,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152.845405104983</v>
+        <v>152.8534573713015</v>
       </c>
     </row>
     <row r="8">
@@ -4879,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>189.0574012105276</v>
+        <v>189.0577346803977</v>
       </c>
     </row>
     <row r="9">
@@ -4887,7 +5087,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>222.0953411371081</v>
+        <v>222.0953279622579</v>
       </c>
     </row>
     <row r="10">
@@ -4895,7 +5095,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>217.2799359766736</v>
+        <v>217.2799290862193</v>
       </c>
     </row>
     <row r="11">
@@ -4903,7 +5103,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>180.1480161972702</v>
+        <v>180.1480195178157</v>
       </c>
     </row>
     <row r="12">
@@ -4911,7 +5111,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>148.6444626891095</v>
+        <v>148.6444623753718</v>
       </c>
     </row>
     <row r="13">
@@ -4919,7 +5119,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>152.7772153293579</v>
+        <v>152.7772824029994</v>
       </c>
     </row>
     <row r="14">
@@ -4927,7 +5127,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>189.0547572706716</v>
+        <v>189.0546872549448</v>
       </c>
     </row>
     <row r="15">
@@ -4935,7 +5135,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>222.0955917317932</v>
+        <v>222.0955941710272</v>
       </c>
     </row>
     <row r="16">
@@ -4943,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>217.2799546909314</v>
+        <v>217.2799552172739</v>
       </c>
     </row>
     <row r="17">
@@ -4951,7 +5151,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>180.1480185895347</v>
+        <v>180.1480185712546</v>
       </c>
     </row>
     <row r="18">
@@ -4959,7 +5159,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>148.6444623822989</v>
+        <v>148.644462382495</v>
       </c>
     </row>
     <row r="19">
@@ -4967,7 +5167,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>152.7772151493148</v>
+        <v>152.7772824030114</v>
       </c>
     </row>
     <row r="20">
@@ -4975,7 +5175,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>189.0547574642828</v>
+        <v>189.0546872553826</v>
       </c>
     </row>
     <row r="21">
@@ -4983,7 +5183,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>222.0955917251714</v>
+        <v>222.0955941705216</v>
       </c>
     </row>
     <row r="22">
@@ -4991,7 +5191,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>217.2799546893305</v>
+        <v>217.279955217338</v>
       </c>
     </row>
     <row r="23">
@@ -4999,7 +5199,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>180.1480185896024</v>
+        <v>180.1480185712385</v>
       </c>
     </row>
     <row r="24">
@@ -5007,7 +5207,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>148.6444623822979</v>
+        <v>148.6444623825056</v>
       </c>
     </row>
     <row r="25">
@@ -5015,7 +5215,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>152.7772160693028</v>
+        <v>152.7772824030219</v>
       </c>
     </row>
     <row r="26">
@@ -5023,7 +5223,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>189.054756503852</v>
+        <v>189.0546872556404</v>
       </c>
     </row>
   </sheetData>
@@ -5473,79 +5673,79 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39.95069569241919</v>
+        <v>39.95069569297092</v>
       </c>
       <c r="C3" t="n">
-        <v>39.95069566509495</v>
+        <v>39.95069566564661</v>
       </c>
       <c r="D3" t="n">
-        <v>39.94899050182349</v>
+        <v>39.94899050237277</v>
       </c>
       <c r="E3" t="n">
-        <v>39.94224390678718</v>
+        <v>39.94224390733372</v>
       </c>
       <c r="F3" t="n">
-        <v>39.93469535955347</v>
+        <v>39.93469536009938</v>
       </c>
       <c r="G3" t="n">
-        <v>39.93469535955347</v>
+        <v>39.93469536009938</v>
       </c>
       <c r="H3" t="n">
-        <v>39.92497447762521</v>
+        <v>39.92497447816874</v>
       </c>
       <c r="I3" t="n">
-        <v>39.899067786976</v>
+        <v>39.89906778751605</v>
       </c>
       <c r="J3" t="n">
-        <v>39.86576536124841</v>
+        <v>39.86576536178672</v>
       </c>
       <c r="K3" t="n">
-        <v>39.84493540139299</v>
+        <v>39.84493540193158</v>
       </c>
       <c r="L3" t="n">
-        <v>39.93469535955347</v>
+        <v>39.93469536009938</v>
       </c>
       <c r="M3" t="n">
-        <v>39.92832570172363</v>
+        <v>39.92832570226908</v>
       </c>
       <c r="N3" t="n">
-        <v>39.91430940718795</v>
+        <v>39.91430940773287</v>
       </c>
       <c r="O3" t="n">
-        <v>39.89895025967706</v>
+        <v>39.8989502602218</v>
       </c>
       <c r="P3" t="n">
-        <v>39.89056661995362</v>
+        <v>39.89056662049849</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.23655487082976</v>
+        <v>40.23655487111707</v>
       </c>
       <c r="R3" t="n">
-        <v>40.23655452703478</v>
+        <v>40.23655452732167</v>
       </c>
       <c r="S3" t="n">
-        <v>40.23409492882571</v>
+        <v>40.23409492910047</v>
       </c>
       <c r="T3" t="n">
-        <v>40.22570015557341</v>
+        <v>40.22570015582729</v>
       </c>
       <c r="U3" t="n">
-        <v>40.21766958282272</v>
+        <v>40.21766958306318</v>
       </c>
       <c r="V3" t="n">
-        <v>40.21766958282272</v>
+        <v>40.21766958306318</v>
       </c>
       <c r="W3" t="n">
-        <v>40.21810007797681</v>
+        <v>40.2181000782167</v>
       </c>
       <c r="X3" t="n">
-        <v>40.21811061996178</v>
+        <v>40.21811062020157</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.21747228479799</v>
+        <v>40.21747228503749</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.21611074879555</v>
+        <v>40.21611074903505</v>
       </c>
     </row>
     <row r="4">
@@ -5553,79 +5753,79 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.13916810617216</v>
+        <v>39.13916821569438</v>
       </c>
       <c r="C4" t="n">
-        <v>39.13562637244799</v>
+        <v>39.13562648131382</v>
       </c>
       <c r="D4" t="n">
-        <v>39.1253474732872</v>
+        <v>39.12534758103376</v>
       </c>
       <c r="E4" t="n">
-        <v>39.11123351821949</v>
+        <v>39.1112336251942</v>
       </c>
       <c r="F4" t="n">
-        <v>39.10193265458157</v>
+        <v>39.10193276142233</v>
       </c>
       <c r="G4" t="n">
-        <v>39.10193265458157</v>
+        <v>39.10193276142233</v>
       </c>
       <c r="H4" t="n">
-        <v>39.08614685604767</v>
+        <v>39.0861469623058</v>
       </c>
       <c r="I4" t="n">
-        <v>39.05113949678792</v>
+        <v>39.05113960226466</v>
       </c>
       <c r="J4" t="n">
-        <v>39.01245835184371</v>
+        <v>39.01245845696457</v>
       </c>
       <c r="K4" t="n">
-        <v>38.99117301861251</v>
+        <v>38.99117312379071</v>
       </c>
       <c r="L4" t="n">
-        <v>39.10193265458157</v>
+        <v>39.10193276142233</v>
       </c>
       <c r="M4" t="n">
-        <v>39.09429008944149</v>
+        <v>39.09429019619061</v>
       </c>
       <c r="N4" t="n">
-        <v>39.07840653335028</v>
+        <v>39.07840663998984</v>
       </c>
       <c r="O4" t="n">
-        <v>39.06190808869603</v>
+        <v>39.06190819530266</v>
       </c>
       <c r="P4" t="n">
-        <v>39.05334489158427</v>
+        <v>39.05334499821428</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.45809406731522</v>
+        <v>39.46143605351828</v>
       </c>
       <c r="R4" t="n">
-        <v>39.45008966297236</v>
+        <v>39.45327088639115</v>
       </c>
       <c r="S4" t="n">
-        <v>39.42717188919738</v>
+        <v>39.42999951458239</v>
       </c>
       <c r="T4" t="n">
-        <v>39.39586576749502</v>
+        <v>39.39831208768413</v>
       </c>
       <c r="U4" t="n">
-        <v>39.37521087039028</v>
+        <v>39.37745396162289</v>
       </c>
       <c r="V4" t="n">
-        <v>39.37521087039028</v>
+        <v>39.37745396162289</v>
       </c>
       <c r="W4" t="n">
-        <v>39.37534180280429</v>
+        <v>39.3775820218693</v>
       </c>
       <c r="X4" t="n">
-        <v>39.37528294140713</v>
+        <v>39.37752142773209</v>
       </c>
       <c r="Y4" t="n">
-        <v>39.37438377563857</v>
+        <v>39.37661870151706</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.37299332791007</v>
+        <v>39.37522833207339</v>
       </c>
     </row>
     <row r="5">
@@ -5633,79 +5833,79 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.12900720218208</v>
+        <v>39.12900719675705</v>
       </c>
       <c r="C5" t="n">
-        <v>39.12147321803036</v>
+        <v>39.12147321361386</v>
       </c>
       <c r="D5" t="n">
-        <v>39.10632882466233</v>
+        <v>39.10632882167931</v>
       </c>
       <c r="E5" t="n">
-        <v>39.09107944984874</v>
+        <v>39.09107944772694</v>
       </c>
       <c r="F5" t="n">
-        <v>39.08339907389356</v>
+        <v>39.08339907191833</v>
       </c>
       <c r="G5" t="n">
-        <v>39.08339907389356</v>
+        <v>39.08339907191833</v>
       </c>
       <c r="H5" t="n">
-        <v>39.06808235773622</v>
+        <v>39.06808235638444</v>
       </c>
       <c r="I5" t="n">
-        <v>39.03736612284406</v>
+        <v>39.0373661223196</v>
       </c>
       <c r="J5" t="n">
-        <v>39.00657165576323</v>
+        <v>39.00657165565173</v>
       </c>
       <c r="K5" t="n">
-        <v>38.99115070174049</v>
+        <v>38.99115070162895</v>
       </c>
       <c r="L5" t="n">
-        <v>39.08339907389356</v>
+        <v>39.08339907191833</v>
       </c>
       <c r="M5" t="n">
-        <v>39.07721226399013</v>
+        <v>39.07721226211807</v>
       </c>
       <c r="N5" t="n">
-        <v>39.064825817301</v>
+        <v>39.06482581556626</v>
       </c>
       <c r="O5" t="n">
-        <v>39.05242679627766</v>
+        <v>39.05242679461134</v>
       </c>
       <c r="P5" t="n">
-        <v>39.04622229760295</v>
+        <v>39.04622229593637</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.31105125540673</v>
+        <v>39.31078975050339</v>
       </c>
       <c r="R5" t="n">
-        <v>39.26425113672885</v>
+        <v>39.26423043417275</v>
       </c>
       <c r="S5" t="n">
-        <v>39.16689988789289</v>
+        <v>39.16730807833645</v>
       </c>
       <c r="T5" t="n">
-        <v>39.06408002081648</v>
+        <v>39.06488154757029</v>
       </c>
       <c r="U5" t="n">
-        <v>39.00909549977626</v>
+        <v>39.01008396879591</v>
       </c>
       <c r="V5" t="n">
-        <v>39.00909549977626</v>
+        <v>39.01008396879591</v>
       </c>
       <c r="W5" t="n">
-        <v>39.00897667961316</v>
+        <v>39.00996667774935</v>
       </c>
       <c r="X5" t="n">
-        <v>39.00833937279327</v>
+        <v>39.00933276486</v>
       </c>
       <c r="Y5" t="n">
-        <v>39.00710274203402</v>
+        <v>39.00809852409844</v>
       </c>
       <c r="Z5" t="n">
-        <v>39.00608469659277</v>
+        <v>39.00708050436342</v>
       </c>
     </row>
     <row r="6">
@@ -5713,79 +5913,79 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08463060360708</v>
+        <v>39.08463060356092</v>
       </c>
       <c r="C6" t="n">
-        <v>39.07964449434272</v>
+        <v>39.07964449427602</v>
       </c>
       <c r="D6" t="n">
-        <v>39.06949359649484</v>
+        <v>39.06949359640523</v>
       </c>
       <c r="E6" t="n">
-        <v>39.05918249861681</v>
+        <v>39.05918249851654</v>
       </c>
       <c r="F6" t="n">
-        <v>39.0539568607969</v>
+        <v>39.05395686069564</v>
       </c>
       <c r="G6" t="n">
-        <v>39.0539568607969</v>
+        <v>39.05395686069564</v>
       </c>
       <c r="H6" t="n">
-        <v>39.0435434786972</v>
+        <v>39.0435434785932</v>
       </c>
       <c r="I6" t="n">
-        <v>39.02263182075141</v>
+        <v>39.02263182064597</v>
       </c>
       <c r="J6" t="n">
-        <v>39.00166122754243</v>
+        <v>39.00166122743691</v>
       </c>
       <c r="K6" t="n">
-        <v>38.99116233341491</v>
+        <v>38.99116233330937</v>
       </c>
       <c r="L6" t="n">
-        <v>39.0539568607969</v>
+        <v>39.05395686069564</v>
       </c>
       <c r="M6" t="n">
-        <v>39.04975192309768</v>
+        <v>39.04975192299509</v>
       </c>
       <c r="N6" t="n">
-        <v>39.04132672802245</v>
+        <v>39.04132672791816</v>
       </c>
       <c r="O6" t="n">
-        <v>39.0328873685527</v>
+        <v>39.03288736844758</v>
       </c>
       <c r="P6" t="n">
-        <v>39.02866163915246</v>
+        <v>39.02866163904732</v>
       </c>
       <c r="Q6" t="n">
-        <v>39.48530489031069</v>
+        <v>39.48410927996271</v>
       </c>
       <c r="R6" t="n">
-        <v>39.4020352819895</v>
+        <v>39.40105675766028</v>
       </c>
       <c r="S6" t="n">
-        <v>39.23868584669294</v>
+        <v>39.23811425027212</v>
       </c>
       <c r="T6" t="n">
-        <v>39.07649434470713</v>
+        <v>39.07630577407528</v>
       </c>
       <c r="U6" t="n">
-        <v>38.99522112498948</v>
+        <v>38.99521280149611</v>
       </c>
       <c r="V6" t="n">
-        <v>38.99522112498948</v>
+        <v>38.99521280149611</v>
       </c>
       <c r="W6" t="n">
-        <v>38.99457069171591</v>
+        <v>38.9945652822044</v>
       </c>
       <c r="X6" t="n">
-        <v>38.99324149534452</v>
+        <v>38.9932400146824</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.99188225558065</v>
+        <v>38.99188276282596</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.99118731983827</v>
+        <v>38.99118782709248</v>
       </c>
     </row>
     <row r="7">
@@ -5793,79 +5993,79 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.08557479363291</v>
+        <v>39.08557479366659</v>
       </c>
       <c r="C7" t="n">
-        <v>39.08033042693347</v>
+        <v>39.08033042696648</v>
       </c>
       <c r="D7" t="n">
-        <v>39.06984325886356</v>
+        <v>39.06984325889537</v>
       </c>
       <c r="E7" t="n">
-        <v>39.05935479527449</v>
+        <v>39.0593547953055</v>
       </c>
       <c r="F7" t="n">
-        <v>39.05410953098428</v>
+        <v>39.05410953101514</v>
       </c>
       <c r="G7" t="n">
-        <v>39.05410953098428</v>
+        <v>39.05410953101514</v>
       </c>
       <c r="H7" t="n">
-        <v>39.0436245602279</v>
+        <v>39.04362456025812</v>
       </c>
       <c r="I7" t="n">
-        <v>39.02264925584158</v>
+        <v>39.02264925587096</v>
       </c>
       <c r="J7" t="n">
-        <v>39.0016627447986</v>
+        <v>39.00166274482756</v>
       </c>
       <c r="K7" t="n">
-        <v>38.99116385107911</v>
+        <v>38.99116385110808</v>
       </c>
       <c r="L7" t="n">
-        <v>39.05410953098428</v>
+        <v>39.05410953101514</v>
       </c>
       <c r="M7" t="n">
-        <v>39.04988600444059</v>
+        <v>39.04988600447134</v>
       </c>
       <c r="N7" t="n">
-        <v>39.04143810917459</v>
+        <v>39.0414381092052</v>
       </c>
       <c r="O7" t="n">
-        <v>39.03298844635733</v>
+        <v>39.03298844638789</v>
       </c>
       <c r="P7" t="n">
-        <v>39.02876272788879</v>
+        <v>39.02876272791936</v>
       </c>
       <c r="Q7" t="n">
-        <v>39.49920777391523</v>
+        <v>39.4992456538191</v>
       </c>
       <c r="R7" t="n">
-        <v>39.41556617088636</v>
+        <v>39.41558213937028</v>
       </c>
       <c r="S7" t="n">
-        <v>39.24827827907907</v>
+        <v>39.24827601316633</v>
       </c>
       <c r="T7" t="n">
-        <v>39.08052664462092</v>
+        <v>39.08052078245021</v>
       </c>
       <c r="U7" t="n">
-        <v>38.9963434394874</v>
+        <v>38.99633814519908</v>
       </c>
       <c r="V7" t="n">
-        <v>38.9963434394874</v>
+        <v>38.99633814519908</v>
       </c>
       <c r="W7" t="n">
-        <v>38.99564548438654</v>
+        <v>38.99564019954575</v>
       </c>
       <c r="X7" t="n">
-        <v>38.99425172527444</v>
+        <v>38.99424645956583</v>
       </c>
       <c r="Y7" t="n">
-        <v>38.99285996063432</v>
+        <v>38.99285470639101</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.99216504204056</v>
+        <v>38.99215978770511</v>
       </c>
     </row>
     <row r="8">
@@ -5873,79 +6073,79 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.13089607071286</v>
+        <v>39.13089607063569</v>
       </c>
       <c r="C8" t="n">
-        <v>39.12288548007101</v>
+        <v>39.12288547999484</v>
       </c>
       <c r="D8" t="n">
-        <v>39.10708789978717</v>
+        <v>39.10708789971238</v>
       </c>
       <c r="E8" t="n">
-        <v>39.09148126276332</v>
+        <v>39.09148126268934</v>
       </c>
       <c r="F8" t="n">
-        <v>39.08375946916743</v>
+        <v>39.08375946909357</v>
       </c>
       <c r="G8" t="n">
-        <v>39.08375946916743</v>
+        <v>39.08375946909357</v>
       </c>
       <c r="H8" t="n">
-        <v>39.06828182802425</v>
+        <v>39.06828182795095</v>
       </c>
       <c r="I8" t="n">
-        <v>39.0374113051957</v>
+        <v>39.03741130512316</v>
       </c>
       <c r="J8" t="n">
-        <v>39.00657444153163</v>
+        <v>39.00657444145943</v>
       </c>
       <c r="K8" t="n">
-        <v>38.99115348860683</v>
+        <v>38.99115348853459</v>
       </c>
       <c r="L8" t="n">
-        <v>39.08375946916743</v>
+        <v>39.08375946909357</v>
       </c>
       <c r="M8" t="n">
-        <v>39.07753730407031</v>
+        <v>39.07753730399654</v>
       </c>
       <c r="N8" t="n">
-        <v>39.06510863251701</v>
+        <v>39.06510863244335</v>
       </c>
       <c r="O8" t="n">
-        <v>39.05269110373246</v>
+        <v>39.05269110365884</v>
       </c>
       <c r="P8" t="n">
-        <v>39.04648664701971</v>
+        <v>39.04648664694607</v>
       </c>
       <c r="Q8" t="n">
-        <v>39.74424080094915</v>
+        <v>39.74424748080921</v>
       </c>
       <c r="R8" t="n">
-        <v>39.6170340521037</v>
+        <v>39.61703963367228</v>
       </c>
       <c r="S8" t="n">
-        <v>39.36818453873716</v>
+        <v>39.36818761020951</v>
       </c>
       <c r="T8" t="n">
-        <v>39.12154530009197</v>
+        <v>39.12154601673878</v>
       </c>
       <c r="U8" t="n">
-        <v>38.99809617049092</v>
+        <v>38.99809580177</v>
       </c>
       <c r="V8" t="n">
-        <v>38.99809617049092</v>
+        <v>38.99809580177</v>
       </c>
       <c r="W8" t="n">
-        <v>38.99707500917741</v>
+        <v>38.9970746225618</v>
       </c>
       <c r="X8" t="n">
-        <v>38.99503613803612</v>
+        <v>38.9950357276628</v>
       </c>
       <c r="Y8" t="n">
-        <v>38.99299908319816</v>
+        <v>38.99299866096834</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.99198067352776</v>
+        <v>38.99198025128704</v>
       </c>
     </row>
     <row r="9">
@@ -5953,79 +6153,79 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39.18391652813892</v>
+        <v>39.18391652814331</v>
       </c>
       <c r="C9" t="n">
-        <v>39.17287152891973</v>
+        <v>39.17287152892327</v>
       </c>
       <c r="D9" t="n">
-        <v>39.15108807004171</v>
+        <v>39.15108807004405</v>
       </c>
       <c r="E9" t="n">
-        <v>39.12956611695891</v>
+        <v>39.12956611696053</v>
       </c>
       <c r="F9" t="n">
-        <v>39.11891700914087</v>
+        <v>39.11891700914238</v>
       </c>
       <c r="G9" t="n">
-        <v>39.11891700914087</v>
+        <v>39.11891700914238</v>
       </c>
       <c r="H9" t="n">
-        <v>39.09756795798139</v>
+        <v>39.0975679579824</v>
       </c>
       <c r="I9" t="n">
-        <v>39.05498184580512</v>
+        <v>39.05498184580547</v>
       </c>
       <c r="J9" t="n">
-        <v>39.01243047654696</v>
+        <v>39.01243047654697</v>
       </c>
       <c r="K9" t="n">
-        <v>38.99114512811418</v>
+        <v>38.9911451281142</v>
       </c>
       <c r="L9" t="n">
-        <v>39.11891700914087</v>
+        <v>39.11891700914238</v>
       </c>
       <c r="M9" t="n">
-        <v>39.11033476193529</v>
+        <v>39.11033476193672</v>
       </c>
       <c r="N9" t="n">
-        <v>39.09319106533926</v>
+        <v>39.09319106534058</v>
       </c>
       <c r="O9" t="n">
-        <v>39.07606088094752</v>
+        <v>39.07606088094877</v>
       </c>
       <c r="P9" t="n">
-        <v>39.06750078375963</v>
+        <v>39.06750078376088</v>
       </c>
       <c r="Q9" t="n">
-        <v>40.02403698345697</v>
+        <v>40.02403731565331</v>
       </c>
       <c r="R9" t="n">
-        <v>39.84987837942711</v>
+        <v>39.84987876466714</v>
       </c>
       <c r="S9" t="n">
-        <v>39.50864852931355</v>
+        <v>39.50864882927844</v>
       </c>
       <c r="T9" t="n">
-        <v>39.16965810985402</v>
+        <v>39.1696582217885</v>
       </c>
       <c r="U9" t="n">
-        <v>38.99958753424587</v>
+        <v>38.99958753960236</v>
       </c>
       <c r="V9" t="n">
-        <v>38.99958753424587</v>
+        <v>38.99958753960236</v>
       </c>
       <c r="W9" t="n">
-        <v>38.99818236878017</v>
+        <v>38.99818237237498</v>
       </c>
       <c r="X9" t="n">
-        <v>38.99537512455262</v>
+        <v>38.99537512574861</v>
       </c>
       <c r="Y9" t="n">
-        <v>38.99256865519364</v>
+        <v>38.99256865517498</v>
       </c>
       <c r="Z9" t="n">
-        <v>38.99116470101737</v>
+        <v>38.9911647009987</v>
       </c>
     </row>
     <row r="10">
@@ -6033,79 +6233,79 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39.1822913453618</v>
+        <v>39.1822913410093</v>
       </c>
       <c r="C10" t="n">
-        <v>39.1716962975573</v>
+        <v>39.17169629324959</v>
       </c>
       <c r="D10" t="n">
-        <v>39.15049324723361</v>
+        <v>39.15049324298901</v>
       </c>
       <c r="E10" t="n">
-        <v>39.12927506304576</v>
+        <v>39.12927505883823</v>
       </c>
       <c r="F10" t="n">
-        <v>39.11865932697016</v>
+        <v>39.11865932276821</v>
       </c>
       <c r="G10" t="n">
-        <v>39.11865932697016</v>
+        <v>39.11865932276821</v>
       </c>
       <c r="H10" t="n">
-        <v>39.09743213001197</v>
+        <v>39.09743212583641</v>
       </c>
       <c r="I10" t="n">
-        <v>39.05495407161182</v>
+        <v>39.05495406746984</v>
       </c>
       <c r="J10" t="n">
-        <v>39.01242970686027</v>
+        <v>39.01242970273283</v>
       </c>
       <c r="K10" t="n">
-        <v>38.99114435800776</v>
+        <v>38.99114435387806</v>
       </c>
       <c r="L10" t="n">
-        <v>39.11865932697016</v>
+        <v>39.11865932276821</v>
       </c>
       <c r="M10" t="n">
-        <v>39.11010876467884</v>
+        <v>39.11010876048068</v>
       </c>
       <c r="N10" t="n">
-        <v>39.09300373417785</v>
+        <v>39.09300372998413</v>
       </c>
       <c r="O10" t="n">
-        <v>39.07589108300554</v>
+        <v>39.07589107881312</v>
       </c>
       <c r="P10" t="n">
-        <v>39.06733094863966</v>
+        <v>39.06733094444633</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.00694821868519</v>
+        <v>40.006948105</v>
       </c>
       <c r="R10" t="n">
-        <v>39.84073443732751</v>
+        <v>39.8407343484463</v>
       </c>
       <c r="S10" t="n">
-        <v>39.506587740245</v>
+        <v>39.50658768416539</v>
       </c>
       <c r="T10" t="n">
-        <v>39.16953961510336</v>
+        <v>39.16953957932113</v>
       </c>
       <c r="U10" t="n">
-        <v>38.99956341983653</v>
+        <v>38.99956339164412</v>
       </c>
       <c r="V10" t="n">
-        <v>38.99956341983653</v>
+        <v>38.99956339164412</v>
       </c>
       <c r="W10" t="n">
-        <v>38.99815981490075</v>
+        <v>38.99815978683475</v>
       </c>
       <c r="X10" t="n">
-        <v>38.99535243987734</v>
+        <v>38.99535241197309</v>
       </c>
       <c r="Y10" t="n">
-        <v>38.99254479904877</v>
+        <v>38.99254477122255</v>
       </c>
       <c r="Z10" t="n">
-        <v>38.9911408440203</v>
+        <v>38.9911408161931</v>
       </c>
     </row>
     <row r="11">
@@ -6113,79 +6313,79 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39.128374977352</v>
+        <v>39.12837497755943</v>
       </c>
       <c r="C11" t="n">
-        <v>39.12105721232783</v>
+        <v>39.12105721249613</v>
       </c>
       <c r="D11" t="n">
-        <v>39.10615884749192</v>
+        <v>39.10615884760434</v>
       </c>
       <c r="E11" t="n">
-        <v>39.09102512727801</v>
+        <v>39.09102512735673</v>
       </c>
       <c r="F11" t="n">
-        <v>39.08335551442483</v>
+        <v>39.08335551449781</v>
       </c>
       <c r="G11" t="n">
-        <v>39.08335551442483</v>
+        <v>39.08335551449781</v>
       </c>
       <c r="H11" t="n">
-        <v>39.06806829774511</v>
+        <v>39.06806829779364</v>
       </c>
       <c r="I11" t="n">
-        <v>39.03736689136245</v>
+        <v>39.03736689137853</v>
       </c>
       <c r="J11" t="n">
-        <v>39.00657230979394</v>
+        <v>39.00657230979382</v>
       </c>
       <c r="K11" t="n">
-        <v>38.99115135602694</v>
+        <v>38.99115135602683</v>
       </c>
       <c r="L11" t="n">
-        <v>39.08335551442483</v>
+        <v>39.08335551449781</v>
       </c>
       <c r="M11" t="n">
-        <v>39.07718282678277</v>
+        <v>39.0771828268517</v>
       </c>
       <c r="N11" t="n">
-        <v>39.06481456664994</v>
+        <v>39.06481456671347</v>
       </c>
       <c r="O11" t="n">
-        <v>39.05242444933587</v>
+        <v>39.05242444939671</v>
       </c>
       <c r="P11" t="n">
-        <v>39.04621995028747</v>
+        <v>39.04621995034832</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.71491119733449</v>
+        <v>39.7149112426338</v>
       </c>
       <c r="R11" t="n">
-        <v>39.60035488811306</v>
+        <v>39.60035492388328</v>
       </c>
       <c r="S11" t="n">
-        <v>39.36325135588862</v>
+        <v>39.36325137602105</v>
       </c>
       <c r="T11" t="n">
-        <v>39.12026870947402</v>
+        <v>39.12026871601282</v>
       </c>
       <c r="U11" t="n">
-        <v>38.99724834971128</v>
+        <v>38.99724835001361</v>
       </c>
       <c r="V11" t="n">
-        <v>38.99724834971128</v>
+        <v>38.99724835001361</v>
       </c>
       <c r="W11" t="n">
-        <v>38.99623427709088</v>
+        <v>38.99623427729053</v>
       </c>
       <c r="X11" t="n">
-        <v>38.99420137102626</v>
+        <v>38.99420137108942</v>
       </c>
       <c r="Y11" t="n">
-        <v>38.99216554256988</v>
+        <v>38.9921655425649</v>
       </c>
       <c r="Z11" t="n">
-        <v>38.99114711136485</v>
+        <v>38.99114711135988</v>
       </c>
     </row>
     <row r="12">
@@ -6193,79 +6393,79 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>39.08463320130395</v>
+        <v>39.08463320130168</v>
       </c>
       <c r="C12" t="n">
-        <v>39.07964572949853</v>
+        <v>39.07964572949705</v>
       </c>
       <c r="D12" t="n">
-        <v>39.06949385934627</v>
+        <v>39.06949385934568</v>
       </c>
       <c r="E12" t="n">
-        <v>39.05918251218601</v>
+        <v>39.05918251218583</v>
       </c>
       <c r="F12" t="n">
-        <v>39.05395686630042</v>
+        <v>39.05395686630029</v>
       </c>
       <c r="G12" t="n">
-        <v>39.05395686630042</v>
+        <v>39.05395686630029</v>
       </c>
       <c r="H12" t="n">
-        <v>39.0435434638493</v>
+        <v>39.04354346384926</v>
       </c>
       <c r="I12" t="n">
         <v>39.02263181055864</v>
       </c>
       <c r="J12" t="n">
-        <v>39.00166121949059</v>
+        <v>39.00166121949061</v>
       </c>
       <c r="K12" t="n">
-        <v>38.99116232536091</v>
+        <v>38.99116232536092</v>
       </c>
       <c r="L12" t="n">
-        <v>39.05395686630042</v>
+        <v>39.05395686630029</v>
       </c>
       <c r="M12" t="n">
-        <v>39.04975191732111</v>
+        <v>39.04975191732103</v>
       </c>
       <c r="N12" t="n">
-        <v>39.04132671511787</v>
+        <v>39.04132671511785</v>
       </c>
       <c r="O12" t="n">
-        <v>39.03288735441905</v>
+        <v>39.03288735441907</v>
       </c>
       <c r="P12" t="n">
-        <v>39.02866162501729</v>
+        <v>39.02866162501731</v>
       </c>
       <c r="Q12" t="n">
-        <v>39.48573310474398</v>
+        <v>39.48573310301042</v>
       </c>
       <c r="R12" t="n">
-        <v>39.40724225154822</v>
+        <v>39.40724225062237</v>
       </c>
       <c r="S12" t="n">
-        <v>39.24506615219035</v>
+        <v>39.24506615197648</v>
       </c>
       <c r="T12" t="n">
-        <v>39.07918307990646</v>
+        <v>39.07918307989185</v>
       </c>
       <c r="U12" t="n">
-        <v>38.99535613975002</v>
+        <v>38.99535613975098</v>
       </c>
       <c r="V12" t="n">
-        <v>38.99535613975002</v>
+        <v>38.99535613975098</v>
       </c>
       <c r="W12" t="n">
-        <v>38.99466406354071</v>
+        <v>38.99466406354193</v>
       </c>
       <c r="X12" t="n">
-        <v>38.99327671880577</v>
+        <v>38.9932767188071</v>
       </c>
       <c r="Y12" t="n">
-        <v>38.99188745809557</v>
+        <v>38.99188745809689</v>
       </c>
       <c r="Z12" t="n">
-        <v>38.99119252244443</v>
+        <v>38.99119252244576</v>
       </c>
     </row>
     <row r="13">
@@ -6273,79 +6473,79 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>39.08557478851508</v>
+        <v>39.08557478913145</v>
       </c>
       <c r="C13" t="n">
-        <v>39.08033042508414</v>
+        <v>39.08033042569597</v>
       </c>
       <c r="D13" t="n">
-        <v>39.06984325819413</v>
+        <v>39.06984325879954</v>
       </c>
       <c r="E13" t="n">
-        <v>39.05935479464337</v>
+        <v>39.05935479524497</v>
       </c>
       <c r="F13" t="n">
-        <v>39.0541095303414</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="G13" t="n">
-        <v>39.0541095303414</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="H13" t="n">
-        <v>39.04362455953492</v>
+        <v>39.0436245601332</v>
       </c>
       <c r="I13" t="n">
-        <v>39.02264925509409</v>
+        <v>39.02264925568883</v>
       </c>
       <c r="J13" t="n">
-        <v>39.00166274402711</v>
+        <v>39.00166274462025</v>
       </c>
       <c r="K13" t="n">
-        <v>38.99116385030739</v>
+        <v>38.99116385090071</v>
       </c>
       <c r="L13" t="n">
-        <v>39.0541095303414</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="M13" t="n">
-        <v>39.04988600378954</v>
+        <v>39.04988600439015</v>
       </c>
       <c r="N13" t="n">
-        <v>39.04143810850989</v>
+        <v>39.04143810910998</v>
       </c>
       <c r="O13" t="n">
-        <v>39.03298844568541</v>
+        <v>39.03298844628532</v>
       </c>
       <c r="P13" t="n">
-        <v>39.02876272721681</v>
+        <v>39.02876272781678</v>
       </c>
       <c r="Q13" t="n">
-        <v>39.49877695039479</v>
+        <v>39.49877863180064</v>
       </c>
       <c r="R13" t="n">
-        <v>39.41532047847303</v>
+        <v>39.41532198056873</v>
       </c>
       <c r="S13" t="n">
-        <v>39.24826310271673</v>
+        <v>39.24826428376215</v>
       </c>
       <c r="T13" t="n">
-        <v>39.08057782585425</v>
+        <v>39.0805787138756</v>
       </c>
       <c r="U13" t="n">
-        <v>38.99639370670926</v>
+        <v>38.99639445855772</v>
       </c>
       <c r="V13" t="n">
-        <v>38.99639370670926</v>
+        <v>38.99639445855772</v>
       </c>
       <c r="W13" t="n">
-        <v>38.99569573566624</v>
+        <v>38.99569648525854</v>
       </c>
       <c r="X13" t="n">
-        <v>38.99430185742555</v>
+        <v>38.99430260402563</v>
       </c>
       <c r="Y13" t="n">
-        <v>38.99291000387635</v>
+        <v>38.99291074899592</v>
       </c>
       <c r="Z13" t="n">
-        <v>38.9922150861603</v>
+        <v>38.99221583129296</v>
       </c>
     </row>
     <row r="14">
@@ -6353,79 +6553,79 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39.13089607074648</v>
+        <v>39.1308960707161</v>
       </c>
       <c r="C14" t="n">
-        <v>39.12288548009507</v>
+        <v>39.12288548007054</v>
       </c>
       <c r="D14" t="n">
-        <v>39.10708789980221</v>
+        <v>39.10708789978589</v>
       </c>
       <c r="E14" t="n">
-        <v>39.09148126277299</v>
+        <v>39.09148126276158</v>
       </c>
       <c r="F14" t="n">
-        <v>39.08375946917611</v>
+        <v>39.08375946916553</v>
       </c>
       <c r="G14" t="n">
-        <v>39.08375946917611</v>
+        <v>39.08375946916553</v>
       </c>
       <c r="H14" t="n">
-        <v>39.06828182802857</v>
+        <v>39.06828182802153</v>
       </c>
       <c r="I14" t="n">
-        <v>39.03741130519409</v>
+        <v>39.03741130519171</v>
       </c>
       <c r="J14" t="n">
-        <v>39.00657444152701</v>
+        <v>39.00657444152697</v>
       </c>
       <c r="K14" t="n">
-        <v>38.99115348860221</v>
+        <v>38.99115348860216</v>
       </c>
       <c r="L14" t="n">
-        <v>39.08375946917611</v>
+        <v>39.08375946916553</v>
       </c>
       <c r="M14" t="n">
-        <v>39.07753730407834</v>
+        <v>39.07753730406835</v>
       </c>
       <c r="N14" t="n">
-        <v>39.06510863252419</v>
+        <v>39.06510863251498</v>
       </c>
       <c r="O14" t="n">
-        <v>39.0526911037392</v>
+        <v>39.05269110373037</v>
       </c>
       <c r="P14" t="n">
-        <v>39.04648664702645</v>
+        <v>39.04648664701761</v>
       </c>
       <c r="Q14" t="n">
-        <v>39.74417760857937</v>
+        <v>39.74417654595072</v>
       </c>
       <c r="R14" t="n">
-        <v>39.61697953475734</v>
+        <v>39.61697870366276</v>
       </c>
       <c r="S14" t="n">
-        <v>39.36815328261618</v>
+        <v>39.36815283832012</v>
       </c>
       <c r="T14" t="n">
-        <v>39.12153691551418</v>
+        <v>39.12153680885818</v>
       </c>
       <c r="U14" t="n">
-        <v>38.9980983960311</v>
+        <v>38.99809844418806</v>
       </c>
       <c r="V14" t="n">
-        <v>38.9980983960311</v>
+        <v>38.99809844418806</v>
       </c>
       <c r="W14" t="n">
-        <v>38.99707740968035</v>
+        <v>38.99707746038975</v>
       </c>
       <c r="X14" t="n">
-        <v>38.99503877093671</v>
+        <v>38.99503882503453</v>
       </c>
       <c r="Y14" t="n">
-        <v>38.99300183207329</v>
+        <v>38.99300188786228</v>
       </c>
       <c r="Z14" t="n">
-        <v>38.99198342247391</v>
+        <v>38.99198347826435</v>
       </c>
     </row>
     <row r="15">
@@ -6433,79 +6633,79 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39.18391652814505</v>
+        <v>39.18391652813911</v>
       </c>
       <c r="C15" t="n">
-        <v>39.17287152892593</v>
+        <v>39.1728715289199</v>
       </c>
       <c r="D15" t="n">
-        <v>39.15108807004798</v>
+        <v>39.15108807004184</v>
       </c>
       <c r="E15" t="n">
-        <v>39.12956611696517</v>
+        <v>39.12956611695903</v>
       </c>
       <c r="F15" t="n">
-        <v>39.11891700914713</v>
+        <v>39.11891700914099</v>
       </c>
       <c r="G15" t="n">
-        <v>39.11891700914713</v>
+        <v>39.11891700914099</v>
       </c>
       <c r="H15" t="n">
-        <v>39.09756795798761</v>
+        <v>39.09756795798147</v>
       </c>
       <c r="I15" t="n">
-        <v>39.05498184581127</v>
+        <v>39.05498184580517</v>
       </c>
       <c r="J15" t="n">
-        <v>39.01243047655307</v>
+        <v>39.01243047654699</v>
       </c>
       <c r="K15" t="n">
-        <v>38.99114512812029</v>
+        <v>38.99114512811421</v>
       </c>
       <c r="L15" t="n">
-        <v>39.11891700914713</v>
+        <v>39.11891700914099</v>
       </c>
       <c r="M15" t="n">
-        <v>39.11033476194155</v>
+        <v>39.11033476193539</v>
       </c>
       <c r="N15" t="n">
-        <v>39.09319106534553</v>
+        <v>39.09319106533937</v>
       </c>
       <c r="O15" t="n">
-        <v>39.07606088095378</v>
+        <v>39.07606088094762</v>
       </c>
       <c r="P15" t="n">
-        <v>39.06750078376589</v>
+        <v>39.06750078375973</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.02403621357735</v>
+        <v>40.02403617463414</v>
       </c>
       <c r="R15" t="n">
-        <v>39.84987662513996</v>
+        <v>39.84987657648039</v>
       </c>
       <c r="S15" t="n">
-        <v>39.50864675248572</v>
+        <v>39.50864671322014</v>
       </c>
       <c r="T15" t="n">
-        <v>39.169657394555</v>
+        <v>39.16965737967076</v>
       </c>
       <c r="U15" t="n">
-        <v>38.9995874993635</v>
+        <v>38.99958749854608</v>
       </c>
       <c r="V15" t="n">
-        <v>38.9995874993635</v>
+        <v>38.99958749854608</v>
       </c>
       <c r="W15" t="n">
-        <v>38.99818234514471</v>
+        <v>38.99818234455982</v>
       </c>
       <c r="X15" t="n">
-        <v>38.99537511642471</v>
+        <v>38.99537511615703</v>
       </c>
       <c r="Y15" t="n">
-        <v>38.99256865497443</v>
+        <v>38.99256865486754</v>
       </c>
       <c r="Z15" t="n">
-        <v>38.99116470079816</v>
+        <v>38.99116470069125</v>
       </c>
     </row>
     <row r="16">
@@ -6513,79 +6713,79 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>39.18229134100904</v>
+        <v>39.18229134100939</v>
       </c>
       <c r="C16" t="n">
-        <v>39.17169629324938</v>
+        <v>39.17169629324965</v>
       </c>
       <c r="D16" t="n">
-        <v>39.15049324298888</v>
+        <v>39.15049324298906</v>
       </c>
       <c r="E16" t="n">
-        <v>39.12927505883813</v>
+        <v>39.12927505883825</v>
       </c>
       <c r="F16" t="n">
-        <v>39.11865932276813</v>
+        <v>39.11865932276825</v>
       </c>
       <c r="G16" t="n">
-        <v>39.11865932276813</v>
+        <v>39.11865932276825</v>
       </c>
       <c r="H16" t="n">
-        <v>39.09743212583638</v>
+        <v>39.09743212583644</v>
       </c>
       <c r="I16" t="n">
-        <v>39.05495406746986</v>
+        <v>39.05495406746987</v>
       </c>
       <c r="J16" t="n">
-        <v>39.01242970273289</v>
+        <v>39.01242970273286</v>
       </c>
       <c r="K16" t="n">
         <v>38.99114435387811</v>
       </c>
       <c r="L16" t="n">
-        <v>39.11865932276813</v>
+        <v>39.11865932276825</v>
       </c>
       <c r="M16" t="n">
-        <v>39.11010876048061</v>
+        <v>39.11010876048071</v>
       </c>
       <c r="N16" t="n">
-        <v>39.09300372998406</v>
+        <v>39.09300372998416</v>
       </c>
       <c r="O16" t="n">
-        <v>39.07589107881306</v>
+        <v>39.07589107881315</v>
       </c>
       <c r="P16" t="n">
-        <v>39.06733094444626</v>
+        <v>39.06733094444635</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.00694835386333</v>
+        <v>40.00694835879087</v>
       </c>
       <c r="R16" t="n">
-        <v>39.84073450039472</v>
+        <v>39.84073450333089</v>
       </c>
       <c r="S16" t="n">
-        <v>39.50658772390611</v>
+        <v>39.50658772470066</v>
       </c>
       <c r="T16" t="n">
-        <v>39.16953958257482</v>
+        <v>39.16953958266068</v>
       </c>
       <c r="U16" t="n">
-        <v>38.99956339170149</v>
+        <v>38.99956339170378</v>
       </c>
       <c r="V16" t="n">
-        <v>38.99956339170149</v>
+        <v>38.99956339170378</v>
       </c>
       <c r="W16" t="n">
-        <v>38.99815978683932</v>
+        <v>38.99815978684023</v>
       </c>
       <c r="X16" t="n">
-        <v>38.99535241195039</v>
+        <v>38.99535241195021</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.99254477119932</v>
+        <v>38.99254477119885</v>
       </c>
       <c r="Z16" t="n">
-        <v>38.99114081616985</v>
+        <v>38.99114081616938</v>
       </c>
     </row>
     <row r="17">
@@ -6593,79 +6793,79 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>39.12837497755942</v>
+        <v>39.12837497755943</v>
       </c>
       <c r="C17" t="n">
         <v>39.12105721249612</v>
       </c>
       <c r="D17" t="n">
-        <v>39.10615884760432</v>
+        <v>39.10615884760433</v>
       </c>
       <c r="E17" t="n">
         <v>39.09102512735672</v>
       </c>
       <c r="F17" t="n">
-        <v>39.08335551449778</v>
+        <v>39.0833555144978</v>
       </c>
       <c r="G17" t="n">
-        <v>39.08335551449778</v>
+        <v>39.0833555144978</v>
       </c>
       <c r="H17" t="n">
         <v>39.06806829779364</v>
       </c>
       <c r="I17" t="n">
-        <v>39.03736689137852</v>
+        <v>39.03736689137853</v>
       </c>
       <c r="J17" t="n">
-        <v>39.0065723097938</v>
+        <v>39.00657230979381</v>
       </c>
       <c r="K17" t="n">
         <v>38.99115135602682</v>
       </c>
       <c r="L17" t="n">
-        <v>39.08335551449778</v>
+        <v>39.0833555144978</v>
       </c>
       <c r="M17" t="n">
-        <v>39.07718282685168</v>
+        <v>39.0771828268517</v>
       </c>
       <c r="N17" t="n">
-        <v>39.06481456671345</v>
+        <v>39.06481456671348</v>
       </c>
       <c r="O17" t="n">
-        <v>39.05242444939669</v>
+        <v>39.05242444939671</v>
       </c>
       <c r="P17" t="n">
-        <v>39.0462199503483</v>
+        <v>39.04621995034832</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.71491123828962</v>
+        <v>39.71491123820066</v>
       </c>
       <c r="R17" t="n">
-        <v>39.6003549224854</v>
+        <v>39.60035492245441</v>
       </c>
       <c r="S17" t="n">
-        <v>39.36325137593182</v>
+        <v>39.36325137592813</v>
       </c>
       <c r="T17" t="n">
-        <v>39.12026871601769</v>
+        <v>39.12026871601697</v>
       </c>
       <c r="U17" t="n">
-        <v>38.99724835001512</v>
+        <v>38.99724835001454</v>
       </c>
       <c r="V17" t="n">
-        <v>38.99724835001512</v>
+        <v>38.99724835001454</v>
       </c>
       <c r="W17" t="n">
-        <v>38.99623427729197</v>
+        <v>38.99623427729139</v>
       </c>
       <c r="X17" t="n">
-        <v>38.99420137109074</v>
+        <v>38.99420137109017</v>
       </c>
       <c r="Y17" t="n">
-        <v>38.99216554256617</v>
+        <v>38.9921655425656</v>
       </c>
       <c r="Z17" t="n">
-        <v>38.99114711136116</v>
+        <v>38.99114711136058</v>
       </c>
     </row>
     <row r="18">
@@ -6673,16 +6873,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>39.08463320130167</v>
+        <v>39.08463320130166</v>
       </c>
       <c r="C18" t="n">
-        <v>39.07964572949704</v>
+        <v>39.07964572949705</v>
       </c>
       <c r="D18" t="n">
-        <v>39.06949385934567</v>
+        <v>39.06949385934568</v>
       </c>
       <c r="E18" t="n">
-        <v>39.05918251218582</v>
+        <v>39.05918251218583</v>
       </c>
       <c r="F18" t="n">
         <v>39.05395686630028</v>
@@ -6691,61 +6891,61 @@
         <v>39.05395686630028</v>
       </c>
       <c r="H18" t="n">
-        <v>39.04354346384925</v>
+        <v>39.04354346384926</v>
       </c>
       <c r="I18" t="n">
         <v>39.02263181055864</v>
       </c>
       <c r="J18" t="n">
-        <v>39.00166121949059</v>
+        <v>39.0016612194906</v>
       </c>
       <c r="K18" t="n">
-        <v>38.99116232536091</v>
+        <v>38.99116232536092</v>
       </c>
       <c r="L18" t="n">
         <v>39.05395686630028</v>
       </c>
       <c r="M18" t="n">
-        <v>39.04975191732102</v>
+        <v>39.04975191732103</v>
       </c>
       <c r="N18" t="n">
-        <v>39.04132671511784</v>
+        <v>39.04132671511785</v>
       </c>
       <c r="O18" t="n">
         <v>39.03288735441907</v>
       </c>
       <c r="P18" t="n">
-        <v>39.02866162501729</v>
+        <v>39.0286616250173</v>
       </c>
       <c r="Q18" t="n">
-        <v>39.48573310302962</v>
+        <v>39.48573310303048</v>
       </c>
       <c r="R18" t="n">
-        <v>39.40724225062327</v>
+        <v>39.4072422506236</v>
       </c>
       <c r="S18" t="n">
-        <v>39.24506615197573</v>
+        <v>39.2450661519758</v>
       </c>
       <c r="T18" t="n">
-        <v>39.07918307989169</v>
+        <v>39.07918307989159</v>
       </c>
       <c r="U18" t="n">
-        <v>38.99535613975106</v>
+        <v>38.9953561397509</v>
       </c>
       <c r="V18" t="n">
-        <v>38.99535613975106</v>
+        <v>38.9953561397509</v>
       </c>
       <c r="W18" t="n">
-        <v>38.994664063542</v>
+        <v>38.99466406354185</v>
       </c>
       <c r="X18" t="n">
-        <v>38.99327671880717</v>
+        <v>38.99327671880701</v>
       </c>
       <c r="Y18" t="n">
-        <v>38.99188745809697</v>
+        <v>38.99188745809681</v>
       </c>
       <c r="Z18" t="n">
-        <v>38.99119252244584</v>
+        <v>38.99119252244568</v>
       </c>
     </row>
     <row r="19">
@@ -6753,79 +6953,79 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>39.08557478851339</v>
+        <v>39.08557478913144</v>
       </c>
       <c r="C19" t="n">
-        <v>39.08033042508246</v>
+        <v>39.08033042569596</v>
       </c>
       <c r="D19" t="n">
-        <v>39.06984325819246</v>
+        <v>39.06984325879952</v>
       </c>
       <c r="E19" t="n">
-        <v>39.05935479464171</v>
+        <v>39.05935479524497</v>
       </c>
       <c r="F19" t="n">
-        <v>39.05410953033974</v>
+        <v>39.0541095309424</v>
       </c>
       <c r="G19" t="n">
-        <v>39.05410953033974</v>
+        <v>39.0541095309424</v>
       </c>
       <c r="H19" t="n">
-        <v>39.04362455953327</v>
+        <v>39.0436245601332</v>
       </c>
       <c r="I19" t="n">
-        <v>39.02264925509245</v>
+        <v>39.02264925568884</v>
       </c>
       <c r="J19" t="n">
-        <v>39.00166274402547</v>
+        <v>39.00166274462025</v>
       </c>
       <c r="K19" t="n">
-        <v>38.99116385030577</v>
+        <v>38.9911638509007</v>
       </c>
       <c r="L19" t="n">
-        <v>39.05410953033974</v>
+        <v>39.0541095309424</v>
       </c>
       <c r="M19" t="n">
-        <v>39.04988600378789</v>
+        <v>39.04988600439014</v>
       </c>
       <c r="N19" t="n">
-        <v>39.04143810850824</v>
+        <v>39.04143810910998</v>
       </c>
       <c r="O19" t="n">
-        <v>39.03298844568376</v>
+        <v>39.03298844628532</v>
       </c>
       <c r="P19" t="n">
-        <v>39.02876272721515</v>
+        <v>39.02876272781678</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.4987769457646</v>
+        <v>39.49877863180093</v>
       </c>
       <c r="R19" t="n">
-        <v>39.41532047432401</v>
+        <v>39.41532198056899</v>
       </c>
       <c r="S19" t="n">
-        <v>39.24826309945017</v>
+        <v>39.24826428376232</v>
       </c>
       <c r="T19" t="n">
-        <v>39.08057782339817</v>
+        <v>39.0805787138757</v>
       </c>
       <c r="U19" t="n">
-        <v>38.99639370463002</v>
+        <v>38.99639445855779</v>
       </c>
       <c r="V19" t="n">
-        <v>38.99639370463002</v>
+        <v>38.99639445855779</v>
       </c>
       <c r="W19" t="n">
-        <v>38.99569573359324</v>
+        <v>38.99569648525861</v>
       </c>
       <c r="X19" t="n">
-        <v>38.99430185536084</v>
+        <v>38.99430260402571</v>
       </c>
       <c r="Y19" t="n">
-        <v>38.99291000181571</v>
+        <v>38.992910748996</v>
       </c>
       <c r="Z19" t="n">
-        <v>38.99221508409963</v>
+        <v>38.99221583129302</v>
       </c>
     </row>
     <row r="20">
@@ -6833,79 +7033,79 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>39.13089607074657</v>
+        <v>39.13089607071608</v>
       </c>
       <c r="C20" t="n">
-        <v>39.12288548009515</v>
+        <v>39.12288548007052</v>
       </c>
       <c r="D20" t="n">
-        <v>39.10708789980225</v>
+        <v>39.10708789978589</v>
       </c>
       <c r="E20" t="n">
-        <v>39.09148126277303</v>
+        <v>39.09148126276158</v>
       </c>
       <c r="F20" t="n">
-        <v>39.08375946917614</v>
+        <v>39.08375946916552</v>
       </c>
       <c r="G20" t="n">
-        <v>39.08375946917614</v>
+        <v>39.08375946916552</v>
       </c>
       <c r="H20" t="n">
-        <v>39.0682818280286</v>
+        <v>39.06828182802153</v>
       </c>
       <c r="I20" t="n">
-        <v>39.0374113051941</v>
+        <v>39.03741130519171</v>
       </c>
       <c r="J20" t="n">
-        <v>39.00657444152701</v>
+        <v>39.00657444152696</v>
       </c>
       <c r="K20" t="n">
-        <v>38.99115348860221</v>
+        <v>38.99115348860217</v>
       </c>
       <c r="L20" t="n">
-        <v>39.08375946917614</v>
+        <v>39.08375946916552</v>
       </c>
       <c r="M20" t="n">
-        <v>39.07753730407838</v>
+        <v>39.07753730406834</v>
       </c>
       <c r="N20" t="n">
-        <v>39.06510863252422</v>
+        <v>39.06510863251498</v>
       </c>
       <c r="O20" t="n">
-        <v>39.05269110373924</v>
+        <v>39.05269110373037</v>
       </c>
       <c r="P20" t="n">
-        <v>39.04648664702648</v>
+        <v>39.0464866470176</v>
       </c>
       <c r="Q20" t="n">
-        <v>39.74417761151814</v>
+        <v>39.74417654596289</v>
       </c>
       <c r="R20" t="n">
-        <v>39.61697953705585</v>
+        <v>39.61697870367352</v>
       </c>
       <c r="S20" t="n">
-        <v>39.36815328384497</v>
+        <v>39.36815283832836</v>
       </c>
       <c r="T20" t="n">
-        <v>39.12153691580918</v>
+        <v>39.12153680886416</v>
       </c>
       <c r="U20" t="n">
-        <v>38.99809839589797</v>
+        <v>38.99809844419298</v>
       </c>
       <c r="V20" t="n">
-        <v>38.99809839589797</v>
+        <v>38.99809844419298</v>
       </c>
       <c r="W20" t="n">
-        <v>38.99707740954015</v>
+        <v>38.99707746039464</v>
       </c>
       <c r="X20" t="n">
-        <v>38.99503877078713</v>
+        <v>38.9950388250394</v>
       </c>
       <c r="Y20" t="n">
-        <v>38.99300183191905</v>
+        <v>38.99300188786713</v>
       </c>
       <c r="Z20" t="n">
-        <v>38.99198342231966</v>
+        <v>38.9919834782692</v>
       </c>
     </row>
     <row r="21">
@@ -6913,79 +7113,79 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39.18391652814513</v>
+        <v>39.18391652813911</v>
       </c>
       <c r="C21" t="n">
-        <v>39.17287152892602</v>
+        <v>39.1728715289199</v>
       </c>
       <c r="D21" t="n">
-        <v>39.15108807004805</v>
+        <v>39.15108807004184</v>
       </c>
       <c r="E21" t="n">
-        <v>39.12956611696526</v>
+        <v>39.12956611695903</v>
       </c>
       <c r="F21" t="n">
-        <v>39.11891700914723</v>
+        <v>39.11891700914099</v>
       </c>
       <c r="G21" t="n">
-        <v>39.11891700914723</v>
+        <v>39.11891700914099</v>
       </c>
       <c r="H21" t="n">
-        <v>39.0975679579877</v>
+        <v>39.09756795798147</v>
       </c>
       <c r="I21" t="n">
-        <v>39.05498184581136</v>
+        <v>39.05498184580517</v>
       </c>
       <c r="J21" t="n">
-        <v>39.01243047655316</v>
+        <v>39.01243047654699</v>
       </c>
       <c r="K21" t="n">
-        <v>38.99114512812038</v>
+        <v>38.9911451281142</v>
       </c>
       <c r="L21" t="n">
-        <v>39.11891700914723</v>
+        <v>39.11891700914099</v>
       </c>
       <c r="M21" t="n">
-        <v>39.11033476194164</v>
+        <v>39.11033476193541</v>
       </c>
       <c r="N21" t="n">
-        <v>39.09319106534561</v>
+        <v>39.09319106533937</v>
       </c>
       <c r="O21" t="n">
-        <v>39.07606088095387</v>
+        <v>39.07606088094762</v>
       </c>
       <c r="P21" t="n">
-        <v>39.06750078376598</v>
+        <v>39.06750078375973</v>
       </c>
       <c r="Q21" t="n">
-        <v>40.02403621368867</v>
+        <v>40.0240361746249</v>
       </c>
       <c r="R21" t="n">
-        <v>39.84987662527769</v>
+        <v>39.84987657647308</v>
       </c>
       <c r="S21" t="n">
-        <v>39.50864675259669</v>
+        <v>39.50864671321603</v>
       </c>
       <c r="T21" t="n">
-        <v>39.16965739459785</v>
+        <v>39.16965737966944</v>
       </c>
       <c r="U21" t="n">
-        <v>38.9995874993671</v>
+        <v>38.99958749854603</v>
       </c>
       <c r="V21" t="n">
-        <v>38.9995874993671</v>
+        <v>38.99958749854603</v>
       </c>
       <c r="W21" t="n">
-        <v>38.99818234514766</v>
+        <v>38.99818234455978</v>
       </c>
       <c r="X21" t="n">
-        <v>38.99537511642678</v>
+        <v>38.99537511615702</v>
       </c>
       <c r="Y21" t="n">
-        <v>38.99256865497605</v>
+        <v>38.99256865486755</v>
       </c>
       <c r="Z21" t="n">
-        <v>38.99116470079977</v>
+        <v>38.99116470069126</v>
       </c>
     </row>
     <row r="22">
@@ -6993,79 +7193,79 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>39.18229134100903</v>
+        <v>39.1822913410094</v>
       </c>
       <c r="C22" t="n">
-        <v>39.17169629324938</v>
+        <v>39.17169629324966</v>
       </c>
       <c r="D22" t="n">
-        <v>39.15049324298888</v>
+        <v>39.15049324298907</v>
       </c>
       <c r="E22" t="n">
-        <v>39.12927505883813</v>
+        <v>39.12927505883827</v>
       </c>
       <c r="F22" t="n">
-        <v>39.11865932276812</v>
+        <v>39.11865932276825</v>
       </c>
       <c r="G22" t="n">
-        <v>39.11865932276812</v>
+        <v>39.11865932276825</v>
       </c>
       <c r="H22" t="n">
-        <v>39.09743212583637</v>
+        <v>39.09743212583644</v>
       </c>
       <c r="I22" t="n">
-        <v>39.05495406746986</v>
+        <v>39.05495406746989</v>
       </c>
       <c r="J22" t="n">
-        <v>39.01242970273288</v>
+        <v>39.01242970273287</v>
       </c>
       <c r="K22" t="n">
-        <v>38.99114435387811</v>
+        <v>38.9911443538781</v>
       </c>
       <c r="L22" t="n">
-        <v>39.11865932276812</v>
+        <v>39.11865932276825</v>
       </c>
       <c r="M22" t="n">
-        <v>39.11010876048061</v>
+        <v>39.11010876048072</v>
       </c>
       <c r="N22" t="n">
-        <v>39.09300372998406</v>
+        <v>39.09300372998416</v>
       </c>
       <c r="O22" t="n">
-        <v>39.07589107881306</v>
+        <v>39.07589107881315</v>
       </c>
       <c r="P22" t="n">
-        <v>39.06733094444626</v>
+        <v>39.06733094444637</v>
       </c>
       <c r="Q22" t="n">
-        <v>40.00694835384718</v>
+        <v>40.00694835879139</v>
       </c>
       <c r="R22" t="n">
-        <v>39.84073450038461</v>
+        <v>39.84073450333117</v>
       </c>
       <c r="S22" t="n">
-        <v>39.50658772390278</v>
+        <v>39.50658772470074</v>
       </c>
       <c r="T22" t="n">
-        <v>39.16953958257422</v>
+        <v>39.16953958266069</v>
       </c>
       <c r="U22" t="n">
-        <v>38.99956339170146</v>
+        <v>38.99956339170379</v>
       </c>
       <c r="V22" t="n">
-        <v>38.99956339170146</v>
+        <v>38.99956339170379</v>
       </c>
       <c r="W22" t="n">
-        <v>38.9981597868393</v>
+        <v>38.99815978684023</v>
       </c>
       <c r="X22" t="n">
-        <v>38.99535241195037</v>
+        <v>38.99535241195022</v>
       </c>
       <c r="Y22" t="n">
-        <v>38.99254477119931</v>
+        <v>38.99254477119884</v>
       </c>
       <c r="Z22" t="n">
-        <v>38.99114081616985</v>
+        <v>38.99114081616939</v>
       </c>
     </row>
     <row r="23">
@@ -7085,10 +7285,10 @@
         <v>39.09102512735672</v>
       </c>
       <c r="F23" t="n">
-        <v>39.08335551449779</v>
+        <v>39.0833555144978</v>
       </c>
       <c r="G23" t="n">
-        <v>39.08335551449779</v>
+        <v>39.0833555144978</v>
       </c>
       <c r="H23" t="n">
         <v>39.06806829779364</v>
@@ -7097,55 +7297,55 @@
         <v>39.03736689137853</v>
       </c>
       <c r="J23" t="n">
-        <v>39.00657230979381</v>
+        <v>39.00657230979382</v>
       </c>
       <c r="K23" t="n">
-        <v>38.99115135602683</v>
+        <v>38.99115135602682</v>
       </c>
       <c r="L23" t="n">
-        <v>39.08335551449779</v>
+        <v>39.0833555144978</v>
       </c>
       <c r="M23" t="n">
         <v>39.0771828268517</v>
       </c>
       <c r="N23" t="n">
-        <v>39.06481456671346</v>
+        <v>39.06481456671348</v>
       </c>
       <c r="O23" t="n">
-        <v>39.0524244493967</v>
+        <v>39.05242444939671</v>
       </c>
       <c r="P23" t="n">
-        <v>39.04621995034831</v>
+        <v>39.04621995034832</v>
       </c>
       <c r="Q23" t="n">
-        <v>39.71491123828997</v>
+        <v>39.71491123820027</v>
       </c>
       <c r="R23" t="n">
-        <v>39.60035492248554</v>
+        <v>39.60035492245407</v>
       </c>
       <c r="S23" t="n">
-        <v>39.36325137593184</v>
+        <v>39.36325137592787</v>
       </c>
       <c r="T23" t="n">
-        <v>39.12026871601769</v>
+        <v>39.12026871601678</v>
       </c>
       <c r="U23" t="n">
-        <v>38.99724835001512</v>
+        <v>38.9972483500144</v>
       </c>
       <c r="V23" t="n">
-        <v>38.99724835001512</v>
+        <v>38.9972483500144</v>
       </c>
       <c r="W23" t="n">
-        <v>38.99623427729197</v>
+        <v>38.99623427729124</v>
       </c>
       <c r="X23" t="n">
-        <v>38.99420137109074</v>
+        <v>38.99420137109002</v>
       </c>
       <c r="Y23" t="n">
-        <v>38.99216554256617</v>
+        <v>38.99216554256545</v>
       </c>
       <c r="Z23" t="n">
-        <v>38.99114711136115</v>
+        <v>38.99114711136043</v>
       </c>
     </row>
     <row r="24">
@@ -7153,10 +7353,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>39.08463320130166</v>
+        <v>39.08463320130167</v>
       </c>
       <c r="C24" t="n">
-        <v>39.07964572949704</v>
+        <v>39.07964572949705</v>
       </c>
       <c r="D24" t="n">
         <v>39.06949385934567</v>
@@ -7195,37 +7395,37 @@
         <v>39.03288735441907</v>
       </c>
       <c r="P24" t="n">
-        <v>39.02866162501729</v>
+        <v>39.02866162501731</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.48573310302963</v>
+        <v>39.48573310303056</v>
       </c>
       <c r="R24" t="n">
-        <v>39.40724225062327</v>
+        <v>39.40724225062366</v>
       </c>
       <c r="S24" t="n">
-        <v>39.24506615197573</v>
+        <v>39.24506615197581</v>
       </c>
       <c r="T24" t="n">
-        <v>39.07918307989169</v>
+        <v>39.07918307989156</v>
       </c>
       <c r="U24" t="n">
-        <v>38.99535613975106</v>
+        <v>38.99535613975084</v>
       </c>
       <c r="V24" t="n">
-        <v>38.99535613975106</v>
+        <v>38.99535613975084</v>
       </c>
       <c r="W24" t="n">
-        <v>38.99466406354201</v>
+        <v>38.99466406354178</v>
       </c>
       <c r="X24" t="n">
-        <v>38.99327671880717</v>
+        <v>38.99327671880695</v>
       </c>
       <c r="Y24" t="n">
-        <v>38.99188745809697</v>
+        <v>38.99188745809674</v>
       </c>
       <c r="Z24" t="n">
-        <v>38.99119252244584</v>
+        <v>38.99119252244562</v>
       </c>
     </row>
     <row r="25">
@@ -7233,79 +7433,79 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>39.08557478852185</v>
+        <v>39.08557478913144</v>
       </c>
       <c r="C25" t="n">
-        <v>39.08033042509086</v>
+        <v>39.08033042569596</v>
       </c>
       <c r="D25" t="n">
-        <v>39.06984325820077</v>
+        <v>39.06984325879953</v>
       </c>
       <c r="E25" t="n">
-        <v>39.05935479464997</v>
+        <v>39.05935479524498</v>
       </c>
       <c r="F25" t="n">
-        <v>39.05410953034801</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="G25" t="n">
-        <v>39.05410953034801</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="H25" t="n">
-        <v>39.04362455954149</v>
+        <v>39.0436245601332</v>
       </c>
       <c r="I25" t="n">
-        <v>39.02264925510062</v>
+        <v>39.02264925568884</v>
       </c>
       <c r="J25" t="n">
-        <v>39.00166274403362</v>
+        <v>39.00166274462025</v>
       </c>
       <c r="K25" t="n">
-        <v>38.99116385031392</v>
+        <v>38.9911638509007</v>
       </c>
       <c r="L25" t="n">
-        <v>39.05410953034801</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="M25" t="n">
-        <v>39.04988600379614</v>
+        <v>39.04988600439014</v>
       </c>
       <c r="N25" t="n">
-        <v>39.04143810851647</v>
+        <v>39.04143810910998</v>
       </c>
       <c r="O25" t="n">
-        <v>39.03298844569199</v>
+        <v>39.03298844628533</v>
       </c>
       <c r="P25" t="n">
-        <v>39.02876272722339</v>
+        <v>39.02876272781678</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.49877696882849</v>
+        <v>39.49877863180117</v>
       </c>
       <c r="R25" t="n">
-        <v>39.41532049492849</v>
+        <v>39.41532198056919</v>
       </c>
       <c r="S25" t="n">
-        <v>39.24826311565081</v>
+        <v>39.24826428376247</v>
       </c>
       <c r="T25" t="n">
-        <v>39.08057783557935</v>
+        <v>39.08057871387582</v>
       </c>
       <c r="U25" t="n">
-        <v>38.99639371494327</v>
+        <v>38.99639445855787</v>
       </c>
       <c r="V25" t="n">
-        <v>38.99639371494327</v>
+        <v>38.99639445855787</v>
       </c>
       <c r="W25" t="n">
-        <v>38.99569574387554</v>
+        <v>38.99569648525868</v>
       </c>
       <c r="X25" t="n">
-        <v>38.9943018656021</v>
+        <v>38.99430260402578</v>
       </c>
       <c r="Y25" t="n">
-        <v>38.99291001203667</v>
+        <v>38.99291074899607</v>
       </c>
       <c r="Z25" t="n">
-        <v>38.99221509432078</v>
+        <v>38.99221583129309</v>
       </c>
     </row>
     <row r="26">
@@ -7313,79 +7513,79 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>39.13089607074614</v>
+        <v>39.13089607071609</v>
       </c>
       <c r="C26" t="n">
-        <v>39.1228854800948</v>
+        <v>39.12288548007054</v>
       </c>
       <c r="D26" t="n">
-        <v>39.10708789980202</v>
+        <v>39.1070878997859</v>
       </c>
       <c r="E26" t="n">
-        <v>39.09148126277287</v>
+        <v>39.09148126276158</v>
       </c>
       <c r="F26" t="n">
-        <v>39.083759469176</v>
+        <v>39.08375946916552</v>
       </c>
       <c r="G26" t="n">
-        <v>39.083759469176</v>
+        <v>39.08375946916552</v>
       </c>
       <c r="H26" t="n">
-        <v>39.06828182802851</v>
+        <v>39.06828182802153</v>
       </c>
       <c r="I26" t="n">
-        <v>39.03741130519407</v>
+        <v>39.03741130519171</v>
       </c>
       <c r="J26" t="n">
-        <v>39.00657444152701</v>
+        <v>39.00657444152697</v>
       </c>
       <c r="K26" t="n">
-        <v>38.9911534886022</v>
+        <v>38.99115348860216</v>
       </c>
       <c r="L26" t="n">
-        <v>39.083759469176</v>
+        <v>39.08375946916552</v>
       </c>
       <c r="M26" t="n">
-        <v>39.07753730407824</v>
+        <v>39.07753730406834</v>
       </c>
       <c r="N26" t="n">
-        <v>39.0651086325241</v>
+        <v>39.06510863251498</v>
       </c>
       <c r="O26" t="n">
-        <v>39.05269110373912</v>
+        <v>39.05269110373037</v>
       </c>
       <c r="P26" t="n">
-        <v>39.04648664702636</v>
+        <v>39.04648664701762</v>
       </c>
       <c r="Q26" t="n">
-        <v>39.74417759694154</v>
+        <v>39.74417654597011</v>
       </c>
       <c r="R26" t="n">
-        <v>39.6169795256553</v>
+        <v>39.61697870367988</v>
       </c>
       <c r="S26" t="n">
-        <v>39.36815327775026</v>
+        <v>39.36815283833325</v>
       </c>
       <c r="T26" t="n">
-        <v>39.12153691434602</v>
+        <v>39.1215368088677</v>
       </c>
       <c r="U26" t="n">
-        <v>38.99809839655843</v>
+        <v>38.9980984441959</v>
       </c>
       <c r="V26" t="n">
-        <v>38.99809839655843</v>
+        <v>38.9980984441959</v>
       </c>
       <c r="W26" t="n">
-        <v>38.99707741023563</v>
+        <v>38.99707746039756</v>
       </c>
       <c r="X26" t="n">
-        <v>38.99503877152909</v>
+        <v>38.9950388250423</v>
       </c>
       <c r="Y26" t="n">
-        <v>38.9930018326842</v>
+        <v>38.99300188787003</v>
       </c>
       <c r="Z26" t="n">
-        <v>38.99198342308483</v>
+        <v>38.9919834782721</v>
       </c>
     </row>
   </sheetData>

--- a/Case_test/Inf_stage_demand/Inf_enmpc_felement=1.xlsx
+++ b/Case_test/Inf_stage_demand/Inf_enmpc_felement=1.xlsx
@@ -475,13 +475,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4.939400855208401e-06</v>
+        <v>4.939407291005563e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>2.694122792567683e-06</v>
+        <v>2.694125427426806e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>4.021534364853784e-06</v>
+        <v>4.021541092214071e-06</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01782624339494395</v>
+        <v>0.01782624335085341</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0139501753835496</v>
+        <v>0.01395017538426028</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003907486664976432</v>
+        <v>0.003907486620191116</v>
       </c>
     </row>
     <row r="5">
@@ -503,13 +503,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0292532529667745</v>
+        <v>0.02925325308596069</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02034992858999947</v>
+        <v>0.02034992857884681</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008937370263023858</v>
+        <v>0.008937370393272231</v>
       </c>
     </row>
     <row r="6">
@@ -517,13 +517,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0285769686128675</v>
+        <v>0.02857696852316583</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01613618630112499</v>
+        <v>0.01613618630855174</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01247513662821509</v>
+        <v>0.01247513653107836</v>
       </c>
     </row>
     <row r="7">
@@ -531,13 +531,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02907759109239278</v>
+        <v>0.02907759109940286</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01654194907887202</v>
+        <v>0.01654194907854966</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01256986179707925</v>
+        <v>0.01256986180441402</v>
       </c>
     </row>
     <row r="8">
@@ -545,13 +545,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03667138003628176</v>
+        <v>0.03667140777393112</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02034298771036722</v>
+        <v>0.02034297220853149</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01636176424886828</v>
+        <v>0.01636175701671995</v>
       </c>
     </row>
     <row r="9">
@@ -559,13 +559,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04402461690801041</v>
+        <v>0.04402461412236178</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02376076904636129</v>
+        <v>0.02376076944516655</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02029660102758298</v>
+        <v>0.02029659784204322</v>
       </c>
     </row>
     <row r="10">
@@ -573,13 +573,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.04301632778669995</v>
+        <v>0.04301632798111876</v>
       </c>
       <c r="C10" t="n">
-        <v>0.02329062322721109</v>
+        <v>0.02329062323249185</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01975843868299873</v>
+        <v>0.01975843885317516</v>
       </c>
     </row>
     <row r="11">
@@ -587,13 +587,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.03486618784407179</v>
+        <v>0.03486618795324366</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01947211556224638</v>
+        <v>0.01947211553945641</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01542740314217674</v>
+        <v>0.01542740327416942</v>
       </c>
     </row>
     <row r="12">
@@ -601,13 +601,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02824710674168528</v>
+        <v>0.02824710673035298</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01614400517291095</v>
+        <v>0.0161440051737188</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01213734307341489</v>
+        <v>0.01213734306127203</v>
       </c>
     </row>
     <row r="13">
@@ -615,13 +615,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.02906168510907547</v>
+        <v>0.02906168495784233</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01654279132075939</v>
+        <v>0.01654279133969924</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01255311017391241</v>
+        <v>0.0125531100006266</v>
       </c>
     </row>
     <row r="14">
@@ -629,13 +629,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.03667062225155579</v>
+        <v>0.03667062429916964</v>
       </c>
       <c r="C14" t="n">
-        <v>0.02034308742224072</v>
+        <v>0.02034308709692191</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01636085611108981</v>
+        <v>0.01636085848552927</v>
       </c>
     </row>
     <row r="15">
@@ -643,13 +643,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0440246706715061</v>
+        <v>0.04402466856115515</v>
       </c>
       <c r="C15" t="n">
-        <v>0.02376076845072252</v>
+        <v>0.02376076875265046</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02029665540605467</v>
+        <v>0.02029665299295267</v>
       </c>
     </row>
     <row r="16">
@@ -657,13 +657,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.04301633399013501</v>
+        <v>0.04301633422359434</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02329062261055726</v>
+        <v>0.02329062258948146</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01975844550543399</v>
+        <v>0.01975844576005695</v>
       </c>
     </row>
     <row r="17">
@@ -671,13 +671,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03486618764151404</v>
+        <v>0.03486618763614547</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01947211557386132</v>
+        <v>0.01947211557416258</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01542740292794057</v>
+        <v>0.01542740292226905</v>
       </c>
     </row>
     <row r="18">
@@ -685,13 +685,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.02824710674312599</v>
+        <v>0.0282471067431498</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01614400517285865</v>
+        <v>0.0161440051728581</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0121373430749081</v>
+        <v>0.01213734307493265</v>
       </c>
     </row>
     <row r="19">
@@ -699,13 +699,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02906168510907872</v>
+        <v>0.02906168510907975</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01654279132075881</v>
+        <v>0.01654279132075904</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0125531101739157</v>
+        <v>0.01255311017391713</v>
       </c>
     </row>
     <row r="20">
@@ -713,13 +713,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.03667062225167252</v>
+        <v>0.0366706222521568</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02034308742222165</v>
+        <v>0.02034308742214253</v>
       </c>
       <c r="D20" t="n">
-        <v>0.01636085611122597</v>
+        <v>0.01636085611178944</v>
       </c>
     </row>
     <row r="21">
@@ -727,13 +727,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.04402467067137451</v>
+        <v>0.04402467067083148</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02376076845074116</v>
+        <v>0.02376076845081956</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02029665540590363</v>
+        <v>0.02029665540528231</v>
       </c>
     </row>
     <row r="22">
@@ -741,13 +741,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.04301633399015023</v>
+        <v>0.04301633399021216</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02329062261055579</v>
+        <v>0.02329062261055005</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01975844550544987</v>
+        <v>0.01975844550551753</v>
       </c>
     </row>
     <row r="23">
@@ -755,13 +755,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.03486618764150994</v>
+        <v>0.03486618764152049</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01947211557386179</v>
+        <v>0.01947211557386016</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01542740292793579</v>
+        <v>0.01542740292794817</v>
       </c>
     </row>
     <row r="24">
@@ -769,13 +769,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.02824710674312825</v>
+        <v>0.02824710674311846</v>
       </c>
       <c r="C24" t="n">
-        <v>0.01614400517285853</v>
+        <v>0.01614400517285925</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01213734307491051</v>
+        <v>0.01213734307490019</v>
       </c>
     </row>
     <row r="25">
@@ -783,13 +783,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02906168510908101</v>
+        <v>0.02906168510908254</v>
       </c>
       <c r="C25" t="n">
-        <v>0.01654279132075865</v>
+        <v>0.0165427913207586</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01255311017391845</v>
+        <v>0.01255311017392026</v>
       </c>
     </row>
     <row r="26">
@@ -797,13 +797,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03667062225174106</v>
+        <v>0.03667062225236985</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02034308742221036</v>
+        <v>0.02034308742210779</v>
       </c>
       <c r="D26" t="n">
-        <v>0.01636085611130633</v>
+        <v>0.01636085611203727</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>118166.5321219524</v>
+        <v>38868.84653135894</v>
       </c>
     </row>
     <row r="3">
@@ -853,7 +853,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>107192.604394083</v>
+        <v>35291.76927307175</v>
       </c>
     </row>
     <row r="4">
@@ -861,7 +861,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>100533.8339551765</v>
+        <v>33095.30214380386</v>
       </c>
     </row>
     <row r="5">
@@ -869,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>95636.64913582048</v>
+        <v>31406.11714528872</v>
       </c>
     </row>
     <row r="6">
@@ -877,7 +877,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>94986.56383750282</v>
+        <v>30029.62855120484</v>
       </c>
     </row>
     <row r="7">
@@ -885,7 +885,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91157.92317556044</v>
+        <v>28884.85485728239</v>
       </c>
     </row>
     <row r="8">
@@ -893,7 +893,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87801.69847488271</v>
+        <v>27902.32599631726</v>
       </c>
     </row>
     <row r="9">
@@ -901,7 +901,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84771.53716838772</v>
+        <v>27902.30355155636</v>
       </c>
     </row>
     <row r="10">
@@ -909,7 +909,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82029.70766033765</v>
+        <v>27012.0611698217</v>
       </c>
     </row>
     <row r="11">
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79559.08325498675</v>
+        <v>26181.17274952676</v>
       </c>
     </row>
     <row r="12">
@@ -925,7 +925,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77313.45137201132</v>
+        <v>25040.77495123483</v>
       </c>
     </row>
     <row r="13">
@@ -933,7 +933,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75010.4840989674</v>
+        <v>25040.5959503058</v>
       </c>
     </row>
     <row r="14">
@@ -941,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>73062.00093162405</v>
+        <v>24378.98017354792</v>
       </c>
     </row>
     <row r="15">
@@ -949,7 +949,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>71205.77097091815</v>
+        <v>23763.18743610133</v>
       </c>
     </row>
     <row r="16">
@@ -957,7 +957,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>69446.18490116032</v>
+        <v>23175.75099040103</v>
       </c>
     </row>
     <row r="17">
@@ -965,7 +965,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>67793.50747332913</v>
+        <v>22609.11651579446</v>
       </c>
     </row>
     <row r="18">
@@ -973,7 +973,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>66239.88850735745</v>
+        <v>22068.68947963005</v>
       </c>
     </row>
     <row r="19">
@@ -981,7 +981,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>64763.9507526187</v>
+        <v>21561.87939847753</v>
       </c>
     </row>
     <row r="20">
@@ -989,7 +989,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>63344.30956067113</v>
+        <v>21087.06409401033</v>
       </c>
     </row>
     <row r="21">
@@ -997,7 +997,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>61970.57693939324</v>
+        <v>20636.0303171699</v>
       </c>
     </row>
     <row r="22">
@@ -1005,7 +1005,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>60647.86528718892</v>
+        <v>20199.11446256928</v>
       </c>
     </row>
     <row r="23">
@@ -1013,7 +1013,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>59385.71217463879</v>
+        <v>19771.87027183147</v>
       </c>
     </row>
     <row r="24">
@@ -1021,7 +1021,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>58182.54597154722</v>
+        <v>19358.77272668794</v>
       </c>
     </row>
     <row r="25">
@@ -1029,7 +1029,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>57026.74865105037</v>
+        <v>18965.91074047688</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5813748380169272</v>
+        <v>0.5002478491514921</v>
       </c>
     </row>
     <row r="3">
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9663050062954426</v>
+        <v>0.8386831982061267</v>
       </c>
     </row>
     <row r="4">
@@ -1079,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7209113463759422</v>
+        <v>1.405047778040171</v>
       </c>
     </row>
     <row r="5">
@@ -1087,7 +1087,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9389876835048199</v>
+        <v>0.9717401880770922</v>
       </c>
     </row>
     <row r="6">
@@ -1095,7 +1095,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8679094547405839</v>
+        <v>1.527405771426857</v>
       </c>
     </row>
     <row r="7">
@@ -1103,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7579735545441508</v>
+        <v>0.7412898195907474</v>
       </c>
     </row>
     <row r="8">
@@ -1111,7 +1111,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9203162845224142</v>
+        <v>1.830027002841234</v>
       </c>
     </row>
     <row r="9">
@@ -1119,7 +1119,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.87995117623359</v>
+        <v>1.350727756507695</v>
       </c>
     </row>
     <row r="10">
@@ -1127,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8286430733278394</v>
+        <v>0.6738549983128905</v>
       </c>
     </row>
     <row r="11">
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.9461590917780995</v>
+        <v>1.136113326996565</v>
       </c>
     </row>
     <row r="12">
@@ -1143,7 +1143,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.068875886499882</v>
+        <v>1.640664910897613</v>
       </c>
     </row>
     <row r="13">
@@ -1151,7 +1151,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7687814338132739</v>
+        <v>1.657390104606748</v>
       </c>
     </row>
     <row r="14">
@@ -1159,7 +1159,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8457668870687485</v>
+        <v>2.654911906458437</v>
       </c>
     </row>
     <row r="15">
@@ -1167,7 +1167,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8223119927570224</v>
+        <v>0.8686239458620548</v>
       </c>
     </row>
     <row r="16">
@@ -1175,7 +1175,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7812387645244598</v>
+        <v>0.6372238006442785</v>
       </c>
     </row>
     <row r="17">
@@ -1183,7 +1183,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8863522615283728</v>
+        <v>0.9827764611691236</v>
       </c>
     </row>
     <row r="18">
@@ -1191,7 +1191,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.475935145281255</v>
+        <v>1.36559977196157</v>
       </c>
     </row>
     <row r="19">
@@ -1199,7 +1199,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6925724791362882</v>
+        <v>0.6763963680714369</v>
       </c>
     </row>
     <row r="20">
@@ -1207,7 +1207,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8549786824733019</v>
+        <v>0.9722266383469105</v>
       </c>
     </row>
     <row r="21">
@@ -1215,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.239589654840529</v>
+        <v>1.012898520566523</v>
       </c>
     </row>
     <row r="22">
@@ -1223,7 +1223,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.67268808465451</v>
+        <v>0.6969631034880877</v>
       </c>
     </row>
     <row r="23">
@@ -1231,7 +1231,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9418226107954979</v>
+        <v>1.092742778360844</v>
       </c>
     </row>
     <row r="24">
@@ -1239,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1.554223558865488</v>
+        <v>0.8864269694313407</v>
       </c>
     </row>
     <row r="25">
@@ -1247,7 +1247,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.8701225994154811</v>
+        <v>0.61289091873914</v>
       </c>
     </row>
     <row r="26">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41.20404577255249</v>
+        <v>57.04349637031555</v>
       </c>
     </row>
   </sheetData>
@@ -1310,13 +1310,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.082506901217855</v>
+        <v>1.08250689733715</v>
       </c>
       <c r="C3" t="n">
-        <v>1.108714763646543</v>
+        <v>1.108714767625651</v>
       </c>
       <c r="D3" t="n">
-        <v>1.116647949430622</v>
+        <v>1.116647953444024</v>
       </c>
     </row>
     <row r="4">
@@ -1324,13 +1324,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.085172428532646</v>
+        <v>1.085172428516152</v>
       </c>
       <c r="C4" t="n">
-        <v>1.083525137789854</v>
+        <v>1.083525137806376</v>
       </c>
       <c r="D4" t="n">
-        <v>1.092446770289794</v>
+        <v>1.092446770215883</v>
       </c>
     </row>
     <row r="5">
@@ -1338,13 +1338,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.084894281094971</v>
+        <v>1.084894281142192</v>
       </c>
       <c r="C5" t="n">
-        <v>1.083521583961463</v>
+        <v>1.083521583914301</v>
       </c>
       <c r="D5" t="n">
-        <v>1.088555325814936</v>
+        <v>1.088555326045306</v>
       </c>
     </row>
     <row r="6">
@@ -1352,13 +1352,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.085780207383593</v>
+        <v>1.085780207344918</v>
       </c>
       <c r="C6" t="n">
-        <v>1.081409670694627</v>
+        <v>1.081409670733147</v>
       </c>
       <c r="D6" t="n">
-        <v>1.092462611383728</v>
+        <v>1.092462611275737</v>
       </c>
     </row>
     <row r="7">
@@ -1366,13 +1366,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.085844199019021</v>
+        <v>1.085844199020658</v>
       </c>
       <c r="C7" t="n">
-        <v>1.081372063100127</v>
+        <v>1.081372063098497</v>
       </c>
       <c r="D7" t="n">
-        <v>1.092817004458691</v>
+        <v>1.092817004461386</v>
       </c>
     </row>
     <row r="8">
@@ -1380,13 +1380,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.087581624665223</v>
+        <v>1.087581688429906</v>
       </c>
       <c r="C8" t="n">
-        <v>1.080896448070517</v>
+        <v>1.080896384699891</v>
       </c>
       <c r="D8" t="n">
-        <v>1.097838798674772</v>
+        <v>1.097838741458808</v>
       </c>
     </row>
     <row r="9">
@@ -1394,13 +1394,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.089561973952372</v>
+        <v>1.08956197255047</v>
       </c>
       <c r="C9" t="n">
-        <v>1.08039374902051</v>
+        <v>1.080393750410494</v>
       </c>
       <c r="D9" t="n">
-        <v>1.103557876746293</v>
+        <v>1.103557872783637</v>
       </c>
     </row>
     <row r="10">
@@ -1408,13 +1408,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.089446738510624</v>
+        <v>1.089446738544195</v>
       </c>
       <c r="C10" t="n">
-        <v>1.080463211875158</v>
+        <v>1.08046321186269</v>
       </c>
       <c r="D10" t="n">
-        <v>1.10320336477201</v>
+        <v>1.103203364642551</v>
       </c>
     </row>
     <row r="11">
@@ -1422,13 +1422,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.087382871015311</v>
+        <v>1.087382871073438</v>
       </c>
       <c r="C11" t="n">
-        <v>1.081024364288227</v>
+        <v>1.081024364229445</v>
       </c>
       <c r="D11" t="n">
-        <v>1.097228972669168</v>
+        <v>1.097228972832564</v>
       </c>
     </row>
     <row r="12">
@@ -1436,13 +1436,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.085751058786831</v>
+        <v>1.085751058783809</v>
       </c>
       <c r="C12" t="n">
-        <v>1.081438774618908</v>
+        <v>1.08143877462193</v>
       </c>
       <c r="D12" t="n">
-        <v>1.092536869974566</v>
+        <v>1.092536869968841</v>
       </c>
     </row>
     <row r="13">
@@ -1450,13 +1450,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.085839895625834</v>
+        <v>1.085839895529286</v>
       </c>
       <c r="C13" t="n">
-        <v>1.081376348661052</v>
+        <v>1.081376348757089</v>
       </c>
       <c r="D13" t="n">
-        <v>1.092808414456462</v>
+        <v>1.092808414117296</v>
       </c>
     </row>
     <row r="14">
@@ -1464,13 +1464,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.087581214578248</v>
+        <v>1.087581215917072</v>
       </c>
       <c r="C14" t="n">
-        <v>1.080896855639131</v>
+        <v>1.080896854308752</v>
       </c>
       <c r="D14" t="n">
-        <v>1.097837253224714</v>
+        <v>1.097837257556208</v>
       </c>
     </row>
     <row r="15">
@@ -1478,13 +1478,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.089561976037969</v>
+        <v>1.089561974978792</v>
       </c>
       <c r="C15" t="n">
-        <v>1.080393746952347</v>
+        <v>1.080393748002598</v>
       </c>
       <c r="D15" t="n">
-        <v>1.103557843173295</v>
+        <v>1.103557840184694</v>
       </c>
     </row>
     <row r="16">
@@ -1492,13 +1492,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.089446740718507</v>
+        <v>1.089446740793976</v>
       </c>
       <c r="C16" t="n">
-        <v>1.080463209685483</v>
+        <v>1.080463209610637</v>
       </c>
       <c r="D16" t="n">
-        <v>1.103203369534604</v>
+        <v>1.103203369680233</v>
       </c>
     </row>
     <row r="17">
@@ -1506,13 +1506,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.087382870965333</v>
+        <v>1.087382870964037</v>
       </c>
       <c r="C17" t="n">
-        <v>1.081024364337912</v>
+        <v>1.081024364339201</v>
       </c>
       <c r="D17" t="n">
-        <v>1.097228972597122</v>
+        <v>1.097228972595335</v>
       </c>
     </row>
     <row r="18">
@@ -1520,13 +1520,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.085751058787103</v>
+        <v>1.085751058787106</v>
       </c>
       <c r="C18" t="n">
-        <v>1.081438774618638</v>
+        <v>1.081438774618635</v>
       </c>
       <c r="D18" t="n">
-        <v>1.092536869974847</v>
+        <v>1.092536869974844</v>
       </c>
     </row>
     <row r="19">
@@ -1540,7 +1540,7 @@
         <v>1.081376348661049</v>
       </c>
       <c r="D19" t="n">
-        <v>1.092808414456468</v>
+        <v>1.092808414456471</v>
       </c>
     </row>
     <row r="20">
@@ -1548,13 +1548,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.087581214578326</v>
+        <v>1.087581214578651</v>
       </c>
       <c r="C20" t="n">
-        <v>1.080896855639052</v>
+        <v>1.080896855638729</v>
       </c>
       <c r="D20" t="n">
-        <v>1.097837253224971</v>
+        <v>1.09783725322603</v>
       </c>
     </row>
     <row r="21">
@@ -1562,13 +1562,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.089561976037903</v>
+        <v>1.089561976037629</v>
       </c>
       <c r="C21" t="n">
-        <v>1.080393746952411</v>
+        <v>1.080393746952683</v>
       </c>
       <c r="D21" t="n">
-        <v>1.103557843173107</v>
+        <v>1.103557843172333</v>
       </c>
     </row>
     <row r="22">
@@ -1576,13 +1576,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.089446740718513</v>
+        <v>1.089446740718534</v>
       </c>
       <c r="C22" t="n">
-        <v>1.080463209685477</v>
+        <v>1.080463209685457</v>
       </c>
       <c r="D22" t="n">
-        <v>1.103203369534613</v>
+        <v>1.103203369534653</v>
       </c>
     </row>
     <row r="23">
@@ -1590,13 +1590,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1.087382870965331</v>
+        <v>1.087382870965338</v>
       </c>
       <c r="C23" t="n">
-        <v>1.081024364337914</v>
+        <v>1.081024364337907</v>
       </c>
       <c r="D23" t="n">
-        <v>1.097228972597113</v>
+        <v>1.097228972597139</v>
       </c>
     </row>
     <row r="24">
@@ -1604,13 +1604,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>1.085751058787104</v>
+        <v>1.0857510587871</v>
       </c>
       <c r="C24" t="n">
-        <v>1.081438774618637</v>
+        <v>1.081438774618641</v>
       </c>
       <c r="D24" t="n">
-        <v>1.092536869974849</v>
+        <v>1.092536869974839</v>
       </c>
     </row>
     <row r="25">
@@ -1618,13 +1618,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>1.085839895625837</v>
+        <v>1.085839895625838</v>
       </c>
       <c r="C25" t="n">
-        <v>1.081376348661048</v>
+        <v>1.081376348661047</v>
       </c>
       <c r="D25" t="n">
-        <v>1.092808414456473</v>
+        <v>1.092808414456477</v>
       </c>
     </row>
     <row r="26">
@@ -1632,13 +1632,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1.087581214578372</v>
+        <v>1.087581214578794</v>
       </c>
       <c r="C26" t="n">
-        <v>1.080896855639007</v>
+        <v>1.080896855638587</v>
       </c>
       <c r="D26" t="n">
-        <v>1.097837253225124</v>
+        <v>1.097837253226497</v>
       </c>
     </row>
   </sheetData>
@@ -2248,19 +2248,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>42.00577081088423</v>
+        <v>42.00577081105108</v>
       </c>
       <c r="C3" t="n">
-        <v>41.91135576159457</v>
+        <v>41.91135576175919</v>
       </c>
       <c r="D3" t="n">
-        <v>41.95935348617113</v>
+        <v>41.95935348633766</v>
       </c>
       <c r="E3" t="n">
-        <v>42.30342051743694</v>
+        <v>42.30342051776375</v>
       </c>
       <c r="F3" t="n">
-        <v>42.30178083985014</v>
+        <v>42.30178084017567</v>
       </c>
     </row>
     <row r="4">
@@ -2268,19 +2268,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.1298198478313</v>
+        <v>41.12981984783108</v>
       </c>
       <c r="C4" t="n">
-        <v>41.01331604301953</v>
+        <v>41.01331604302236</v>
       </c>
       <c r="D4" t="n">
-        <v>41.0787122476073</v>
+        <v>41.07871224760763</v>
       </c>
       <c r="E4" t="n">
-        <v>41.4196300062613</v>
+        <v>41.41963000405966</v>
       </c>
       <c r="F4" t="n">
-        <v>41.41728895209967</v>
+        <v>41.41728894990716</v>
       </c>
     </row>
     <row r="5">
@@ -2288,19 +2288,19 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.11032497234608</v>
+        <v>41.11032497234604</v>
       </c>
       <c r="C5" t="n">
         <v>41.01329245800957</v>
       </c>
       <c r="D5" t="n">
-        <v>41.07122015090437</v>
+        <v>41.07122015090433</v>
       </c>
       <c r="E5" t="n">
-        <v>41.0332076338772</v>
+        <v>41.03320763816882</v>
       </c>
       <c r="F5" t="n">
-        <v>41.03004840510501</v>
+        <v>41.03004840935925</v>
       </c>
     </row>
     <row r="6">
@@ -2314,13 +2314,13 @@
         <v>41.01330469292704</v>
       </c>
       <c r="D6" t="n">
-        <v>41.05274877101983</v>
+        <v>41.05274877101982</v>
       </c>
       <c r="E6" t="n">
-        <v>41.01756522469758</v>
+        <v>41.01756522466253</v>
       </c>
       <c r="F6" t="n">
-        <v>41.01333150885741</v>
+        <v>41.01333150886015</v>
       </c>
     </row>
     <row r="7">
@@ -2328,19 +2328,19 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.07951643026905</v>
+        <v>41.07951643026907</v>
       </c>
       <c r="C7" t="n">
         <v>41.01330628944115</v>
       </c>
       <c r="D7" t="n">
-        <v>41.05285510251809</v>
+        <v>41.0528551025181</v>
       </c>
       <c r="E7" t="n">
-        <v>41.01874893047633</v>
+        <v>41.01874893045289</v>
       </c>
       <c r="F7" t="n">
-        <v>41.01435387686005</v>
+        <v>41.01435387683679</v>
       </c>
     </row>
     <row r="8">
@@ -2348,19 +2348,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41.11070406027971</v>
+        <v>41.11070406035739</v>
       </c>
       <c r="C8" t="n">
-        <v>41.01329538944848</v>
+        <v>41.01329538952498</v>
       </c>
       <c r="D8" t="n">
-        <v>41.07149821156884</v>
+        <v>41.07149821164637</v>
       </c>
       <c r="E8" t="n">
-        <v>41.02059774185243</v>
+        <v>41.02059785050383</v>
       </c>
       <c r="F8" t="n">
-        <v>41.01416502940393</v>
+        <v>41.01416513688459</v>
       </c>
     </row>
     <row r="9">
@@ -2368,19 +2368,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41.14768492507029</v>
+        <v>41.14768492506869</v>
       </c>
       <c r="C9" t="n">
-        <v>41.01328659544366</v>
+        <v>41.01328659544365</v>
       </c>
       <c r="D9" t="n">
-        <v>41.09360217422266</v>
+        <v>41.09360217422132</v>
       </c>
       <c r="E9" t="n">
-        <v>41.02216684353032</v>
+        <v>41.02216684217838</v>
       </c>
       <c r="F9" t="n">
-        <v>41.01330718340842</v>
+        <v>41.01330718345252</v>
       </c>
     </row>
     <row r="10">
@@ -2388,19 +2388,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41.14741387467972</v>
+        <v>41.14741387544662</v>
       </c>
       <c r="C10" t="n">
-        <v>41.01328578105444</v>
+        <v>41.01328578180814</v>
       </c>
       <c r="D10" t="n">
-        <v>41.09342352677695</v>
+        <v>41.09342352754227</v>
       </c>
       <c r="E10" t="n">
-        <v>41.02214144322139</v>
+        <v>41.02214143779332</v>
       </c>
       <c r="F10" t="n">
-        <v>41.01328205989962</v>
+        <v>41.01328205453785</v>
       </c>
     </row>
     <row r="11">
@@ -2408,19 +2408,19 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41.11027915596995</v>
+        <v>41.1102791559566</v>
       </c>
       <c r="C11" t="n">
-        <v>41.01329314634554</v>
+        <v>41.01329314634555</v>
       </c>
       <c r="D11" t="n">
-        <v>41.07121768367048</v>
+        <v>41.07121768365936</v>
       </c>
       <c r="E11" t="n">
-        <v>41.01970633992908</v>
+        <v>41.01970633998786</v>
       </c>
       <c r="F11" t="n">
-        <v>41.01328868154356</v>
+        <v>41.01328868154312</v>
       </c>
     </row>
     <row r="12">
@@ -2428,19 +2428,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>41.07935584812449</v>
+        <v>41.07935584812451</v>
       </c>
       <c r="C12" t="n">
-        <v>41.01330468456637</v>
+        <v>41.01330468456636</v>
       </c>
       <c r="D12" t="n">
-        <v>41.0527487562622</v>
+        <v>41.05274875626218</v>
       </c>
       <c r="E12" t="n">
-        <v>41.01771599669743</v>
+        <v>41.01771599669769</v>
       </c>
       <c r="F12" t="n">
-        <v>41.01333644771902</v>
+        <v>41.01333644771936</v>
       </c>
     </row>
     <row r="13">
@@ -2448,19 +2448,19 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41.07951643019253</v>
+        <v>41.07951643018833</v>
       </c>
       <c r="C13" t="n">
-        <v>41.01330628922302</v>
+        <v>41.01330628921887</v>
       </c>
       <c r="D13" t="n">
-        <v>41.05285510241018</v>
+        <v>41.05285510240599</v>
       </c>
       <c r="E13" t="n">
-        <v>41.01880816433339</v>
+        <v>41.01880815691384</v>
       </c>
       <c r="F13" t="n">
-        <v>41.01441282695558</v>
+        <v>41.01441281960232</v>
       </c>
     </row>
     <row r="14">
@@ -2468,19 +2468,19 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>41.1107040603554</v>
+        <v>41.1107040603633</v>
       </c>
       <c r="C14" t="n">
-        <v>41.01329538951955</v>
+        <v>41.01329538952726</v>
       </c>
       <c r="D14" t="n">
-        <v>41.07149821164409</v>
+        <v>41.07149821165196</v>
       </c>
       <c r="E14" t="n">
-        <v>41.0206005213104</v>
+        <v>41.02060060301999</v>
       </c>
       <c r="F14" t="n">
-        <v>41.01416842373731</v>
+        <v>41.01416850448623</v>
       </c>
     </row>
     <row r="15">
@@ -2488,19 +2488,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41.14768492506882</v>
+        <v>41.14768492506865</v>
       </c>
       <c r="C15" t="n">
-        <v>41.01328659544368</v>
+        <v>41.01328659544366</v>
       </c>
       <c r="D15" t="n">
-        <v>41.09360217422145</v>
+        <v>41.0936021742213</v>
       </c>
       <c r="E15" t="n">
-        <v>41.0221668003448</v>
+        <v>41.02216679932913</v>
       </c>
       <c r="F15" t="n">
-        <v>41.01330718308503</v>
+        <v>41.01330718311836</v>
       </c>
     </row>
     <row r="16">
@@ -2508,19 +2508,19 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41.14741387467976</v>
+        <v>41.14741387467975</v>
       </c>
       <c r="C16" t="n">
         <v>41.01328578105448</v>
       </c>
       <c r="D16" t="n">
-        <v>41.09342352677697</v>
+        <v>41.09342352677696</v>
       </c>
       <c r="E16" t="n">
-        <v>41.02214144328415</v>
+        <v>41.0221414432848</v>
       </c>
       <c r="F16" t="n">
-        <v>41.01328205987468</v>
+        <v>41.01328205987377</v>
       </c>
     </row>
     <row r="17">
@@ -2528,19 +2528,19 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>41.11027915596994</v>
+        <v>41.11027915596993</v>
       </c>
       <c r="C17" t="n">
-        <v>41.01329314634553</v>
+        <v>41.01329314634554</v>
       </c>
       <c r="D17" t="n">
         <v>41.07121768367048</v>
       </c>
       <c r="E17" t="n">
-        <v>41.01970633993006</v>
+        <v>41.01970633993057</v>
       </c>
       <c r="F17" t="n">
-        <v>41.01328868154429</v>
+        <v>41.01328868154477</v>
       </c>
     </row>
     <row r="18">
@@ -2548,19 +2548,19 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41.07935584812449</v>
+        <v>41.07935584812447</v>
       </c>
       <c r="C18" t="n">
         <v>41.01330468456636</v>
       </c>
       <c r="D18" t="n">
-        <v>41.05274875626219</v>
+        <v>41.05274875626218</v>
       </c>
       <c r="E18" t="n">
-        <v>41.01771599669734</v>
+        <v>41.0177159966974</v>
       </c>
       <c r="F18" t="n">
-        <v>41.01333644771893</v>
+        <v>41.01333644771899</v>
       </c>
     </row>
     <row r="19">
@@ -2568,19 +2568,19 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41.07951643019253</v>
+        <v>41.07951643019254</v>
       </c>
       <c r="C19" t="n">
         <v>41.01330628922302</v>
       </c>
       <c r="D19" t="n">
-        <v>41.05285510241018</v>
+        <v>41.05285510241019</v>
       </c>
       <c r="E19" t="n">
-        <v>41.01880816433347</v>
+        <v>41.01880816433355</v>
       </c>
       <c r="F19" t="n">
-        <v>41.01441282695566</v>
+        <v>41.01441282695574</v>
       </c>
     </row>
     <row r="20">
@@ -2588,19 +2588,19 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>41.11070406035539</v>
+        <v>41.11070406035538</v>
       </c>
       <c r="C20" t="n">
-        <v>41.01329538951955</v>
+        <v>41.01329538951953</v>
       </c>
       <c r="D20" t="n">
-        <v>41.07149821164409</v>
+        <v>41.07149821164408</v>
       </c>
       <c r="E20" t="n">
-        <v>41.02060052131556</v>
+        <v>41.02060052133669</v>
       </c>
       <c r="F20" t="n">
-        <v>41.0141684237424</v>
+        <v>41.01416842376331</v>
       </c>
     </row>
     <row r="21">
@@ -2617,10 +2617,10 @@
         <v>41.09360217422145</v>
       </c>
       <c r="E21" t="n">
-        <v>41.02216680034475</v>
+        <v>41.02216680034441</v>
       </c>
       <c r="F21" t="n">
-        <v>41.01330718308504</v>
+        <v>41.01330718308498</v>
       </c>
     </row>
     <row r="22">
@@ -2628,19 +2628,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>41.14741387467976</v>
+        <v>41.14741387467974</v>
       </c>
       <c r="C22" t="n">
-        <v>41.01328578105448</v>
+        <v>41.01328578105447</v>
       </c>
       <c r="D22" t="n">
-        <v>41.09342352677698</v>
+        <v>41.09342352677697</v>
       </c>
       <c r="E22" t="n">
-        <v>41.02214144328416</v>
+        <v>41.02214144328415</v>
       </c>
       <c r="F22" t="n">
-        <v>41.01328205987469</v>
+        <v>41.01328205987468</v>
       </c>
     </row>
     <row r="23">
@@ -2657,10 +2657,10 @@
         <v>41.07121768367048</v>
       </c>
       <c r="E23" t="n">
-        <v>41.0197063399299</v>
+        <v>41.01970633993042</v>
       </c>
       <c r="F23" t="n">
-        <v>41.01328868154413</v>
+        <v>41.01328868154465</v>
       </c>
     </row>
     <row r="24">
@@ -2668,19 +2668,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>41.07935584812449</v>
+        <v>41.07935584812448</v>
       </c>
       <c r="C24" t="n">
-        <v>41.01330468456637</v>
+        <v>41.01330468456636</v>
       </c>
       <c r="D24" t="n">
-        <v>41.0527487562622</v>
+        <v>41.05274875626218</v>
       </c>
       <c r="E24" t="n">
-        <v>41.01771599669728</v>
+        <v>41.01771599669735</v>
       </c>
       <c r="F24" t="n">
-        <v>41.01333644771887</v>
+        <v>41.01333644771894</v>
       </c>
     </row>
     <row r="25">
@@ -2688,19 +2688,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>41.07951643019254</v>
+        <v>41.07951643019253</v>
       </c>
       <c r="C25" t="n">
         <v>41.01330628922302</v>
       </c>
       <c r="D25" t="n">
-        <v>41.05285510241019</v>
+        <v>41.05285510241018</v>
       </c>
       <c r="E25" t="n">
-        <v>41.01880816433355</v>
+        <v>41.01880816433365</v>
       </c>
       <c r="F25" t="n">
-        <v>41.01441282695573</v>
+        <v>41.01441282695584</v>
       </c>
     </row>
     <row r="26">
@@ -2708,19 +2708,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>41.1107040603554</v>
+        <v>41.11070406035538</v>
       </c>
       <c r="C26" t="n">
-        <v>41.01329538951954</v>
+        <v>41.01329538951953</v>
       </c>
       <c r="D26" t="n">
-        <v>41.07149821164409</v>
+        <v>41.07149821164408</v>
       </c>
       <c r="E26" t="n">
-        <v>41.02060052131865</v>
+        <v>41.02060052134606</v>
       </c>
       <c r="F26" t="n">
-        <v>41.01416842374546</v>
+        <v>41.01416842377257</v>
       </c>
     </row>
   </sheetData>
@@ -2829,34 +2829,34 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>37.25055143791961</v>
+        <v>37.25055144550893</v>
       </c>
       <c r="C3" t="n">
-        <v>74.25037185571284</v>
+        <v>74.25037186028163</v>
       </c>
       <c r="D3" t="n">
-        <v>34.30632890561256</v>
+        <v>34.30632890635194</v>
       </c>
       <c r="E3" t="n">
-        <v>38.88529911202312</v>
+        <v>38.88529911239222</v>
       </c>
       <c r="F3" t="n">
-        <v>39.76249191205618</v>
+        <v>39.76249191235717</v>
       </c>
       <c r="G3" t="n">
-        <v>41.6169478457869</v>
+        <v>41.61694784593736</v>
       </c>
       <c r="H3" t="n">
-        <v>7.462855573430432</v>
+        <v>7.462855597448564</v>
       </c>
       <c r="I3" t="n">
-        <v>13.83019949601609</v>
+        <v>13.83019951835453</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.693304777724028</v>
+        <v>-1.693304763870811</v>
       </c>
       <c r="K3" t="n">
-        <v>20.90526651885144</v>
+        <v>20.90526652577336</v>
       </c>
     </row>
     <row r="4">
@@ -2864,34 +2864,34 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>90.73471205061495</v>
+        <v>90.73471204299881</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3216312105566</v>
+        <v>106.3216312059925</v>
       </c>
       <c r="D4" t="n">
-        <v>39.46045107921293</v>
+        <v>39.46045107848461</v>
       </c>
       <c r="E4" t="n">
-        <v>41.46137922892487</v>
+        <v>41.46137922856211</v>
       </c>
       <c r="F4" t="n">
-        <v>41.88477201494423</v>
+        <v>41.88477201464369</v>
       </c>
       <c r="G4" t="n">
-        <v>42.67934452450825</v>
+        <v>42.67934452435806</v>
       </c>
       <c r="H4" t="n">
-        <v>22.82152747052476</v>
+        <v>22.82152728261784</v>
       </c>
       <c r="I4" t="n">
-        <v>26.62577622512355</v>
+        <v>26.62577605177247</v>
       </c>
       <c r="J4" t="n">
-        <v>5.865451095280497</v>
+        <v>5.865450988099212</v>
       </c>
       <c r="K4" t="n">
-        <v>24.66726867384637</v>
+        <v>24.66726862030316</v>
       </c>
     </row>
     <row r="5">
@@ -2899,34 +2899,34 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>110.1314989559164</v>
+        <v>110.1314989559412</v>
       </c>
       <c r="C5" t="n">
-        <v>110.4914168971747</v>
+        <v>110.4914168971688</v>
       </c>
       <c r="D5" t="n">
-        <v>36.95360596465075</v>
+        <v>36.95360596463968</v>
       </c>
       <c r="E5" t="n">
-        <v>36.98610841500082</v>
+        <v>36.9861084149945</v>
       </c>
       <c r="F5" t="n">
-        <v>36.97807806028067</v>
+        <v>36.97807806028014</v>
       </c>
       <c r="G5" t="n">
-        <v>36.99098739634297</v>
+        <v>36.99098739634264</v>
       </c>
       <c r="H5" t="n">
-        <v>46.47880173806641</v>
+        <v>46.47880223043003</v>
       </c>
       <c r="I5" t="n">
-        <v>47.72161888530924</v>
+        <v>47.7216193322019</v>
       </c>
       <c r="J5" t="n">
-        <v>20.52171863764992</v>
+        <v>20.52171891216044</v>
       </c>
       <c r="K5" t="n">
-        <v>28.75715175508025</v>
+        <v>28.75715189216364</v>
       </c>
     </row>
     <row r="6">
@@ -2934,34 +2934,34 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>90.1030103232589</v>
+        <v>90.10301032326095</v>
       </c>
       <c r="C6" t="n">
-        <v>90.80009356614275</v>
+        <v>90.80009356614413</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47864266253792</v>
+        <v>30.47864266253798</v>
       </c>
       <c r="E6" t="n">
-        <v>30.51341244551946</v>
+        <v>30.51341244551947</v>
       </c>
       <c r="F6" t="n">
-        <v>30.48408947637567</v>
+        <v>30.48408947637574</v>
       </c>
       <c r="G6" t="n">
-        <v>30.5064266784589</v>
+        <v>30.50642667845894</v>
       </c>
       <c r="H6" t="n">
-        <v>60.37189164392185</v>
+        <v>60.37189130001899</v>
       </c>
       <c r="I6" t="n">
-        <v>60.03690118564934</v>
+        <v>60.03690088558579</v>
       </c>
       <c r="J6" t="n">
-        <v>29.8023417217814</v>
+        <v>29.80234154053469</v>
       </c>
       <c r="K6" t="n">
-        <v>30.16229514003503</v>
+        <v>30.16229504963099</v>
       </c>
     </row>
     <row r="7">
@@ -2969,34 +2969,34 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91.58544321362238</v>
+        <v>91.58544321362248</v>
       </c>
       <c r="C7" t="n">
         <v>91.57882607308026</v>
       </c>
       <c r="D7" t="n">
-        <v>30.52504472409668</v>
+        <v>30.5250447240967</v>
       </c>
       <c r="E7" t="n">
-        <v>30.52500358071557</v>
+        <v>30.52500358071559</v>
       </c>
       <c r="F7" t="n">
-        <v>30.52520195442339</v>
+        <v>30.5252019544234</v>
       </c>
       <c r="G7" t="n">
-        <v>30.52509608025694</v>
+        <v>30.52509608025695</v>
       </c>
       <c r="H7" t="n">
-        <v>61.18631241131764</v>
+        <v>61.18631242508912</v>
       </c>
       <c r="I7" t="n">
-        <v>61.13823618412264</v>
+        <v>61.13823618670006</v>
       </c>
       <c r="J7" t="n">
-        <v>30.56925145962059</v>
+        <v>30.56925145869391</v>
       </c>
       <c r="K7" t="n">
-        <v>30.54673987694646</v>
+        <v>30.54673987639372</v>
       </c>
     </row>
     <row r="8">
@@ -3004,34 +3004,34 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112.4849285757944</v>
+        <v>112.4849285793302</v>
       </c>
       <c r="C8" t="n">
-        <v>111.7800974037958</v>
+        <v>111.7800974059219</v>
       </c>
       <c r="D8" t="n">
-        <v>37.04642580897113</v>
+        <v>37.04642580931473</v>
       </c>
       <c r="E8" t="n">
-        <v>37.01159054767197</v>
+        <v>37.0115905478435</v>
       </c>
       <c r="F8" t="n">
-        <v>37.04122864310875</v>
+        <v>37.04122864324885</v>
       </c>
       <c r="G8" t="n">
-        <v>37.01872848187251</v>
+        <v>37.01872848194255</v>
       </c>
       <c r="H8" t="n">
-        <v>74.81436497211885</v>
+        <v>74.81437327270591</v>
       </c>
       <c r="I8" t="n">
-        <v>74.24705226833126</v>
+        <v>74.24705974375372</v>
       </c>
       <c r="J8" t="n">
-        <v>37.02087379024079</v>
+        <v>37.02087836766274</v>
       </c>
       <c r="K8" t="n">
-        <v>37.00321989353031</v>
+        <v>37.00322217950015</v>
       </c>
     </row>
     <row r="9">
@@ -3039,34 +3039,34 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132.1828816433474</v>
+        <v>132.1828816397277</v>
       </c>
       <c r="C9" t="n">
-        <v>131.3502063659727</v>
+        <v>131.3502063638078</v>
       </c>
       <c r="D9" t="n">
-        <v>43.53028168036469</v>
+        <v>43.53028168002015</v>
       </c>
       <c r="E9" t="n">
-        <v>43.48881898332452</v>
+        <v>43.48881898315292</v>
       </c>
       <c r="F9" t="n">
-        <v>43.52390821438647</v>
+        <v>43.52390821424385</v>
       </c>
       <c r="G9" t="n">
-        <v>43.49721428532813</v>
+        <v>43.49721428525685</v>
       </c>
       <c r="H9" t="n">
-        <v>87.86490892293523</v>
+        <v>87.86490005694598</v>
       </c>
       <c r="I9" t="n">
-        <v>87.2003740828346</v>
+        <v>87.20036645230473</v>
       </c>
       <c r="J9" t="n">
-        <v>43.47297333869658</v>
+        <v>43.47296875756791</v>
       </c>
       <c r="K9" t="n">
-        <v>43.46538187671602</v>
+        <v>43.46537959217822</v>
       </c>
     </row>
     <row r="10">
@@ -3074,34 +3074,34 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>130.4072929677857</v>
+        <v>130.4072930027934</v>
       </c>
       <c r="C10" t="n">
-        <v>130.4185496920055</v>
+        <v>130.4185497130307</v>
       </c>
       <c r="D10" t="n">
-        <v>43.47493262306737</v>
+        <v>43.47493262645413</v>
       </c>
       <c r="E10" t="n">
-        <v>43.47499817396505</v>
+        <v>43.47499817565506</v>
       </c>
       <c r="F10" t="n">
-        <v>43.47466052076354</v>
+        <v>43.47466052214914</v>
       </c>
       <c r="G10" t="n">
-        <v>43.47483859353713</v>
+        <v>43.47483859422979</v>
       </c>
       <c r="H10" t="n">
-        <v>86.93813977440415</v>
+        <v>86.93813993011992</v>
       </c>
       <c r="I10" t="n">
-        <v>86.94789123994893</v>
+        <v>86.94789102314702</v>
       </c>
       <c r="J10" t="n">
-        <v>43.47395772871176</v>
+        <v>43.47395750506257</v>
       </c>
       <c r="K10" t="n">
-        <v>43.47446577743224</v>
+        <v>43.4744656624829</v>
       </c>
     </row>
     <row r="11">
@@ -3109,34 +3109,34 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>109.2321279276741</v>
+        <v>109.2321278920631</v>
       </c>
       <c r="C11" t="n">
-        <v>110.0711282018977</v>
+        <v>110.0711281805939</v>
       </c>
       <c r="D11" t="n">
-        <v>36.94467585941053</v>
+        <v>36.94467585601808</v>
       </c>
       <c r="E11" t="n">
-        <v>36.98617781243808</v>
+        <v>36.98617781074812</v>
       </c>
       <c r="F11" t="n">
-        <v>36.95089826901793</v>
+        <v>36.95089826761425</v>
       </c>
       <c r="G11" t="n">
-        <v>36.97769365128823</v>
+        <v>36.97769365058672</v>
       </c>
       <c r="H11" t="n">
-        <v>73.01146101532713</v>
+        <v>73.01146145085453</v>
       </c>
       <c r="I11" t="n">
-        <v>73.68959816410531</v>
+        <v>73.68959854437961</v>
       </c>
       <c r="J11" t="n">
-        <v>36.96577180741791</v>
+        <v>36.96577203602537</v>
       </c>
       <c r="K11" t="n">
-        <v>36.99151763060286</v>
+        <v>36.99151774460567</v>
       </c>
     </row>
     <row r="12">
@@ -3144,34 +3144,34 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>90.10733079819606</v>
+        <v>90.10733079888479</v>
       </c>
       <c r="C12" t="n">
-        <v>90.80119241368692</v>
+        <v>90.80119241400435</v>
       </c>
       <c r="D12" t="n">
-        <v>30.4786392615341</v>
+        <v>30.4786392615406</v>
       </c>
       <c r="E12" t="n">
-        <v>30.51341088313324</v>
+        <v>30.51341088313318</v>
       </c>
       <c r="F12" t="n">
-        <v>30.48410237279765</v>
+        <v>30.48410237281817</v>
       </c>
       <c r="G12" t="n">
-        <v>30.5064288943822</v>
+        <v>30.50642889439223</v>
       </c>
       <c r="H12" t="n">
-        <v>60.23445126363148</v>
+        <v>60.23445123926778</v>
       </c>
       <c r="I12" t="n">
-        <v>60.79359633928522</v>
+        <v>60.79359633253331</v>
       </c>
       <c r="J12" t="n">
-        <v>30.4980978732809</v>
+        <v>30.49809787303379</v>
       </c>
       <c r="K12" t="n">
-        <v>30.51877996590295</v>
+        <v>30.5187799659188</v>
       </c>
     </row>
     <row r="13">
@@ -3179,34 +3179,34 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>91.5854380827646</v>
+        <v>91.58543808257062</v>
       </c>
       <c r="C13" t="n">
-        <v>91.57882592001691</v>
+        <v>91.57882591990136</v>
       </c>
       <c r="D13" t="n">
-        <v>30.52504476573318</v>
+        <v>30.5250447657146</v>
       </c>
       <c r="E13" t="n">
-        <v>30.52500359897793</v>
+        <v>30.52500359896866</v>
       </c>
       <c r="F13" t="n">
-        <v>30.52520197973765</v>
+        <v>30.52520197973006</v>
       </c>
       <c r="G13" t="n">
-        <v>30.52509609349431</v>
+        <v>30.52509609349052</v>
       </c>
       <c r="H13" t="n">
-        <v>61.14066094014781</v>
+        <v>61.14066037815272</v>
       </c>
       <c r="I13" t="n">
-        <v>61.12553028694049</v>
+        <v>61.12552977718197</v>
       </c>
       <c r="J13" t="n">
-        <v>30.57083479765598</v>
+        <v>30.57083448460817</v>
       </c>
       <c r="K13" t="n">
-        <v>30.54788838470175</v>
+        <v>30.54788822833308</v>
       </c>
     </row>
     <row r="14">
@@ -3214,34 +3214,34 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>112.4849285836827</v>
+        <v>112.4849285842346</v>
       </c>
       <c r="C14" t="n">
-        <v>111.7800974084793</v>
+        <v>111.7800974088107</v>
       </c>
       <c r="D14" t="n">
-        <v>37.04642581021124</v>
+        <v>37.04642581026462</v>
       </c>
       <c r="E14" t="n">
-        <v>37.01159054832053</v>
+        <v>37.01159054834718</v>
       </c>
       <c r="F14" t="n">
-        <v>37.04122864343285</v>
+        <v>37.04122864345465</v>
       </c>
       <c r="G14" t="n">
-        <v>37.01872848203801</v>
+        <v>37.01872848204892</v>
       </c>
       <c r="H14" t="n">
-        <v>74.81037494371277</v>
+        <v>74.81038177394126</v>
       </c>
       <c r="I14" t="n">
-        <v>74.24317125602458</v>
+        <v>74.24317739005444</v>
       </c>
       <c r="J14" t="n">
-        <v>37.01850591178878</v>
+        <v>37.01850966342267</v>
       </c>
       <c r="K14" t="n">
-        <v>37.0020385419595</v>
+        <v>37.00204041537135</v>
       </c>
     </row>
     <row r="15">
@@ -3249,34 +3249,34 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>132.1828816398197</v>
+        <v>132.182881639451</v>
       </c>
       <c r="C15" t="n">
-        <v>131.3502063638784</v>
+        <v>131.3502063636581</v>
       </c>
       <c r="D15" t="n">
-        <v>43.53028168004283</v>
+        <v>43.53028168000801</v>
       </c>
       <c r="E15" t="n">
-        <v>43.48881898316516</v>
+        <v>43.48881898314785</v>
       </c>
       <c r="F15" t="n">
-        <v>43.52390821424815</v>
+        <v>43.52390821423366</v>
       </c>
       <c r="G15" t="n">
-        <v>43.49721428525903</v>
+        <v>43.49721428525179</v>
       </c>
       <c r="H15" t="n">
-        <v>87.86489722380651</v>
+        <v>87.86489052934476</v>
       </c>
       <c r="I15" t="n">
-        <v>87.20020788599021</v>
+        <v>87.20020214395797</v>
       </c>
       <c r="J15" t="n">
-        <v>43.47283165972882</v>
+        <v>43.4728282176084</v>
       </c>
       <c r="K15" t="n">
-        <v>43.46530969252393</v>
+        <v>43.46530797618253</v>
       </c>
     </row>
     <row r="16">
@@ -3284,34 +3284,34 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>130.4072929678643</v>
+        <v>130.4072929678732</v>
       </c>
       <c r="C16" t="n">
-        <v>130.4185496920412</v>
+        <v>130.4185496920457</v>
       </c>
       <c r="D16" t="n">
-        <v>43.47493262306819</v>
+        <v>43.47493262306833</v>
       </c>
       <c r="E16" t="n">
-        <v>43.47499817396507</v>
+        <v>43.47499817396511</v>
       </c>
       <c r="F16" t="n">
-        <v>43.47466052076583</v>
+        <v>43.4746605207661</v>
       </c>
       <c r="G16" t="n">
-        <v>43.47483859353824</v>
+        <v>43.47483859353838</v>
       </c>
       <c r="H16" t="n">
-        <v>86.93815482003079</v>
+        <v>86.93815525132831</v>
       </c>
       <c r="I16" t="n">
-        <v>86.94789608253464</v>
+        <v>86.94789620056164</v>
       </c>
       <c r="J16" t="n">
-        <v>43.47395794908545</v>
+        <v>43.47395795256487</v>
       </c>
       <c r="K16" t="n">
-        <v>43.47446578377902</v>
+        <v>43.47446578305073</v>
       </c>
     </row>
     <row r="17">
@@ -3319,16 +3319,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>109.2321279276721</v>
+        <v>109.2321279276719</v>
       </c>
       <c r="C17" t="n">
         <v>110.0711282018968</v>
       </c>
       <c r="D17" t="n">
-        <v>36.94467585941036</v>
+        <v>36.94467585941035</v>
       </c>
       <c r="E17" t="n">
-        <v>36.98617781243799</v>
+        <v>36.98617781243797</v>
       </c>
       <c r="F17" t="n">
         <v>36.95089826901788</v>
@@ -3337,16 +3337,16 @@
         <v>36.97769365128821</v>
       </c>
       <c r="H17" t="n">
-        <v>73.0114608083026</v>
+        <v>73.0114608034427</v>
       </c>
       <c r="I17" t="n">
-        <v>73.68959814929649</v>
+        <v>73.68959814905716</v>
       </c>
       <c r="J17" t="n">
-        <v>36.96577180849236</v>
+        <v>36.96577180855412</v>
       </c>
       <c r="K17" t="n">
-        <v>36.99151763114872</v>
+        <v>36.9915176311786</v>
       </c>
     </row>
     <row r="18">
@@ -3354,34 +3354,34 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>90.10733079819603</v>
+        <v>90.10733079819565</v>
       </c>
       <c r="C18" t="n">
-        <v>90.80119241368685</v>
+        <v>90.80119241368649</v>
       </c>
       <c r="D18" t="n">
-        <v>30.47863926153414</v>
+        <v>30.47863926153408</v>
       </c>
       <c r="E18" t="n">
-        <v>30.51341088313327</v>
+        <v>30.51341088313325</v>
       </c>
       <c r="F18" t="n">
-        <v>30.48410237279764</v>
+        <v>30.48410237279762</v>
       </c>
       <c r="G18" t="n">
-        <v>30.5064288943822</v>
+        <v>30.50642889438219</v>
       </c>
       <c r="H18" t="n">
-        <v>60.23445126398868</v>
+        <v>60.23445126396005</v>
       </c>
       <c r="I18" t="n">
-        <v>60.79359633920603</v>
+        <v>60.79359633917443</v>
       </c>
       <c r="J18" t="n">
-        <v>30.49809787324413</v>
+        <v>30.49809787322576</v>
       </c>
       <c r="K18" t="n">
-        <v>30.51877996588505</v>
+        <v>30.51877996587594</v>
       </c>
     </row>
     <row r="19">
@@ -3389,34 +3389,34 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>91.5854380827644</v>
+        <v>91.58543808276534</v>
       </c>
       <c r="C19" t="n">
-        <v>91.57882592001707</v>
+        <v>91.57882592001772</v>
       </c>
       <c r="D19" t="n">
-        <v>30.52504476573321</v>
+        <v>30.52504476573328</v>
       </c>
       <c r="E19" t="n">
-        <v>30.52500359897795</v>
+        <v>30.52500359897798</v>
       </c>
       <c r="F19" t="n">
-        <v>30.52520197973767</v>
+        <v>30.52520197973771</v>
       </c>
       <c r="G19" t="n">
-        <v>30.52509609349433</v>
+        <v>30.52509609349434</v>
       </c>
       <c r="H19" t="n">
-        <v>61.14066094016476</v>
+        <v>61.14066094016753</v>
       </c>
       <c r="I19" t="n">
-        <v>61.1255302869534</v>
+        <v>61.12553028695488</v>
       </c>
       <c r="J19" t="n">
-        <v>30.57083479766369</v>
+        <v>30.57083479766456</v>
       </c>
       <c r="K19" t="n">
-        <v>30.54788838470552</v>
+        <v>30.54788838470605</v>
       </c>
     </row>
     <row r="20">
@@ -3424,34 +3424,34 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>112.4849285836829</v>
+        <v>112.4849285836826</v>
       </c>
       <c r="C20" t="n">
-        <v>111.7800974084794</v>
+        <v>111.7800974084791</v>
       </c>
       <c r="D20" t="n">
-        <v>37.04642581021123</v>
+        <v>37.04642581021121</v>
       </c>
       <c r="E20" t="n">
-        <v>37.01159054832053</v>
+        <v>37.01159054832052</v>
       </c>
       <c r="F20" t="n">
-        <v>37.04122864343283</v>
+        <v>37.04122864343282</v>
       </c>
       <c r="G20" t="n">
         <v>37.018728482038</v>
       </c>
       <c r="H20" t="n">
-        <v>74.81037494410079</v>
+        <v>74.81037494570776</v>
       </c>
       <c r="I20" t="n">
-        <v>74.2431712563744</v>
+        <v>74.24317125782159</v>
       </c>
       <c r="J20" t="n">
-        <v>37.01850591200297</v>
+        <v>37.01850591288912</v>
       </c>
       <c r="K20" t="n">
-        <v>37.00203854206641</v>
+        <v>37.00203854250903</v>
       </c>
     </row>
     <row r="21">
@@ -3459,16 +3459,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>132.18288163982</v>
+        <v>132.1828816398202</v>
       </c>
       <c r="C21" t="n">
-        <v>131.3502063638785</v>
+        <v>131.3502063638786</v>
       </c>
       <c r="D21" t="n">
         <v>43.53028168004288</v>
       </c>
       <c r="E21" t="n">
-        <v>43.48881898316519</v>
+        <v>43.4888189831652</v>
       </c>
       <c r="F21" t="n">
         <v>43.52390821424816</v>
@@ -3477,16 +3477,16 @@
         <v>43.49721428525903</v>
       </c>
       <c r="H21" t="n">
-        <v>87.86489722338598</v>
+        <v>87.86489722165683</v>
       </c>
       <c r="I21" t="n">
-        <v>87.2002078856281</v>
+        <v>87.2002078841395</v>
       </c>
       <c r="J21" t="n">
-        <v>43.4728316595114</v>
+        <v>43.47283165861766</v>
       </c>
       <c r="K21" t="n">
-        <v>43.46530969241564</v>
+        <v>43.46530969196993</v>
       </c>
     </row>
     <row r="22">
@@ -3494,34 +3494,34 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>130.4072929678649</v>
+        <v>130.4072929678644</v>
       </c>
       <c r="C22" t="n">
-        <v>130.4185496920417</v>
+        <v>130.4185496920415</v>
       </c>
       <c r="D22" t="n">
-        <v>43.47493262306822</v>
+        <v>43.47493262306818</v>
       </c>
       <c r="E22" t="n">
-        <v>43.47499817396508</v>
+        <v>43.47499817396507</v>
       </c>
       <c r="F22" t="n">
-        <v>43.47466052076583</v>
+        <v>43.47466052076581</v>
       </c>
       <c r="G22" t="n">
-        <v>43.47483859353824</v>
+        <v>43.47483859353823</v>
       </c>
       <c r="H22" t="n">
-        <v>86.93815482005829</v>
+        <v>86.93815482017494</v>
       </c>
       <c r="I22" t="n">
-        <v>86.94789608254229</v>
+        <v>86.9478960825772</v>
       </c>
       <c r="J22" t="n">
-        <v>43.47395794908573</v>
+        <v>43.47395794908908</v>
       </c>
       <c r="K22" t="n">
-        <v>43.47446578377855</v>
+        <v>43.47446578377977</v>
       </c>
     </row>
     <row r="23">
@@ -3529,34 +3529,34 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>109.2321279276718</v>
+        <v>109.2321279276725</v>
       </c>
       <c r="C23" t="n">
-        <v>110.0711282018966</v>
+        <v>110.0711282018972</v>
       </c>
       <c r="D23" t="n">
-        <v>36.94467585941035</v>
+        <v>36.94467585941037</v>
       </c>
       <c r="E23" t="n">
         <v>36.98617781243799</v>
       </c>
       <c r="F23" t="n">
-        <v>36.95089826901788</v>
+        <v>36.95089826901791</v>
       </c>
       <c r="G23" t="n">
         <v>36.97769365128821</v>
       </c>
       <c r="H23" t="n">
-        <v>73.01146080828981</v>
+        <v>73.01146080832925</v>
       </c>
       <c r="I23" t="n">
-        <v>73.6895981492853</v>
+        <v>73.68959814932212</v>
       </c>
       <c r="J23" t="n">
-        <v>36.96577180848564</v>
+        <v>36.96577180850806</v>
       </c>
       <c r="K23" t="n">
-        <v>36.9915176311453</v>
+        <v>36.99151763115661</v>
       </c>
     </row>
     <row r="24">
@@ -3564,34 +3564,34 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>90.10733079819597</v>
+        <v>90.10733079819576</v>
       </c>
       <c r="C24" t="n">
-        <v>90.80119241368692</v>
+        <v>90.80119241368659</v>
       </c>
       <c r="D24" t="n">
-        <v>30.47863926153412</v>
+        <v>30.47863926153408</v>
       </c>
       <c r="E24" t="n">
-        <v>30.51341088313325</v>
+        <v>30.51341088313323</v>
       </c>
       <c r="F24" t="n">
-        <v>30.48410237279764</v>
+        <v>30.48410237279763</v>
       </c>
       <c r="G24" t="n">
         <v>30.5064288943822</v>
       </c>
       <c r="H24" t="n">
-        <v>60.23445126399749</v>
+        <v>60.23445126396047</v>
       </c>
       <c r="I24" t="n">
-        <v>60.79359633921353</v>
+        <v>60.79359633918144</v>
       </c>
       <c r="J24" t="n">
-        <v>30.49809787324859</v>
+        <v>30.49809787322931</v>
       </c>
       <c r="K24" t="n">
-        <v>30.51877996588719</v>
+        <v>30.5187799658776</v>
       </c>
     </row>
     <row r="25">
@@ -3599,34 +3599,34 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>91.5854380827646</v>
+        <v>91.58543808276482</v>
       </c>
       <c r="C25" t="n">
-        <v>91.57882592001718</v>
+        <v>91.57882592001738</v>
       </c>
       <c r="D25" t="n">
-        <v>30.52504476573323</v>
+        <v>30.52504476573326</v>
       </c>
       <c r="E25" t="n">
-        <v>30.52500359897796</v>
+        <v>30.52500359897798</v>
       </c>
       <c r="F25" t="n">
-        <v>30.52520197973768</v>
+        <v>30.52520197973769</v>
       </c>
       <c r="G25" t="n">
         <v>30.52509609349433</v>
       </c>
       <c r="H25" t="n">
-        <v>61.14066094017428</v>
+        <v>61.14066094017824</v>
       </c>
       <c r="I25" t="n">
-        <v>61.12553028696226</v>
+        <v>61.12553028696475</v>
       </c>
       <c r="J25" t="n">
-        <v>30.57083479766919</v>
+        <v>30.57083479767048</v>
       </c>
       <c r="K25" t="n">
-        <v>30.54788838470837</v>
+        <v>30.54788838470895</v>
       </c>
     </row>
     <row r="26">
@@ -3634,34 +3634,34 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>112.4849285836829</v>
+        <v>112.4849285836827</v>
       </c>
       <c r="C26" t="n">
-        <v>111.7800974084793</v>
+        <v>111.7800974084792</v>
       </c>
       <c r="D26" t="n">
-        <v>37.04642581021124</v>
+        <v>37.04642581021123</v>
       </c>
       <c r="E26" t="n">
         <v>37.01159054832053</v>
       </c>
       <c r="F26" t="n">
-        <v>37.04122864343284</v>
+        <v>37.04122864343281</v>
       </c>
       <c r="G26" t="n">
-        <v>37.01872848203801</v>
+        <v>37.01872848203799</v>
       </c>
       <c r="H26" t="n">
-        <v>74.81037494432928</v>
+        <v>74.81037494641464</v>
       </c>
       <c r="I26" t="n">
-        <v>74.24317125658042</v>
+        <v>74.24317125845859</v>
       </c>
       <c r="J26" t="n">
-        <v>37.01850591212927</v>
+        <v>37.01850591327956</v>
       </c>
       <c r="K26" t="n">
-        <v>37.00203854212946</v>
+        <v>37.00203854270411</v>
       </c>
     </row>
   </sheetData>
@@ -3810,49 +3810,49 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>42.02260091717802</v>
+        <v>42.02260091734663</v>
       </c>
       <c r="C3" t="n">
-        <v>42.02080732148311</v>
+        <v>42.020807321651</v>
       </c>
       <c r="D3" t="n">
-        <v>42.01371083752576</v>
+        <v>42.0137108376928</v>
       </c>
       <c r="E3" t="n">
-        <v>41.99554578888829</v>
+        <v>41.99554578905441</v>
       </c>
       <c r="F3" t="n">
-        <v>41.96829553694039</v>
+        <v>41.96829553710544</v>
       </c>
       <c r="G3" t="n">
-        <v>41.93326599558497</v>
+        <v>41.9332659957495</v>
       </c>
       <c r="H3" t="n">
-        <v>41.99907081268591</v>
+        <v>41.99907081285263</v>
       </c>
       <c r="I3" t="n">
-        <v>41.98432761130181</v>
+        <v>41.98432761146838</v>
       </c>
       <c r="J3" t="n">
-        <v>41.96817191449776</v>
+        <v>41.96817191466426</v>
       </c>
       <c r="K3" t="n">
-        <v>42.32328486429486</v>
+        <v>42.32328486468478</v>
       </c>
       <c r="L3" t="n">
-        <v>42.3206977074821</v>
+        <v>42.32069770785554</v>
       </c>
       <c r="M3" t="n">
-        <v>42.31186756820239</v>
+        <v>42.31186756854746</v>
       </c>
       <c r="N3" t="n">
-        <v>42.30387333873909</v>
+        <v>42.30387333906514</v>
       </c>
       <c r="O3" t="n">
-        <v>42.30388442744771</v>
+        <v>42.30388442777367</v>
       </c>
       <c r="P3" t="n">
-        <v>42.30321298722858</v>
+        <v>42.3032129875541</v>
       </c>
     </row>
     <row r="4">
@@ -3860,49 +3860,49 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.16526097647309</v>
+        <v>41.16526097646953</v>
       </c>
       <c r="C4" t="n">
-        <v>41.1544489964277</v>
+        <v>41.15444899642596</v>
       </c>
       <c r="D4" t="n">
-        <v>41.13960306887309</v>
+        <v>41.13960306887262</v>
       </c>
       <c r="E4" t="n">
-        <v>41.11321537260552</v>
+        <v>41.11321537260628</v>
       </c>
       <c r="F4" t="n">
-        <v>41.07639247639154</v>
+        <v>41.07639247639365</v>
       </c>
       <c r="G4" t="n">
-        <v>41.03570526669764</v>
+        <v>41.03570526670046</v>
       </c>
       <c r="H4" t="n">
-        <v>41.12178092727272</v>
+        <v>41.12178092727267</v>
       </c>
       <c r="I4" t="n">
-        <v>41.10507362512818</v>
+        <v>41.10507362512836</v>
       </c>
       <c r="J4" t="n">
-        <v>41.0877195454234</v>
+        <v>41.08771954542371</v>
       </c>
       <c r="K4" t="n">
-        <v>41.49937891474011</v>
+        <v>41.49937891147657</v>
       </c>
       <c r="L4" t="n">
-        <v>41.47490065337267</v>
+        <v>41.47490065050991</v>
       </c>
       <c r="M4" t="n">
-        <v>41.44156986720108</v>
+        <v>41.44156986476973</v>
       </c>
       <c r="N4" t="n">
-        <v>41.41976470791139</v>
+        <v>41.41976470571296</v>
       </c>
       <c r="O4" t="n">
-        <v>41.41970097126793</v>
+        <v>41.41970096907147</v>
       </c>
       <c r="P4" t="n">
-        <v>41.41875142826649</v>
+        <v>41.41875142607406</v>
       </c>
     </row>
     <row r="5">
@@ -3910,49 +3910,49 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.15037369828381</v>
+        <v>41.15037369828377</v>
       </c>
       <c r="C5" t="n">
-        <v>41.13444389461469</v>
+        <v>41.13444389461465</v>
       </c>
       <c r="D5" t="n">
-        <v>41.11840366439692</v>
+        <v>41.11840366439686</v>
       </c>
       <c r="E5" t="n">
-        <v>41.09421390810758</v>
+        <v>41.09421390810754</v>
       </c>
       <c r="F5" t="n">
         <v>41.06190468234119</v>
       </c>
       <c r="G5" t="n">
-        <v>41.02951316670723</v>
+        <v>41.02951316670724</v>
       </c>
       <c r="H5" t="n">
-        <v>41.1038173049612</v>
+        <v>41.10381730496115</v>
       </c>
       <c r="I5" t="n">
-        <v>41.09078847801447</v>
+        <v>41.09078847801443</v>
       </c>
       <c r="J5" t="n">
-        <v>41.07774642453654</v>
+        <v>41.07774642453649</v>
       </c>
       <c r="K5" t="n">
-        <v>41.30053453047054</v>
+        <v>41.30053453985365</v>
       </c>
       <c r="L5" t="n">
-        <v>41.19858563042261</v>
+        <v>41.1985856376694</v>
       </c>
       <c r="M5" t="n">
-        <v>41.09084710036698</v>
+        <v>41.09084710561527</v>
       </c>
       <c r="N5" t="n">
-        <v>41.03308425993443</v>
+        <v>41.03308426421815</v>
       </c>
       <c r="O5" t="n">
-        <v>41.03241747133608</v>
+        <v>41.03241747560235</v>
       </c>
       <c r="P5" t="n">
-        <v>41.03111922092781</v>
+        <v>41.03111922518194</v>
       </c>
     </row>
     <row r="6">
@@ -3972,10 +3972,10 @@
         <v>41.06840240592481</v>
       </c>
       <c r="F6" t="n">
-        <v>41.04640623685212</v>
+        <v>41.04640623685214</v>
       </c>
       <c r="G6" t="n">
-        <v>41.0243480760432</v>
+        <v>41.02434807604322</v>
       </c>
       <c r="H6" t="n">
         <v>41.07493282991543</v>
@@ -3987,22 +3987,22 @@
         <v>41.05719365332317</v>
       </c>
       <c r="K6" t="n">
-        <v>41.44445688003366</v>
+        <v>41.44445687559962</v>
       </c>
       <c r="L6" t="n">
-        <v>41.27306392062883</v>
+        <v>41.27306391812885</v>
       </c>
       <c r="M6" t="n">
-        <v>41.10286380503776</v>
+        <v>41.10286380422856</v>
       </c>
       <c r="N6" t="n">
-        <v>41.01688412404769</v>
+        <v>41.01688412402514</v>
       </c>
       <c r="O6" t="n">
-        <v>41.01549012608951</v>
+        <v>41.01549012608378</v>
       </c>
       <c r="P6" t="n">
-        <v>41.01406248503955</v>
+        <v>41.01406248504229</v>
       </c>
     </row>
     <row r="7">
@@ -4019,40 +4019,40 @@
         <v>41.08503372212858</v>
       </c>
       <c r="E7" t="n">
-        <v>41.06848769261106</v>
+        <v>41.06848769261108</v>
       </c>
       <c r="F7" t="n">
-        <v>41.04642457629501</v>
+        <v>41.04642457629502</v>
       </c>
       <c r="G7" t="n">
-        <v>41.0243496721281</v>
+        <v>41.02434967212811</v>
       </c>
       <c r="H7" t="n">
-        <v>41.07507386506571</v>
+        <v>41.07507386506573</v>
       </c>
       <c r="I7" t="n">
-        <v>41.06618784880381</v>
+        <v>41.06618784880383</v>
       </c>
       <c r="J7" t="n">
-        <v>41.05729997332278</v>
+        <v>41.05729997332279</v>
       </c>
       <c r="K7" t="n">
-        <v>41.45973557064465</v>
+        <v>41.45973557071237</v>
       </c>
       <c r="L7" t="n">
-        <v>41.28375268836124</v>
+        <v>41.28375268835003</v>
       </c>
       <c r="M7" t="n">
-        <v>41.10729741030674</v>
+        <v>41.10729741028062</v>
       </c>
       <c r="N7" t="n">
-        <v>41.01801478827524</v>
+        <v>41.01801478825184</v>
       </c>
       <c r="O7" t="n">
-        <v>41.0165487667709</v>
+        <v>41.01654876674759</v>
       </c>
       <c r="P7" t="n">
-        <v>41.01508483511049</v>
+        <v>41.01508483508724</v>
       </c>
     </row>
     <row r="8">
@@ -4060,49 +4060,49 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>41.15185920699719</v>
+        <v>41.15185920707656</v>
       </c>
       <c r="C8" t="n">
-        <v>41.13524233961589</v>
+        <v>41.13524233969424</v>
       </c>
       <c r="D8" t="n">
-        <v>41.1188263181086</v>
+        <v>41.11882631818637</v>
       </c>
       <c r="E8" t="n">
-        <v>41.09442372457995</v>
+        <v>41.09442372465721</v>
       </c>
       <c r="F8" t="n">
-        <v>41.06195220839525</v>
+        <v>41.06195220847196</v>
       </c>
       <c r="G8" t="n">
-        <v>41.02951609699125</v>
+        <v>41.02951609706773</v>
       </c>
       <c r="H8" t="n">
-        <v>41.10415920401734</v>
+        <v>41.10415920409495</v>
       </c>
       <c r="I8" t="n">
-        <v>41.09108596221496</v>
+        <v>41.0910859622925</v>
       </c>
       <c r="J8" t="n">
-        <v>41.07802444106258</v>
+        <v>41.0780244411401</v>
       </c>
       <c r="K8" t="n">
-        <v>41.67164096412463</v>
+        <v>41.67164120414309</v>
       </c>
       <c r="L8" t="n">
-        <v>41.40988308744262</v>
+        <v>41.40988327088991</v>
       </c>
       <c r="M8" t="n">
-        <v>41.15045027709211</v>
+        <v>41.15045040945203</v>
       </c>
       <c r="N8" t="n">
-        <v>41.01952360270126</v>
+        <v>41.01952371095874</v>
       </c>
       <c r="O8" t="n">
-        <v>41.01737896753971</v>
+        <v>41.01737907527534</v>
       </c>
       <c r="P8" t="n">
-        <v>41.01523625539623</v>
+        <v>41.01523636287411</v>
       </c>
     </row>
     <row r="9">
@@ -4110,49 +4110,49 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41.20443761021514</v>
+        <v>41.2044376102114</v>
       </c>
       <c r="C9" t="n">
-        <v>41.18152442725738</v>
+        <v>41.18152442725489</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15888631219285</v>
+        <v>41.15888631219111</v>
       </c>
       <c r="E9" t="n">
-        <v>41.12522867889214</v>
+        <v>41.12522867889107</v>
       </c>
       <c r="F9" t="n">
-        <v>41.08043398466196</v>
+        <v>41.08043398466158</v>
       </c>
       <c r="G9" t="n">
-        <v>41.03567583517204</v>
+        <v>41.03567583517203</v>
       </c>
       <c r="H9" t="n">
-        <v>41.1386575891682</v>
+        <v>41.13865758916668</v>
       </c>
       <c r="I9" t="n">
-        <v>41.12062479378625</v>
+        <v>41.12062479378486</v>
       </c>
       <c r="J9" t="n">
-        <v>41.10260621137259</v>
+        <v>41.10260621137125</v>
       </c>
       <c r="K9" t="n">
-        <v>41.91655549481484</v>
+        <v>41.91655533254206</v>
       </c>
       <c r="L9" t="n">
-        <v>41.5576288439289</v>
+        <v>41.55762875269702</v>
       </c>
       <c r="M9" t="n">
-        <v>41.20105765597157</v>
+        <v>41.20105762635708</v>
       </c>
       <c r="N9" t="n">
-        <v>41.02068880214372</v>
+        <v>41.02068880125892</v>
       </c>
       <c r="O9" t="n">
-        <v>41.01773596733844</v>
+        <v>41.01773596707346</v>
       </c>
       <c r="P9" t="n">
-        <v>41.01478394883323</v>
+        <v>41.01478394887732</v>
       </c>
     </row>
     <row r="10">
@@ -4160,49 +4160,49 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41.20320142499043</v>
+        <v>41.20320142577667</v>
       </c>
       <c r="C10" t="n">
-        <v>41.18089875154555</v>
+        <v>41.18089875232024</v>
       </c>
       <c r="D10" t="n">
-        <v>41.15858015934335</v>
+        <v>41.15858016011126</v>
       </c>
       <c r="E10" t="n">
-        <v>41.12508580227966</v>
+        <v>41.12508580304173</v>
       </c>
       <c r="F10" t="n">
-        <v>41.08040476569862</v>
+        <v>41.08040476645456</v>
       </c>
       <c r="G10" t="n">
-        <v>41.03567502122669</v>
+        <v>41.03567502197999</v>
       </c>
       <c r="H10" t="n">
-        <v>41.13841986692493</v>
+        <v>41.13841986769113</v>
       </c>
       <c r="I10" t="n">
-        <v>41.12042774292667</v>
+        <v>41.12042774369206</v>
       </c>
       <c r="J10" t="n">
-        <v>41.10242760303393</v>
+        <v>41.10242760379909</v>
       </c>
       <c r="K10" t="n">
-        <v>41.90693683493755</v>
+        <v>41.90693682784585</v>
       </c>
       <c r="L10" t="n">
-        <v>41.55546080462258</v>
+        <v>41.55546079621239</v>
       </c>
       <c r="M10" t="n">
-        <v>41.20093286052121</v>
+        <v>41.20093285380714</v>
       </c>
       <c r="N10" t="n">
-        <v>41.02066504528221</v>
+        <v>41.0206650398756</v>
       </c>
       <c r="O10" t="n">
-        <v>41.01771207559118</v>
+        <v>41.01771207021443</v>
       </c>
       <c r="P10" t="n">
-        <v>41.01475882622184</v>
+        <v>41.01475882086027</v>
       </c>
     </row>
     <row r="11">
@@ -4210,49 +4210,49 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>41.14993612270071</v>
+        <v>41.14993612266998</v>
       </c>
       <c r="C11" t="n">
-        <v>41.13426510541967</v>
+        <v>41.13426510539913</v>
       </c>
       <c r="D11" t="n">
-        <v>41.11834652688777</v>
+        <v>41.11834652687339</v>
       </c>
       <c r="E11" t="n">
-        <v>41.09419912041638</v>
+        <v>41.09419912040751</v>
       </c>
       <c r="F11" t="n">
-        <v>41.06190549128472</v>
+        <v>41.06190549128178</v>
       </c>
       <c r="G11" t="n">
-        <v>41.02951385477415</v>
+        <v>41.02951385477416</v>
       </c>
       <c r="H11" t="n">
-        <v>41.1037863431361</v>
+        <v>41.10378634312351</v>
       </c>
       <c r="I11" t="n">
-        <v>41.09077664577867</v>
+        <v>41.09077664576707</v>
       </c>
       <c r="J11" t="n">
-        <v>41.07774395769543</v>
+        <v>41.07774395768431</v>
       </c>
       <c r="K11" t="n">
-        <v>41.65409095931995</v>
+        <v>41.65409096612856</v>
       </c>
       <c r="L11" t="n">
-        <v>41.40469085246701</v>
+        <v>41.40469085634123</v>
       </c>
       <c r="M11" t="n">
-        <v>41.14910673356265</v>
+        <v>41.14910673482314</v>
       </c>
       <c r="N11" t="n">
-        <v>41.0186396758164</v>
+        <v>41.01863967585539</v>
       </c>
       <c r="O11" t="n">
-        <v>41.01650133993594</v>
+        <v>41.01650133994863</v>
       </c>
       <c r="P11" t="n">
-        <v>41.01435993017582</v>
+        <v>41.0143599301754</v>
       </c>
     </row>
     <row r="12">
@@ -4260,49 +4260,49 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>41.1063769757456</v>
+        <v>41.10637697574587</v>
       </c>
       <c r="C12" t="n">
-        <v>41.09569861380906</v>
+        <v>41.09569861380917</v>
       </c>
       <c r="D12" t="n">
-        <v>41.08485250413821</v>
+        <v>41.08485250413823</v>
       </c>
       <c r="E12" t="n">
-        <v>41.06840239041623</v>
+        <v>41.06840239041622</v>
       </c>
       <c r="F12" t="n">
-        <v>41.04640622624165</v>
+        <v>41.04640622624164</v>
       </c>
       <c r="G12" t="n">
-        <v>41.0243480676848</v>
+        <v>41.02434806768478</v>
       </c>
       <c r="H12" t="n">
-        <v>41.07493282394712</v>
+        <v>41.07493282394711</v>
       </c>
       <c r="I12" t="n">
         <v>41.06607067764573</v>
       </c>
       <c r="J12" t="n">
-        <v>41.05719363856714</v>
+        <v>41.05719363856713</v>
       </c>
       <c r="K12" t="n">
-        <v>41.4509631622871</v>
+        <v>41.45096316210844</v>
       </c>
       <c r="L12" t="n">
-        <v>41.28037635877465</v>
+        <v>41.28037635873324</v>
       </c>
       <c r="M12" t="n">
-        <v>41.10589033241186</v>
+        <v>41.10589033240903</v>
       </c>
       <c r="N12" t="n">
-        <v>41.01698802833911</v>
+        <v>41.01698802833943</v>
       </c>
       <c r="O12" t="n">
-        <v>41.01552873374725</v>
+        <v>41.01552873374758</v>
       </c>
       <c r="P12" t="n">
-        <v>41.01406742381453</v>
+        <v>41.01406742381486</v>
       </c>
     </row>
     <row r="13">
@@ -4310,49 +4310,49 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>41.10709718135497</v>
+        <v>41.10709718135068</v>
       </c>
       <c r="C13" t="n">
-        <v>41.09606613366236</v>
+        <v>41.09606613365811</v>
       </c>
       <c r="D13" t="n">
-        <v>41.08503372206491</v>
+        <v>41.0850337220607</v>
       </c>
       <c r="E13" t="n">
-        <v>41.06848769247966</v>
+        <v>41.06848769247546</v>
       </c>
       <c r="F13" t="n">
-        <v>41.04642457610344</v>
+        <v>41.04642457609928</v>
       </c>
       <c r="G13" t="n">
-        <v>41.02434967191004</v>
+        <v>41.02434967190588</v>
       </c>
       <c r="H13" t="n">
-        <v>41.0750738649803</v>
+        <v>41.07507386497609</v>
       </c>
       <c r="I13" t="n">
-        <v>41.06618784870365</v>
+        <v>41.06618784869945</v>
       </c>
       <c r="J13" t="n">
-        <v>41.0572999732149</v>
+        <v>41.0572999732107</v>
       </c>
       <c r="K13" t="n">
-        <v>41.45946191960276</v>
+        <v>41.45946190478043</v>
       </c>
       <c r="L13" t="n">
-        <v>41.2837403506519</v>
+        <v>41.28374033899675</v>
       </c>
       <c r="M13" t="n">
-        <v>41.107358346146</v>
+        <v>41.10735833738259</v>
       </c>
       <c r="N13" t="n">
-        <v>41.01807399305268</v>
+        <v>41.0180739856554</v>
       </c>
       <c r="O13" t="n">
-        <v>41.01660782296977</v>
+        <v>41.01660781560203</v>
       </c>
       <c r="P13" t="n">
-        <v>41.01514378417211</v>
+        <v>41.01514377681897</v>
       </c>
     </row>
     <row r="14">
@@ -4360,49 +4360,49 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>41.15185920707681</v>
+        <v>41.15185920708498</v>
       </c>
       <c r="C14" t="n">
-        <v>41.13524233969321</v>
+        <v>41.13524233970122</v>
       </c>
       <c r="D14" t="n">
-        <v>41.11882631818459</v>
+        <v>41.11882631819251</v>
       </c>
       <c r="E14" t="n">
-        <v>41.09442372465419</v>
+        <v>41.09442372466202</v>
       </c>
       <c r="F14" t="n">
-        <v>41.06195220846736</v>
+        <v>41.06195220847512</v>
       </c>
       <c r="G14" t="n">
-        <v>41.0295160970623</v>
+        <v>41.02951609707</v>
       </c>
       <c r="H14" t="n">
-        <v>41.10415920409287</v>
+        <v>41.10415920410076</v>
       </c>
       <c r="I14" t="n">
-        <v>41.09108596229031</v>
+        <v>41.09108596229817</v>
       </c>
       <c r="J14" t="n">
-        <v>41.07802444113783</v>
+        <v>41.07802444114569</v>
       </c>
       <c r="K14" t="n">
-        <v>41.67157687418999</v>
+        <v>41.67157706391707</v>
       </c>
       <c r="L14" t="n">
-        <v>41.40984651222894</v>
+        <v>41.40984665535934</v>
       </c>
       <c r="M14" t="n">
-        <v>41.15044059167649</v>
+        <v>41.15044069284241</v>
       </c>
       <c r="N14" t="n">
-        <v>41.01952658770337</v>
+        <v>41.01952666908989</v>
       </c>
       <c r="O14" t="n">
-        <v>41.01738222554596</v>
+        <v>41.0173823065044</v>
       </c>
       <c r="P14" t="n">
-        <v>41.01523964964191</v>
+        <v>41.01523973038876</v>
       </c>
     </row>
     <row r="15">
@@ -4410,49 +4410,49 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>41.20443761021159</v>
+        <v>41.20443761021122</v>
       </c>
       <c r="C15" t="n">
-        <v>41.18152442725505</v>
+        <v>41.1815244272548</v>
       </c>
       <c r="D15" t="n">
-        <v>41.15888631219126</v>
+        <v>41.15888631219106</v>
       </c>
       <c r="E15" t="n">
-        <v>41.12522867889115</v>
+        <v>41.12522867889104</v>
       </c>
       <c r="F15" t="n">
-        <v>41.08043398466164</v>
+        <v>41.08043398466159</v>
       </c>
       <c r="G15" t="n">
-        <v>41.03567583517206</v>
+        <v>41.03567583517205</v>
       </c>
       <c r="H15" t="n">
-        <v>41.1386575891668</v>
+        <v>41.13865758916664</v>
       </c>
       <c r="I15" t="n">
-        <v>41.12062479378498</v>
+        <v>41.12062479378483</v>
       </c>
       <c r="J15" t="n">
-        <v>41.10260621137138</v>
+        <v>41.10260621137122</v>
       </c>
       <c r="K15" t="n">
-        <v>41.91655319314531</v>
+        <v>41.91655307087921</v>
       </c>
       <c r="L15" t="n">
-        <v>41.55762661812852</v>
+        <v>41.55762654950566</v>
       </c>
       <c r="M15" t="n">
-        <v>41.20105677018029</v>
+        <v>41.20105674792516</v>
       </c>
       <c r="N15" t="n">
-        <v>41.020688772886</v>
+        <v>41.0206887722214</v>
       </c>
       <c r="O15" t="n">
-        <v>41.01773595724944</v>
+        <v>41.01773595705055</v>
       </c>
       <c r="P15" t="n">
-        <v>41.01478394850984</v>
+        <v>41.01478394854317</v>
       </c>
     </row>
     <row r="16">
@@ -4460,10 +4460,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>41.2032014249905</v>
+        <v>41.20320142499052</v>
       </c>
       <c r="C16" t="n">
-        <v>41.1808987515456</v>
+        <v>41.18089875154561</v>
       </c>
       <c r="D16" t="n">
         <v>41.15858015934338</v>
@@ -4475,34 +4475,34 @@
         <v>41.08040476569865</v>
       </c>
       <c r="G16" t="n">
-        <v>41.03567502122672</v>
+        <v>41.03567502122673</v>
       </c>
       <c r="H16" t="n">
         <v>41.13841986692496</v>
       </c>
       <c r="I16" t="n">
-        <v>41.12042774292671</v>
+        <v>41.1204277429267</v>
       </c>
       <c r="J16" t="n">
-        <v>41.10242760303396</v>
+        <v>41.10242760303395</v>
       </c>
       <c r="K16" t="n">
-        <v>41.90693699785469</v>
+        <v>41.90693700233071</v>
       </c>
       <c r="L16" t="n">
-        <v>41.55546084726008</v>
+        <v>41.55546084828651</v>
       </c>
       <c r="M16" t="n">
-        <v>41.20093286403394</v>
+        <v>41.20093286410667</v>
       </c>
       <c r="N16" t="n">
-        <v>41.02066504528798</v>
+        <v>41.02066504528743</v>
       </c>
       <c r="O16" t="n">
-        <v>41.01771207556712</v>
+        <v>41.01771207556611</v>
       </c>
       <c r="P16" t="n">
-        <v>41.01475882619692</v>
+        <v>41.014758826196</v>
       </c>
     </row>
     <row r="17">
@@ -4531,28 +4531,28 @@
         <v>41.1037863431361</v>
       </c>
       <c r="I17" t="n">
-        <v>41.09077664577869</v>
+        <v>41.09077664577868</v>
       </c>
       <c r="J17" t="n">
-        <v>41.07774395769543</v>
+        <v>41.07774395769542</v>
       </c>
       <c r="K17" t="n">
-        <v>41.65409095781698</v>
+        <v>41.65409095778313</v>
       </c>
       <c r="L17" t="n">
-        <v>41.40469085236927</v>
+        <v>41.40469085236841</v>
       </c>
       <c r="M17" t="n">
-        <v>41.14910673356702</v>
+        <v>41.14910673356783</v>
       </c>
       <c r="N17" t="n">
-        <v>41.01863967581731</v>
+        <v>41.01863967581782</v>
       </c>
       <c r="O17" t="n">
-        <v>41.01650133993673</v>
+        <v>41.01650133993723</v>
       </c>
       <c r="P17" t="n">
-        <v>41.01435993017657</v>
+        <v>41.01435993017705</v>
       </c>
     </row>
     <row r="18">
@@ -4560,49 +4560,49 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>41.1063769757456</v>
+        <v>41.10637697574559</v>
       </c>
       <c r="C18" t="n">
         <v>41.09569861380906</v>
       </c>
       <c r="D18" t="n">
-        <v>41.08485250413821</v>
+        <v>41.08485250413819</v>
       </c>
       <c r="E18" t="n">
-        <v>41.06840239041622</v>
+        <v>41.06840239041621</v>
       </c>
       <c r="F18" t="n">
-        <v>41.04640622624165</v>
+        <v>41.04640622624164</v>
       </c>
       <c r="G18" t="n">
-        <v>41.02434806768479</v>
+        <v>41.02434806768478</v>
       </c>
       <c r="H18" t="n">
-        <v>41.0749328239471</v>
+        <v>41.07493282394709</v>
       </c>
       <c r="I18" t="n">
-        <v>41.06607067764573</v>
+        <v>41.06607067764571</v>
       </c>
       <c r="J18" t="n">
-        <v>41.05719363856713</v>
+        <v>41.05719363856712</v>
       </c>
       <c r="K18" t="n">
-        <v>41.4509631622884</v>
+        <v>41.45096316228803</v>
       </c>
       <c r="L18" t="n">
-        <v>41.28037635877394</v>
+        <v>41.28037635877374</v>
       </c>
       <c r="M18" t="n">
-        <v>41.10589033241159</v>
+        <v>41.10589033241158</v>
       </c>
       <c r="N18" t="n">
-        <v>41.01698802833902</v>
+        <v>41.01698802833909</v>
       </c>
       <c r="O18" t="n">
-        <v>41.01552873374715</v>
+        <v>41.01552873374721</v>
       </c>
       <c r="P18" t="n">
-        <v>41.01406742381443</v>
+        <v>41.0140674238145</v>
       </c>
     </row>
     <row r="19">
@@ -4610,7 +4610,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>41.10709718135496</v>
+        <v>41.10709718135497</v>
       </c>
       <c r="C19" t="n">
         <v>41.09606613366235</v>
@@ -4622,37 +4622,37 @@
         <v>41.06848769247966</v>
       </c>
       <c r="F19" t="n">
-        <v>41.04642457610344</v>
+        <v>41.04642457610345</v>
       </c>
       <c r="G19" t="n">
-        <v>41.02434967191003</v>
+        <v>41.02434967191004</v>
       </c>
       <c r="H19" t="n">
         <v>41.0750738649803</v>
       </c>
       <c r="I19" t="n">
-        <v>41.06618784870365</v>
+        <v>41.06618784870366</v>
       </c>
       <c r="J19" t="n">
         <v>41.0572999732149</v>
       </c>
       <c r="K19" t="n">
-        <v>41.45946191960304</v>
+        <v>41.45946191960315</v>
       </c>
       <c r="L19" t="n">
-        <v>41.28374035065208</v>
+        <v>41.28374035065217</v>
       </c>
       <c r="M19" t="n">
-        <v>41.10735834614611</v>
+        <v>41.10735834614619</v>
       </c>
       <c r="N19" t="n">
-        <v>41.01807399305275</v>
+        <v>41.01807399305284</v>
       </c>
       <c r="O19" t="n">
-        <v>41.01660782296985</v>
+        <v>41.01660782296993</v>
       </c>
       <c r="P19" t="n">
-        <v>41.01514378417219</v>
+        <v>41.01514378417227</v>
       </c>
     </row>
     <row r="20">
@@ -4666,7 +4666,7 @@
         <v>41.13524233969321</v>
       </c>
       <c r="D20" t="n">
-        <v>41.11882631818459</v>
+        <v>41.11882631818458</v>
       </c>
       <c r="E20" t="n">
         <v>41.09442372465418</v>
@@ -4678,7 +4678,7 @@
         <v>41.02951609706228</v>
       </c>
       <c r="H20" t="n">
-        <v>41.10415920409287</v>
+        <v>41.10415920409286</v>
       </c>
       <c r="I20" t="n">
         <v>41.09108596229029</v>
@@ -4687,22 +4687,22 @@
         <v>41.07802444113782</v>
       </c>
       <c r="K20" t="n">
-        <v>41.67157687420129</v>
+        <v>41.67157687424785</v>
       </c>
       <c r="L20" t="n">
-        <v>41.40984651223761</v>
+        <v>41.40984651227321</v>
       </c>
       <c r="M20" t="n">
-        <v>41.15044059168276</v>
+        <v>41.15044059170847</v>
       </c>
       <c r="N20" t="n">
-        <v>41.01952658770852</v>
+        <v>41.01952658772957</v>
       </c>
       <c r="O20" t="n">
-        <v>41.01738222555107</v>
+        <v>41.01738222557202</v>
       </c>
       <c r="P20" t="n">
-        <v>41.01523964964702</v>
+        <v>41.01523964966792</v>
       </c>
     </row>
     <row r="21">
@@ -4716,7 +4716,7 @@
         <v>41.18152442725505</v>
       </c>
       <c r="D21" t="n">
-        <v>41.15888631219125</v>
+        <v>41.15888631219124</v>
       </c>
       <c r="E21" t="n">
         <v>41.12522867889115</v>
@@ -4737,22 +4737,22 @@
         <v>41.10260621137138</v>
       </c>
       <c r="K21" t="n">
-        <v>41.91655319313763</v>
+        <v>41.91655319310591</v>
       </c>
       <c r="L21" t="n">
-        <v>41.5576266181242</v>
+        <v>41.55762661810633</v>
       </c>
       <c r="M21" t="n">
-        <v>41.2010567701789</v>
+        <v>41.20105677017305</v>
       </c>
       <c r="N21" t="n">
-        <v>41.02068877288596</v>
+        <v>41.02068877288571</v>
       </c>
       <c r="O21" t="n">
-        <v>41.01773595724941</v>
+        <v>41.0177359572493</v>
       </c>
       <c r="P21" t="n">
-        <v>41.01478394850985</v>
+        <v>41.01478394850979</v>
       </c>
     </row>
     <row r="22">
@@ -4760,49 +4760,49 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>41.20320142499051</v>
+        <v>41.2032014249905</v>
       </c>
       <c r="C22" t="n">
-        <v>41.18089875154561</v>
+        <v>41.18089875154559</v>
       </c>
       <c r="D22" t="n">
-        <v>41.15858015934339</v>
+        <v>41.15858015934337</v>
       </c>
       <c r="E22" t="n">
-        <v>41.12508580227969</v>
+        <v>41.12508580227968</v>
       </c>
       <c r="F22" t="n">
-        <v>41.08040476569866</v>
+        <v>41.08040476569865</v>
       </c>
       <c r="G22" t="n">
-        <v>41.03567502122673</v>
+        <v>41.03567502122672</v>
       </c>
       <c r="H22" t="n">
-        <v>41.13841986692496</v>
+        <v>41.13841986692494</v>
       </c>
       <c r="I22" t="n">
-        <v>41.12042774292671</v>
+        <v>41.12042774292669</v>
       </c>
       <c r="J22" t="n">
-        <v>41.10242760303396</v>
+        <v>41.10242760303395</v>
       </c>
       <c r="K22" t="n">
-        <v>41.90693699785498</v>
+        <v>41.90693699785623</v>
       </c>
       <c r="L22" t="n">
-        <v>41.55546084726016</v>
+        <v>41.55546084726047</v>
       </c>
       <c r="M22" t="n">
-        <v>41.20093286403396</v>
+        <v>41.20093286403399</v>
       </c>
       <c r="N22" t="n">
-        <v>41.02066504528798</v>
+        <v>41.02066504528797</v>
       </c>
       <c r="O22" t="n">
-        <v>41.01771207556712</v>
+        <v>41.01771207556711</v>
       </c>
       <c r="P22" t="n">
-        <v>41.01475882619692</v>
+        <v>41.01475882619691</v>
       </c>
     </row>
     <row r="23">
@@ -4828,7 +4828,7 @@
         <v>41.02951385477414</v>
       </c>
       <c r="H23" t="n">
-        <v>41.1037863431361</v>
+        <v>41.10378634313611</v>
       </c>
       <c r="I23" t="n">
         <v>41.09077664577869</v>
@@ -4837,22 +4837,22 @@
         <v>41.07774395769543</v>
       </c>
       <c r="K23" t="n">
-        <v>41.65409095781661</v>
+        <v>41.65409095781777</v>
       </c>
       <c r="L23" t="n">
-        <v>41.40469085236899</v>
+        <v>41.40469085236988</v>
       </c>
       <c r="M23" t="n">
-        <v>41.14910673356682</v>
+        <v>41.14910673356747</v>
       </c>
       <c r="N23" t="n">
-        <v>41.01863967581715</v>
+        <v>41.01863967581768</v>
       </c>
       <c r="O23" t="n">
-        <v>41.01650133993657</v>
+        <v>41.01650133993709</v>
       </c>
       <c r="P23" t="n">
-        <v>41.01435993017641</v>
+        <v>41.01435993017693</v>
       </c>
     </row>
     <row r="24">
@@ -4866,43 +4866,43 @@
         <v>41.09569861380906</v>
       </c>
       <c r="D24" t="n">
-        <v>41.08485250413821</v>
+        <v>41.0848525041382</v>
       </c>
       <c r="E24" t="n">
-        <v>41.06840239041622</v>
+        <v>41.06840239041621</v>
       </c>
       <c r="F24" t="n">
-        <v>41.04640622624165</v>
+        <v>41.04640622624164</v>
       </c>
       <c r="G24" t="n">
-        <v>41.02434806768479</v>
+        <v>41.02434806768478</v>
       </c>
       <c r="H24" t="n">
-        <v>41.07493282394711</v>
+        <v>41.07493282394709</v>
       </c>
       <c r="I24" t="n">
-        <v>41.06607067764573</v>
+        <v>41.06607067764572</v>
       </c>
       <c r="J24" t="n">
         <v>41.05719363856713</v>
       </c>
       <c r="K24" t="n">
-        <v>41.45096316228846</v>
+        <v>41.45096316228804</v>
       </c>
       <c r="L24" t="n">
-        <v>41.28037635877394</v>
+        <v>41.28037635877374</v>
       </c>
       <c r="M24" t="n">
-        <v>41.10589033241156</v>
+        <v>41.10589033241154</v>
       </c>
       <c r="N24" t="n">
-        <v>41.01698802833896</v>
+        <v>41.01698802833904</v>
       </c>
       <c r="O24" t="n">
-        <v>41.0155287337471</v>
+        <v>41.01552873374717</v>
       </c>
       <c r="P24" t="n">
-        <v>41.01406742381437</v>
+        <v>41.01406742381445</v>
       </c>
     </row>
     <row r="25">
@@ -4910,7 +4910,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>41.10709718135497</v>
+        <v>41.10709718135496</v>
       </c>
       <c r="C25" t="n">
         <v>41.09606613366235</v>
@@ -4919,40 +4919,40 @@
         <v>41.08503372206491</v>
       </c>
       <c r="E25" t="n">
-        <v>41.06848769247966</v>
+        <v>41.06848769247965</v>
       </c>
       <c r="F25" t="n">
-        <v>41.04642457610345</v>
+        <v>41.04642457610344</v>
       </c>
       <c r="G25" t="n">
-        <v>41.02434967191004</v>
+        <v>41.02434967191003</v>
       </c>
       <c r="H25" t="n">
         <v>41.0750738649803</v>
       </c>
       <c r="I25" t="n">
-        <v>41.06618784870365</v>
+        <v>41.06618784870366</v>
       </c>
       <c r="J25" t="n">
         <v>41.0572999732149</v>
       </c>
       <c r="K25" t="n">
-        <v>41.45946191960325</v>
+        <v>41.45946191960339</v>
       </c>
       <c r="L25" t="n">
-        <v>41.28374035065223</v>
+        <v>41.28374035065236</v>
       </c>
       <c r="M25" t="n">
-        <v>41.10735834614622</v>
+        <v>41.10735834614633</v>
       </c>
       <c r="N25" t="n">
-        <v>41.01807399305283</v>
+        <v>41.01807399305294</v>
       </c>
       <c r="O25" t="n">
-        <v>41.01660782296992</v>
+        <v>41.01660782297003</v>
       </c>
       <c r="P25" t="n">
-        <v>41.01514378417227</v>
+        <v>41.01514378417237</v>
       </c>
     </row>
     <row r="26">
@@ -4960,49 +4960,49 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>41.15185920707682</v>
+        <v>41.1518592070768</v>
       </c>
       <c r="C26" t="n">
-        <v>41.13524233969321</v>
+        <v>41.1352423396932</v>
       </c>
       <c r="D26" t="n">
-        <v>41.11882631818459</v>
+        <v>41.11882631818458</v>
       </c>
       <c r="E26" t="n">
         <v>41.09442372465418</v>
       </c>
       <c r="F26" t="n">
-        <v>41.06195220846737</v>
+        <v>41.06195220846735</v>
       </c>
       <c r="G26" t="n">
-        <v>41.02951609706229</v>
+        <v>41.02951609706228</v>
       </c>
       <c r="H26" t="n">
-        <v>41.10415920409287</v>
+        <v>41.10415920409286</v>
       </c>
       <c r="I26" t="n">
         <v>41.09108596229029</v>
       </c>
       <c r="J26" t="n">
-        <v>41.07802444113783</v>
+        <v>41.07802444113781</v>
       </c>
       <c r="K26" t="n">
-        <v>41.67157687420799</v>
+        <v>41.6715768742684</v>
       </c>
       <c r="L26" t="n">
-        <v>41.40984651224276</v>
+        <v>41.40984651228895</v>
       </c>
       <c r="M26" t="n">
-        <v>41.1504405916865</v>
+        <v>41.15044059171986</v>
       </c>
       <c r="N26" t="n">
-        <v>41.01952658771159</v>
+        <v>41.01952658773889</v>
       </c>
       <c r="O26" t="n">
-        <v>41.01738222555412</v>
+        <v>41.01738222558131</v>
       </c>
       <c r="P26" t="n">
-        <v>41.01523964965006</v>
+        <v>41.01523964967718</v>
       </c>
     </row>
   </sheetData>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02698522722773939</v>
+        <v>0.0269852636222802</v>
       </c>
     </row>
     <row r="4">
@@ -5047,7 +5047,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>94.42578653320632</v>
+        <v>94.42578631815329</v>
       </c>
     </row>
     <row r="5">
@@ -5055,7 +5055,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>155.4480914685664</v>
+        <v>155.4480920179005</v>
       </c>
     </row>
     <row r="6">
@@ -5063,7 +5063,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>150.3306578382298</v>
+        <v>150.3306574321826</v>
       </c>
     </row>
     <row r="7">
@@ -5071,7 +5071,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>152.8534573713015</v>
+        <v>152.8534574053213</v>
       </c>
     </row>
     <row r="8">
@@ -5079,7 +5079,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>189.0577346803977</v>
+        <v>189.0577440652056</v>
       </c>
     </row>
     <row r="9">
@@ -5087,7 +5087,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>222.0953279622579</v>
+        <v>222.0953172817173</v>
       </c>
     </row>
     <row r="10">
@@ -5095,7 +5095,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>217.2799290862193</v>
+        <v>217.2799299891331</v>
       </c>
     </row>
     <row r="11">
@@ -5103,7 +5103,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>180.1480195178157</v>
+        <v>180.1480199655551</v>
       </c>
     </row>
     <row r="12">
@@ -5111,7 +5111,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>148.6444623753718</v>
+        <v>148.644462320827</v>
       </c>
     </row>
     <row r="13">
@@ -5119,7 +5119,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>152.7772824029994</v>
+        <v>152.7772817748634</v>
       </c>
     </row>
     <row r="14">
@@ -5127,7 +5127,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>189.0546872549448</v>
+        <v>189.0546950059771</v>
       </c>
     </row>
     <row r="15">
@@ -5135,7 +5135,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>222.0955941710272</v>
+        <v>222.0955860727515</v>
       </c>
     </row>
     <row r="16">
@@ -5143,7 +5143,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>217.2799552172739</v>
+        <v>217.2799562186515</v>
       </c>
     </row>
     <row r="17">
@@ -5151,7 +5151,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>180.1480185712546</v>
+        <v>180.1480185461099</v>
       </c>
     </row>
     <row r="18">
@@ -5159,7 +5159,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>148.644462382495</v>
+        <v>148.6444623826164</v>
       </c>
     </row>
     <row r="19">
@@ -5167,7 +5167,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>152.7772824030114</v>
+        <v>152.7772824030175</v>
       </c>
     </row>
     <row r="20">
@@ -5175,7 +5175,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>189.0546872553826</v>
+        <v>189.0546872571979</v>
       </c>
     </row>
     <row r="21">
@@ -5183,7 +5183,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>222.0955941705216</v>
+        <v>222.0955941684405</v>
       </c>
     </row>
     <row r="22">
@@ -5191,7 +5191,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>217.279955217338</v>
+        <v>217.2799552176024</v>
       </c>
     </row>
     <row r="23">
@@ -5199,7 +5199,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>180.1480185712385</v>
+        <v>180.1480185712783</v>
       </c>
     </row>
     <row r="24">
@@ -5207,7 +5207,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>148.6444623825056</v>
+        <v>148.6444623824613</v>
       </c>
     </row>
     <row r="25">
@@ -5215,7 +5215,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>152.7772824030219</v>
+        <v>152.7772824030285</v>
       </c>
     </row>
     <row r="26">
@@ -5223,7 +5223,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>189.0546872556404</v>
+        <v>189.0546872579964</v>
       </c>
     </row>
   </sheetData>
@@ -5673,79 +5673,79 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>39.95069569297092</v>
+        <v>39.95069569313122</v>
       </c>
       <c r="C3" t="n">
-        <v>39.95069566564661</v>
+        <v>39.95069566580689</v>
       </c>
       <c r="D3" t="n">
-        <v>39.94899050237277</v>
+        <v>39.94899050253238</v>
       </c>
       <c r="E3" t="n">
-        <v>39.94224390733372</v>
+        <v>39.94224390749251</v>
       </c>
       <c r="F3" t="n">
-        <v>39.93469536009938</v>
+        <v>39.934695360258</v>
       </c>
       <c r="G3" t="n">
-        <v>39.93469536009938</v>
+        <v>39.934695360258</v>
       </c>
       <c r="H3" t="n">
-        <v>39.92497447816874</v>
+        <v>39.92497447832666</v>
       </c>
       <c r="I3" t="n">
-        <v>39.89906778751605</v>
+        <v>39.89906778767296</v>
       </c>
       <c r="J3" t="n">
-        <v>39.86576536178672</v>
+        <v>39.86576536194313</v>
       </c>
       <c r="K3" t="n">
-        <v>39.84493540193158</v>
+        <v>39.84493540208808</v>
       </c>
       <c r="L3" t="n">
-        <v>39.93469536009938</v>
+        <v>39.934695360258</v>
       </c>
       <c r="M3" t="n">
-        <v>39.92832570226908</v>
+        <v>39.92832570242758</v>
       </c>
       <c r="N3" t="n">
-        <v>39.91430940773287</v>
+        <v>39.91430940789122</v>
       </c>
       <c r="O3" t="n">
-        <v>39.8989502602218</v>
+        <v>39.89895026038009</v>
       </c>
       <c r="P3" t="n">
-        <v>39.89056662049849</v>
+        <v>39.89056662065681</v>
       </c>
       <c r="Q3" t="n">
-        <v>40.23655487111707</v>
+        <v>40.23655487148834</v>
       </c>
       <c r="R3" t="n">
-        <v>40.23655452732167</v>
+        <v>40.23655452769236</v>
       </c>
       <c r="S3" t="n">
-        <v>40.23409492910047</v>
+        <v>40.2340949294555</v>
       </c>
       <c r="T3" t="n">
-        <v>40.22570015582729</v>
+        <v>40.22570015615535</v>
       </c>
       <c r="U3" t="n">
-        <v>40.21766958306318</v>
+        <v>40.21766958337388</v>
       </c>
       <c r="V3" t="n">
-        <v>40.21766958306318</v>
+        <v>40.21766958337388</v>
       </c>
       <c r="W3" t="n">
-        <v>40.2181000782167</v>
+        <v>40.21810007852667</v>
       </c>
       <c r="X3" t="n">
-        <v>40.21811062020157</v>
+        <v>40.21811062051146</v>
       </c>
       <c r="Y3" t="n">
-        <v>40.21747228503749</v>
+        <v>40.21747228534695</v>
       </c>
       <c r="Z3" t="n">
-        <v>40.21611074903505</v>
+        <v>40.21611074934453</v>
       </c>
     </row>
     <row r="4">
@@ -5753,79 +5753,79 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.13916821569438</v>
+        <v>39.13916821569</v>
       </c>
       <c r="C4" t="n">
-        <v>39.13562648131382</v>
+        <v>39.13562648131044</v>
       </c>
       <c r="D4" t="n">
-        <v>39.12534758103376</v>
+        <v>39.12534758103209</v>
       </c>
       <c r="E4" t="n">
-        <v>39.1112336251942</v>
+        <v>39.11123362519375</v>
       </c>
       <c r="F4" t="n">
-        <v>39.10193276142233</v>
+        <v>39.10193276142212</v>
       </c>
       <c r="G4" t="n">
-        <v>39.10193276142233</v>
+        <v>39.10193276142212</v>
       </c>
       <c r="H4" t="n">
-        <v>39.0861469623058</v>
+        <v>39.08614696230651</v>
       </c>
       <c r="I4" t="n">
-        <v>39.05113960226466</v>
+        <v>39.05113960226667</v>
       </c>
       <c r="J4" t="n">
-        <v>39.01245845696457</v>
+        <v>39.01245845696726</v>
       </c>
       <c r="K4" t="n">
-        <v>38.99117312379071</v>
+        <v>38.99117312379339</v>
       </c>
       <c r="L4" t="n">
-        <v>39.10193276142233</v>
+        <v>39.10193276142212</v>
       </c>
       <c r="M4" t="n">
-        <v>39.09429019619061</v>
+        <v>39.09429019619057</v>
       </c>
       <c r="N4" t="n">
-        <v>39.07840663998984</v>
+        <v>39.07840663999002</v>
       </c>
       <c r="O4" t="n">
-        <v>39.06190819530266</v>
+        <v>39.06190819530297</v>
       </c>
       <c r="P4" t="n">
-        <v>39.05334499821428</v>
+        <v>39.05334499821458</v>
       </c>
       <c r="Q4" t="n">
-        <v>39.46143605351828</v>
+        <v>39.461436050242</v>
       </c>
       <c r="R4" t="n">
-        <v>39.45327088639115</v>
+        <v>39.45327088328851</v>
       </c>
       <c r="S4" t="n">
-        <v>39.42999951458239</v>
+        <v>39.42999951186078</v>
       </c>
       <c r="T4" t="n">
-        <v>39.39831208768413</v>
+        <v>39.39831208537265</v>
       </c>
       <c r="U4" t="n">
-        <v>39.37745396162289</v>
+        <v>39.3774539595298</v>
       </c>
       <c r="V4" t="n">
-        <v>39.37745396162289</v>
+        <v>39.3774539595298</v>
       </c>
       <c r="W4" t="n">
-        <v>39.3775820218693</v>
+        <v>39.37758201977927</v>
       </c>
       <c r="X4" t="n">
-        <v>39.37752142773209</v>
+        <v>39.37752142564393</v>
       </c>
       <c r="Y4" t="n">
-        <v>39.37661870151706</v>
+        <v>39.37661869943272</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.37522833207339</v>
+        <v>39.37522832998898</v>
       </c>
     </row>
     <row r="5">
@@ -5833,25 +5833,25 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.12900719675705</v>
+        <v>39.12900719675702</v>
       </c>
       <c r="C5" t="n">
-        <v>39.12147321361386</v>
+        <v>39.12147321361382</v>
       </c>
       <c r="D5" t="n">
-        <v>39.10632882167931</v>
+        <v>39.10632882167927</v>
       </c>
       <c r="E5" t="n">
-        <v>39.09107944772694</v>
+        <v>39.09107944772689</v>
       </c>
       <c r="F5" t="n">
-        <v>39.08339907191833</v>
+        <v>39.08339907191829</v>
       </c>
       <c r="G5" t="n">
-        <v>39.08339907191833</v>
+        <v>39.08339907191829</v>
       </c>
       <c r="H5" t="n">
-        <v>39.06808235638444</v>
+        <v>39.06808235638442</v>
       </c>
       <c r="I5" t="n">
         <v>39.0373661223196</v>
@@ -5863,49 +5863,49 @@
         <v>38.99115070162895</v>
       </c>
       <c r="L5" t="n">
-        <v>39.08339907191833</v>
+        <v>39.08339907191829</v>
       </c>
       <c r="M5" t="n">
-        <v>39.07721226211807</v>
+        <v>39.07721226211802</v>
       </c>
       <c r="N5" t="n">
-        <v>39.06482581556626</v>
+        <v>39.06482581556621</v>
       </c>
       <c r="O5" t="n">
-        <v>39.05242679461134</v>
+        <v>39.0524267946113</v>
       </c>
       <c r="P5" t="n">
-        <v>39.04622229593637</v>
+        <v>39.04622229593633</v>
       </c>
       <c r="Q5" t="n">
-        <v>39.31078975050339</v>
+        <v>39.31078976053372</v>
       </c>
       <c r="R5" t="n">
-        <v>39.26423043417275</v>
+        <v>39.26423044309323</v>
       </c>
       <c r="S5" t="n">
-        <v>39.16730807833645</v>
+        <v>39.16730808522593</v>
       </c>
       <c r="T5" t="n">
-        <v>39.06488154757029</v>
+        <v>39.06488155255983</v>
       </c>
       <c r="U5" t="n">
-        <v>39.01008396879591</v>
+        <v>39.01008397287594</v>
       </c>
       <c r="V5" t="n">
-        <v>39.01008396879591</v>
+        <v>39.01008397287594</v>
       </c>
       <c r="W5" t="n">
-        <v>39.00996667774935</v>
+        <v>39.00996668182187</v>
       </c>
       <c r="X5" t="n">
-        <v>39.00933276486</v>
+        <v>39.00933276891591</v>
       </c>
       <c r="Y5" t="n">
-        <v>39.00809852409844</v>
+        <v>39.00809852814282</v>
       </c>
       <c r="Z5" t="n">
-        <v>39.00708050436342</v>
+        <v>39.0070805084079</v>
       </c>
     </row>
     <row r="6">
@@ -5913,7 +5913,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.08463060356092</v>
+        <v>39.08463060356091</v>
       </c>
       <c r="C6" t="n">
         <v>39.07964449427602</v>
@@ -5931,16 +5931,16 @@
         <v>39.05395686069564</v>
       </c>
       <c r="H6" t="n">
-        <v>39.0435434785932</v>
+        <v>39.04354347859321</v>
       </c>
       <c r="I6" t="n">
-        <v>39.02263182064597</v>
+        <v>39.02263182064598</v>
       </c>
       <c r="J6" t="n">
-        <v>39.00166122743691</v>
+        <v>39.00166122743692</v>
       </c>
       <c r="K6" t="n">
-        <v>38.99116233330937</v>
+        <v>38.99116233330938</v>
       </c>
       <c r="L6" t="n">
         <v>39.05395686069564</v>
@@ -5949,43 +5949,43 @@
         <v>39.04975192299509</v>
       </c>
       <c r="N6" t="n">
-        <v>39.04132672791816</v>
+        <v>39.04132672791817</v>
       </c>
       <c r="O6" t="n">
-        <v>39.03288736844758</v>
+        <v>39.03288736844757</v>
       </c>
       <c r="P6" t="n">
-        <v>39.02866163904732</v>
+        <v>39.02866163904731</v>
       </c>
       <c r="Q6" t="n">
-        <v>39.48410927996271</v>
+        <v>39.48410927465326</v>
       </c>
       <c r="R6" t="n">
-        <v>39.40105675766028</v>
+        <v>39.40105675344486</v>
       </c>
       <c r="S6" t="n">
-        <v>39.23811425027212</v>
+        <v>39.2381142478954</v>
       </c>
       <c r="T6" t="n">
-        <v>39.07630577407528</v>
+        <v>39.07630577330598</v>
       </c>
       <c r="U6" t="n">
-        <v>38.99521280149611</v>
+        <v>38.99521280146278</v>
       </c>
       <c r="V6" t="n">
-        <v>38.99521280149611</v>
+        <v>38.99521280146278</v>
       </c>
       <c r="W6" t="n">
-        <v>38.9945652822044</v>
+        <v>38.99456528218296</v>
       </c>
       <c r="X6" t="n">
-        <v>38.9932400146824</v>
+        <v>38.99324001467695</v>
       </c>
       <c r="Y6" t="n">
-        <v>38.99188276282596</v>
+        <v>38.99188276282857</v>
       </c>
       <c r="Z6" t="n">
-        <v>38.99118782709248</v>
+        <v>38.99118782709509</v>
       </c>
     </row>
     <row r="7">
@@ -5993,79 +5993,79 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.08557479366659</v>
+        <v>39.08557479366658</v>
       </c>
       <c r="C7" t="n">
-        <v>39.08033042696648</v>
+        <v>39.08033042696649</v>
       </c>
       <c r="D7" t="n">
-        <v>39.06984325889537</v>
+        <v>39.06984325889538</v>
       </c>
       <c r="E7" t="n">
         <v>39.0593547953055</v>
       </c>
       <c r="F7" t="n">
-        <v>39.05410953101514</v>
+        <v>39.05410953101516</v>
       </c>
       <c r="G7" t="n">
-        <v>39.05410953101514</v>
+        <v>39.05410953101516</v>
       </c>
       <c r="H7" t="n">
-        <v>39.04362456025812</v>
+        <v>39.04362456025815</v>
       </c>
       <c r="I7" t="n">
-        <v>39.02264925587096</v>
+        <v>39.02264925587097</v>
       </c>
       <c r="J7" t="n">
-        <v>39.00166274482756</v>
+        <v>39.00166274482757</v>
       </c>
       <c r="K7" t="n">
         <v>38.99116385110808</v>
       </c>
       <c r="L7" t="n">
-        <v>39.05410953101514</v>
+        <v>39.05410953101516</v>
       </c>
       <c r="M7" t="n">
-        <v>39.04988600447134</v>
+        <v>39.04988600447136</v>
       </c>
       <c r="N7" t="n">
-        <v>39.0414381092052</v>
+        <v>39.04143810920522</v>
       </c>
       <c r="O7" t="n">
-        <v>39.03298844638789</v>
+        <v>39.0329884463879</v>
       </c>
       <c r="P7" t="n">
         <v>39.02876272791936</v>
       </c>
       <c r="Q7" t="n">
-        <v>39.4992456538191</v>
+        <v>39.49924565397607</v>
       </c>
       <c r="R7" t="n">
-        <v>39.41558213937028</v>
+        <v>39.41558213943467</v>
       </c>
       <c r="S7" t="n">
-        <v>39.24827601316633</v>
+        <v>39.24827601315568</v>
       </c>
       <c r="T7" t="n">
-        <v>39.08052078245021</v>
+        <v>39.08052078242537</v>
       </c>
       <c r="U7" t="n">
-        <v>38.99633814519908</v>
+        <v>38.99633814517679</v>
       </c>
       <c r="V7" t="n">
-        <v>38.99633814519908</v>
+        <v>38.99633814517679</v>
       </c>
       <c r="W7" t="n">
-        <v>38.99564019954575</v>
+        <v>38.99564019952351</v>
       </c>
       <c r="X7" t="n">
-        <v>38.99424645956583</v>
+        <v>38.99424645954367</v>
       </c>
       <c r="Y7" t="n">
-        <v>38.99285470639101</v>
+        <v>38.99285470636891</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.99215978770511</v>
+        <v>38.992159787683</v>
       </c>
     </row>
     <row r="8">
@@ -6073,79 +6073,79 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>39.13089607063569</v>
+        <v>39.13089607071185</v>
       </c>
       <c r="C8" t="n">
-        <v>39.12288547999484</v>
+        <v>39.12288548007029</v>
       </c>
       <c r="D8" t="n">
-        <v>39.10708789971238</v>
+        <v>39.10708789978688</v>
       </c>
       <c r="E8" t="n">
-        <v>39.09148126268934</v>
+        <v>39.09148126276327</v>
       </c>
       <c r="F8" t="n">
-        <v>39.08375946909357</v>
+        <v>39.08375946916742</v>
       </c>
       <c r="G8" t="n">
-        <v>39.08375946909357</v>
+        <v>39.08375946916742</v>
       </c>
       <c r="H8" t="n">
-        <v>39.06828182795095</v>
+        <v>39.0682818280244</v>
       </c>
       <c r="I8" t="n">
-        <v>39.03741130512316</v>
+        <v>39.03741130519609</v>
       </c>
       <c r="J8" t="n">
-        <v>39.00657444145943</v>
+        <v>39.00657444153214</v>
       </c>
       <c r="K8" t="n">
-        <v>38.99115348853459</v>
+        <v>38.99115348860733</v>
       </c>
       <c r="L8" t="n">
-        <v>39.08375946909357</v>
+        <v>39.08375946916742</v>
       </c>
       <c r="M8" t="n">
-        <v>39.07753730399654</v>
+        <v>39.07753730407033</v>
       </c>
       <c r="N8" t="n">
-        <v>39.06510863244335</v>
+        <v>39.06510863251707</v>
       </c>
       <c r="O8" t="n">
-        <v>39.05269110365884</v>
+        <v>39.05269110373253</v>
       </c>
       <c r="P8" t="n">
-        <v>39.04648664694607</v>
+        <v>39.04648664701978</v>
       </c>
       <c r="Q8" t="n">
-        <v>39.74424748080921</v>
+        <v>39.74424773965874</v>
       </c>
       <c r="R8" t="n">
-        <v>39.61703963367228</v>
+        <v>39.61703986185675</v>
       </c>
       <c r="S8" t="n">
-        <v>39.36818761020951</v>
+        <v>39.36818778461202</v>
       </c>
       <c r="T8" t="n">
-        <v>39.12154601673878</v>
+        <v>39.12154614257276</v>
       </c>
       <c r="U8" t="n">
-        <v>38.99809580177</v>
+        <v>38.9980959050644</v>
       </c>
       <c r="V8" t="n">
-        <v>38.99809580177</v>
+        <v>38.9980959050644</v>
       </c>
       <c r="W8" t="n">
-        <v>38.9970746225618</v>
+        <v>38.9970747254817</v>
       </c>
       <c r="X8" t="n">
-        <v>38.9950357276628</v>
+        <v>38.99503583008657</v>
       </c>
       <c r="Y8" t="n">
-        <v>38.99299866096834</v>
+        <v>38.99299876314708</v>
       </c>
       <c r="Z8" t="n">
-        <v>38.99198025128704</v>
+        <v>38.99198035346841</v>
       </c>
     </row>
     <row r="9">
@@ -6153,79 +6153,79 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39.18391652814331</v>
+        <v>39.18391652813891</v>
       </c>
       <c r="C9" t="n">
-        <v>39.17287152892327</v>
+        <v>39.17287152891971</v>
       </c>
       <c r="D9" t="n">
-        <v>39.15108807004405</v>
+        <v>39.15108807004169</v>
       </c>
       <c r="E9" t="n">
-        <v>39.12956611696053</v>
+        <v>39.12956611695889</v>
       </c>
       <c r="F9" t="n">
-        <v>39.11891700914238</v>
+        <v>39.11891700914086</v>
       </c>
       <c r="G9" t="n">
-        <v>39.11891700914238</v>
+        <v>39.11891700914086</v>
       </c>
       <c r="H9" t="n">
-        <v>39.0975679579824</v>
+        <v>39.09756795798138</v>
       </c>
       <c r="I9" t="n">
-        <v>39.05498184580547</v>
+        <v>39.05498184580511</v>
       </c>
       <c r="J9" t="n">
-        <v>39.01243047654697</v>
+        <v>39.01243047654696</v>
       </c>
       <c r="K9" t="n">
-        <v>38.9911451281142</v>
+        <v>38.99114512811418</v>
       </c>
       <c r="L9" t="n">
-        <v>39.11891700914238</v>
+        <v>39.11891700914086</v>
       </c>
       <c r="M9" t="n">
-        <v>39.11033476193672</v>
+        <v>39.11033476193527</v>
       </c>
       <c r="N9" t="n">
-        <v>39.09319106534058</v>
+        <v>39.09319106533924</v>
       </c>
       <c r="O9" t="n">
-        <v>39.07606088094877</v>
+        <v>39.07606088094749</v>
       </c>
       <c r="P9" t="n">
-        <v>39.06750078376088</v>
+        <v>39.06750078375961</v>
       </c>
       <c r="Q9" t="n">
-        <v>40.02403731565331</v>
+        <v>40.02403712043738</v>
       </c>
       <c r="R9" t="n">
-        <v>39.84987876466714</v>
+        <v>39.84987861039514</v>
       </c>
       <c r="S9" t="n">
-        <v>39.50864882927844</v>
+        <v>39.5086487425447</v>
       </c>
       <c r="T9" t="n">
-        <v>39.1696582217885</v>
+        <v>39.16965819363413</v>
       </c>
       <c r="U9" t="n">
-        <v>38.99958753960236</v>
+        <v>38.99958753831707</v>
       </c>
       <c r="V9" t="n">
-        <v>38.99958753960236</v>
+        <v>38.99958753831707</v>
       </c>
       <c r="W9" t="n">
-        <v>38.99818237237498</v>
+        <v>38.99818237153382</v>
       </c>
       <c r="X9" t="n">
-        <v>38.99537512574861</v>
+        <v>38.99537512549669</v>
       </c>
       <c r="Y9" t="n">
-        <v>38.99256865517498</v>
+        <v>38.99256865521691</v>
       </c>
       <c r="Z9" t="n">
-        <v>38.9911647009987</v>
+        <v>38.99116470104063</v>
       </c>
     </row>
     <row r="10">
@@ -6233,79 +6233,79 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39.1822913410093</v>
+        <v>39.18229134176455</v>
       </c>
       <c r="C10" t="n">
-        <v>39.17169629324959</v>
+        <v>39.17169629399706</v>
       </c>
       <c r="D10" t="n">
-        <v>39.15049324298901</v>
+        <v>39.15049324372551</v>
       </c>
       <c r="E10" t="n">
-        <v>39.12927505883823</v>
+        <v>39.12927505956828</v>
       </c>
       <c r="F10" t="n">
-        <v>39.11865932276821</v>
+        <v>39.11865932349729</v>
       </c>
       <c r="G10" t="n">
-        <v>39.11865932276821</v>
+        <v>39.11865932349729</v>
       </c>
       <c r="H10" t="n">
-        <v>39.09743212583641</v>
+        <v>39.09743212656091</v>
       </c>
       <c r="I10" t="n">
-        <v>39.05495406746984</v>
+        <v>39.05495406818851</v>
       </c>
       <c r="J10" t="n">
-        <v>39.01242970273283</v>
+        <v>39.01242970344899</v>
       </c>
       <c r="K10" t="n">
-        <v>38.99114435387806</v>
+        <v>38.9911443545946</v>
       </c>
       <c r="L10" t="n">
-        <v>39.11865932276821</v>
+        <v>39.11865932349729</v>
       </c>
       <c r="M10" t="n">
-        <v>39.11010876048068</v>
+        <v>39.1101087612091</v>
       </c>
       <c r="N10" t="n">
-        <v>39.09300372998413</v>
+        <v>39.09300373071178</v>
       </c>
       <c r="O10" t="n">
-        <v>39.07589107881312</v>
+        <v>39.07589107954055</v>
       </c>
       <c r="P10" t="n">
-        <v>39.06733094444633</v>
+        <v>39.06733094517392</v>
       </c>
       <c r="Q10" t="n">
-        <v>40.006948105</v>
+        <v>40.00694810153807</v>
       </c>
       <c r="R10" t="n">
-        <v>39.8407343484463</v>
+        <v>39.84073434170426</v>
       </c>
       <c r="S10" t="n">
-        <v>39.50658768416539</v>
+        <v>39.50658767616986</v>
       </c>
       <c r="T10" t="n">
-        <v>39.16953957932113</v>
+        <v>39.1695395729381</v>
       </c>
       <c r="U10" t="n">
-        <v>38.99956339164412</v>
+        <v>38.99956338648367</v>
       </c>
       <c r="V10" t="n">
-        <v>38.99956339164412</v>
+        <v>38.99956338648367</v>
       </c>
       <c r="W10" t="n">
-        <v>38.99815978683475</v>
+        <v>38.9981597816947</v>
       </c>
       <c r="X10" t="n">
-        <v>38.99535241197309</v>
+        <v>38.99535240686144</v>
       </c>
       <c r="Y10" t="n">
-        <v>38.99254477122255</v>
+        <v>38.99254476612533</v>
       </c>
       <c r="Z10" t="n">
-        <v>38.9911408161931</v>
+        <v>38.99114081109568</v>
       </c>
     </row>
     <row r="11">
@@ -6313,79 +6313,79 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>39.12837497755943</v>
+        <v>39.12837497752343</v>
       </c>
       <c r="C11" t="n">
-        <v>39.12105721249613</v>
+        <v>39.12105721246692</v>
       </c>
       <c r="D11" t="n">
-        <v>39.10615884760434</v>
+        <v>39.10615884758482</v>
       </c>
       <c r="E11" t="n">
-        <v>39.09102512735673</v>
+        <v>39.09102512734306</v>
       </c>
       <c r="F11" t="n">
-        <v>39.08335551449781</v>
+        <v>39.08335551448513</v>
       </c>
       <c r="G11" t="n">
-        <v>39.08335551449781</v>
+        <v>39.08335551448513</v>
       </c>
       <c r="H11" t="n">
-        <v>39.06806829779364</v>
+        <v>39.06806829778522</v>
       </c>
       <c r="I11" t="n">
-        <v>39.03736689137853</v>
+        <v>39.03736689137575</v>
       </c>
       <c r="J11" t="n">
         <v>39.00657230979382</v>
       </c>
       <c r="K11" t="n">
-        <v>38.99115135602683</v>
+        <v>38.99115135602685</v>
       </c>
       <c r="L11" t="n">
-        <v>39.08335551449781</v>
+        <v>39.08335551448513</v>
       </c>
       <c r="M11" t="n">
-        <v>39.0771828268517</v>
+        <v>39.07718282683972</v>
       </c>
       <c r="N11" t="n">
-        <v>39.06481456671347</v>
+        <v>39.06481456670243</v>
       </c>
       <c r="O11" t="n">
-        <v>39.05242444939671</v>
+        <v>39.05242444938614</v>
       </c>
       <c r="P11" t="n">
-        <v>39.04621995034832</v>
+        <v>39.04621995033776</v>
       </c>
       <c r="Q11" t="n">
-        <v>39.7149112426338</v>
+        <v>39.71491125067102</v>
       </c>
       <c r="R11" t="n">
-        <v>39.60035492388328</v>
+        <v>39.6003549303562</v>
       </c>
       <c r="S11" t="n">
-        <v>39.36325137602105</v>
+        <v>39.36325137970424</v>
       </c>
       <c r="T11" t="n">
-        <v>39.12026871601282</v>
+        <v>39.12026871721115</v>
       </c>
       <c r="U11" t="n">
-        <v>38.99724835001361</v>
+        <v>38.9972483500695</v>
       </c>
       <c r="V11" t="n">
-        <v>38.99724835001361</v>
+        <v>38.9972483500695</v>
       </c>
       <c r="W11" t="n">
-        <v>38.99623427729053</v>
+        <v>38.99623427732759</v>
       </c>
       <c r="X11" t="n">
-        <v>38.99420137108942</v>
+        <v>38.99420137110148</v>
       </c>
       <c r="Y11" t="n">
-        <v>38.9921655425649</v>
+        <v>38.9921655425645</v>
       </c>
       <c r="Z11" t="n">
-        <v>38.99114711135988</v>
+        <v>38.99114711135947</v>
       </c>
     </row>
     <row r="12">
@@ -6393,40 +6393,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>39.08463320130168</v>
+        <v>39.08463320130206</v>
       </c>
       <c r="C12" t="n">
-        <v>39.07964572949705</v>
+        <v>39.07964572949731</v>
       </c>
       <c r="D12" t="n">
-        <v>39.06949385934568</v>
+        <v>39.06949385934578</v>
       </c>
       <c r="E12" t="n">
-        <v>39.05918251218583</v>
+        <v>39.05918251218586</v>
       </c>
       <c r="F12" t="n">
-        <v>39.05395686630029</v>
+        <v>39.0539568663003</v>
       </c>
       <c r="G12" t="n">
-        <v>39.05395686630029</v>
+        <v>39.0539568663003</v>
       </c>
       <c r="H12" t="n">
-        <v>39.04354346384926</v>
+        <v>39.04354346384925</v>
       </c>
       <c r="I12" t="n">
-        <v>39.02263181055864</v>
+        <v>39.02263181055863</v>
       </c>
       <c r="J12" t="n">
-        <v>39.00166121949061</v>
+        <v>39.00166121949059</v>
       </c>
       <c r="K12" t="n">
-        <v>38.99116232536092</v>
+        <v>38.99116232536091</v>
       </c>
       <c r="L12" t="n">
-        <v>39.05395686630029</v>
+        <v>39.0539568663003</v>
       </c>
       <c r="M12" t="n">
-        <v>39.04975191732103</v>
+        <v>39.04975191732104</v>
       </c>
       <c r="N12" t="n">
         <v>39.04132671511785</v>
@@ -6435,37 +6435,37 @@
         <v>39.03288735441907</v>
       </c>
       <c r="P12" t="n">
-        <v>39.02866162501731</v>
+        <v>39.02866162501729</v>
       </c>
       <c r="Q12" t="n">
-        <v>39.48573310301042</v>
+        <v>39.4857331026936</v>
       </c>
       <c r="R12" t="n">
-        <v>39.40724225062237</v>
+        <v>39.40724225045251</v>
       </c>
       <c r="S12" t="n">
-        <v>39.24506615197648</v>
+        <v>39.24506615193712</v>
       </c>
       <c r="T12" t="n">
-        <v>39.07918307989185</v>
+        <v>39.07918307988916</v>
       </c>
       <c r="U12" t="n">
-        <v>38.99535613975098</v>
+        <v>38.99535613975122</v>
       </c>
       <c r="V12" t="n">
-        <v>38.99535613975098</v>
+        <v>38.99535613975122</v>
       </c>
       <c r="W12" t="n">
-        <v>38.99466406354193</v>
+        <v>38.99466406354223</v>
       </c>
       <c r="X12" t="n">
-        <v>38.9932767188071</v>
+        <v>38.99327671880742</v>
       </c>
       <c r="Y12" t="n">
-        <v>38.99188745809689</v>
+        <v>38.9918874580972</v>
       </c>
       <c r="Z12" t="n">
-        <v>38.99119252244576</v>
+        <v>38.99119252244608</v>
       </c>
     </row>
     <row r="13">
@@ -6473,79 +6473,79 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>39.08557478913145</v>
+        <v>39.08557478912734</v>
       </c>
       <c r="C13" t="n">
-        <v>39.08033042569597</v>
+        <v>39.0803304256919</v>
       </c>
       <c r="D13" t="n">
-        <v>39.06984325879954</v>
+        <v>39.06984325879549</v>
       </c>
       <c r="E13" t="n">
-        <v>39.05935479524497</v>
+        <v>39.05935479524096</v>
       </c>
       <c r="F13" t="n">
-        <v>39.05410953094241</v>
+        <v>39.0541095309384</v>
       </c>
       <c r="G13" t="n">
-        <v>39.05410953094241</v>
+        <v>39.0541095309384</v>
       </c>
       <c r="H13" t="n">
-        <v>39.0436245601332</v>
+        <v>39.04362456012922</v>
       </c>
       <c r="I13" t="n">
-        <v>39.02264925568883</v>
+        <v>39.02264925568488</v>
       </c>
       <c r="J13" t="n">
-        <v>39.00166274462025</v>
+        <v>39.0016627446163</v>
       </c>
       <c r="K13" t="n">
-        <v>38.99116385090071</v>
+        <v>38.99116385089676</v>
       </c>
       <c r="L13" t="n">
-        <v>39.05410953094241</v>
+        <v>39.0541095309384</v>
       </c>
       <c r="M13" t="n">
-        <v>39.04988600439015</v>
+        <v>39.04988600438614</v>
       </c>
       <c r="N13" t="n">
-        <v>39.04143810910998</v>
+        <v>39.04143810910598</v>
       </c>
       <c r="O13" t="n">
-        <v>39.03298844628532</v>
+        <v>39.03298844628132</v>
       </c>
       <c r="P13" t="n">
-        <v>39.02876272781678</v>
+        <v>39.02876272781278</v>
       </c>
       <c r="Q13" t="n">
-        <v>39.49877863180064</v>
+        <v>39.49877861602967</v>
       </c>
       <c r="R13" t="n">
-        <v>39.41532198056873</v>
+        <v>39.4153219664772</v>
       </c>
       <c r="S13" t="n">
-        <v>39.24826428376215</v>
+        <v>39.24826427268165</v>
       </c>
       <c r="T13" t="n">
-        <v>39.0805787138756</v>
+        <v>39.08057870554426</v>
       </c>
       <c r="U13" t="n">
-        <v>38.99639445855772</v>
+        <v>38.99639445150398</v>
       </c>
       <c r="V13" t="n">
-        <v>38.99639445855772</v>
+        <v>38.99639445150398</v>
       </c>
       <c r="W13" t="n">
-        <v>38.99569648525854</v>
+        <v>38.99569647822597</v>
       </c>
       <c r="X13" t="n">
-        <v>38.99430260402563</v>
+        <v>38.99430259702115</v>
       </c>
       <c r="Y13" t="n">
-        <v>38.99291074899592</v>
+        <v>38.99291074200533</v>
       </c>
       <c r="Z13" t="n">
-        <v>38.99221583129296</v>
+        <v>38.99221582430224</v>
       </c>
     </row>
     <row r="14">
@@ -6553,79 +6553,79 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>39.1308960707161</v>
+        <v>39.13089607072397</v>
       </c>
       <c r="C14" t="n">
-        <v>39.12288548007054</v>
+        <v>39.1228854800783</v>
       </c>
       <c r="D14" t="n">
-        <v>39.10708789978589</v>
+        <v>39.1070878997935</v>
       </c>
       <c r="E14" t="n">
-        <v>39.09148126276158</v>
+        <v>39.09148126276911</v>
       </c>
       <c r="F14" t="n">
-        <v>39.08375946916553</v>
+        <v>39.08375946917304</v>
       </c>
       <c r="G14" t="n">
-        <v>39.08375946916553</v>
+        <v>39.08375946917304</v>
       </c>
       <c r="H14" t="n">
-        <v>39.06828182802153</v>
+        <v>39.06828182802898</v>
       </c>
       <c r="I14" t="n">
-        <v>39.03741130519171</v>
+        <v>39.03741130519909</v>
       </c>
       <c r="J14" t="n">
-        <v>39.00657444152697</v>
+        <v>39.0065744415343</v>
       </c>
       <c r="K14" t="n">
-        <v>38.99115348860216</v>
+        <v>38.9911534886095</v>
       </c>
       <c r="L14" t="n">
-        <v>39.08375946916553</v>
+        <v>39.08375946917304</v>
       </c>
       <c r="M14" t="n">
-        <v>39.07753730406835</v>
+        <v>39.07753730407585</v>
       </c>
       <c r="N14" t="n">
-        <v>39.06510863251498</v>
+        <v>39.06510863252247</v>
       </c>
       <c r="O14" t="n">
-        <v>39.05269110373037</v>
+        <v>39.05269110373786</v>
       </c>
       <c r="P14" t="n">
-        <v>39.04648664701761</v>
+        <v>39.0464866470251</v>
       </c>
       <c r="Q14" t="n">
-        <v>39.74417654595072</v>
+        <v>39.74417675168603</v>
       </c>
       <c r="R14" t="n">
-        <v>39.61697870366276</v>
+        <v>39.61697888403544</v>
       </c>
       <c r="S14" t="n">
-        <v>39.36815283832012</v>
+        <v>39.36815297439354</v>
       </c>
       <c r="T14" t="n">
-        <v>39.12153680885818</v>
+        <v>39.12153690503617</v>
       </c>
       <c r="U14" t="n">
-        <v>38.99809844418806</v>
+        <v>38.998098521869</v>
       </c>
       <c r="V14" t="n">
-        <v>38.99809844418806</v>
+        <v>38.998098521869</v>
       </c>
       <c r="W14" t="n">
-        <v>38.99707746038975</v>
+        <v>38.99707753776354</v>
       </c>
       <c r="X14" t="n">
-        <v>38.99503882503453</v>
+        <v>38.99503890200136</v>
       </c>
       <c r="Y14" t="n">
-        <v>38.99300188786228</v>
+        <v>38.99300196462794</v>
       </c>
       <c r="Z14" t="n">
-        <v>38.99198347826435</v>
+        <v>38.99198355503198</v>
       </c>
     </row>
     <row r="15">
@@ -6633,79 +6633,79 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>39.18391652813911</v>
+        <v>39.18391652813866</v>
       </c>
       <c r="C15" t="n">
-        <v>39.1728715289199</v>
+        <v>39.17287152891954</v>
       </c>
       <c r="D15" t="n">
-        <v>39.15108807004184</v>
+        <v>39.1510880700416</v>
       </c>
       <c r="E15" t="n">
-        <v>39.12956611695903</v>
+        <v>39.12956611695885</v>
       </c>
       <c r="F15" t="n">
-        <v>39.11891700914099</v>
+        <v>39.11891700914082</v>
       </c>
       <c r="G15" t="n">
-        <v>39.11891700914099</v>
+        <v>39.11891700914082</v>
       </c>
       <c r="H15" t="n">
-        <v>39.09756795798147</v>
+        <v>39.09756795798136</v>
       </c>
       <c r="I15" t="n">
-        <v>39.05498184580517</v>
+        <v>39.05498184580512</v>
       </c>
       <c r="J15" t="n">
-        <v>39.01243047654699</v>
+        <v>39.01243047654698</v>
       </c>
       <c r="K15" t="n">
-        <v>38.99114512811421</v>
+        <v>38.9911451281142</v>
       </c>
       <c r="L15" t="n">
-        <v>39.11891700914099</v>
+        <v>39.11891700914082</v>
       </c>
       <c r="M15" t="n">
-        <v>39.11033476193539</v>
+        <v>39.11033476193524</v>
       </c>
       <c r="N15" t="n">
-        <v>39.09319106533937</v>
+        <v>39.09319106533922</v>
       </c>
       <c r="O15" t="n">
-        <v>39.07606088094762</v>
+        <v>39.07606088094747</v>
       </c>
       <c r="P15" t="n">
-        <v>39.06750078375973</v>
+        <v>39.06750078375958</v>
       </c>
       <c r="Q15" t="n">
-        <v>40.02403617463414</v>
+        <v>40.02403602733516</v>
       </c>
       <c r="R15" t="n">
-        <v>39.84987657648039</v>
+        <v>39.84987646024256</v>
       </c>
       <c r="S15" t="n">
-        <v>39.50864671322014</v>
+        <v>39.50864664798069</v>
       </c>
       <c r="T15" t="n">
-        <v>39.16965737967076</v>
+        <v>39.1696573585129</v>
       </c>
       <c r="U15" t="n">
-        <v>38.99958749854608</v>
+        <v>38.99958749758049</v>
       </c>
       <c r="V15" t="n">
-        <v>38.99958749854608</v>
+        <v>38.99958749758049</v>
       </c>
       <c r="W15" t="n">
-        <v>38.99818234455982</v>
+        <v>38.99818234392798</v>
       </c>
       <c r="X15" t="n">
-        <v>38.99537511615703</v>
+        <v>38.99537511596796</v>
       </c>
       <c r="Y15" t="n">
-        <v>38.99256865486754</v>
+        <v>38.99256865489923</v>
       </c>
       <c r="Z15" t="n">
-        <v>38.99116470069125</v>
+        <v>38.99116470072294</v>
       </c>
     </row>
     <row r="16">
@@ -6713,22 +6713,22 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>39.18229134100939</v>
+        <v>39.1822913410094</v>
       </c>
       <c r="C16" t="n">
-        <v>39.17169629324965</v>
+        <v>39.17169629324967</v>
       </c>
       <c r="D16" t="n">
-        <v>39.15049324298906</v>
+        <v>39.15049324298907</v>
       </c>
       <c r="E16" t="n">
-        <v>39.12927505883825</v>
+        <v>39.12927505883826</v>
       </c>
       <c r="F16" t="n">
-        <v>39.11865932276825</v>
+        <v>39.11865932276823</v>
       </c>
       <c r="G16" t="n">
-        <v>39.11865932276825</v>
+        <v>39.11865932276823</v>
       </c>
       <c r="H16" t="n">
         <v>39.09743212583644</v>
@@ -6737,55 +6737,55 @@
         <v>39.05495406746987</v>
       </c>
       <c r="J16" t="n">
-        <v>39.01242970273286</v>
+        <v>39.01242970273287</v>
       </c>
       <c r="K16" t="n">
-        <v>38.99114435387811</v>
+        <v>38.9911443538781</v>
       </c>
       <c r="L16" t="n">
-        <v>39.11865932276825</v>
+        <v>39.11865932276823</v>
       </c>
       <c r="M16" t="n">
         <v>39.11010876048071</v>
       </c>
       <c r="N16" t="n">
-        <v>39.09300372998416</v>
+        <v>39.09300372998415</v>
       </c>
       <c r="O16" t="n">
-        <v>39.07589107881315</v>
+        <v>39.07589107881314</v>
       </c>
       <c r="P16" t="n">
-        <v>39.06733094444635</v>
+        <v>39.06733094444634</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.00694835879087</v>
+        <v>40.00694836684337</v>
       </c>
       <c r="R16" t="n">
-        <v>39.84073450333089</v>
+        <v>39.84073450758621</v>
       </c>
       <c r="S16" t="n">
-        <v>39.50658772470066</v>
+        <v>39.5065877256765</v>
       </c>
       <c r="T16" t="n">
-        <v>39.16953958266068</v>
+        <v>39.16953958272981</v>
       </c>
       <c r="U16" t="n">
-        <v>38.99956339170378</v>
+        <v>38.99956339170441</v>
       </c>
       <c r="V16" t="n">
-        <v>38.99956339170378</v>
+        <v>38.99956339170441</v>
       </c>
       <c r="W16" t="n">
-        <v>38.99815978684023</v>
+        <v>38.99815978683971</v>
       </c>
       <c r="X16" t="n">
-        <v>38.99535241195021</v>
+        <v>38.99535241194926</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.99254477119885</v>
+        <v>38.99254477119798</v>
       </c>
       <c r="Z16" t="n">
-        <v>38.99114081616938</v>
+        <v>38.99114081616852</v>
       </c>
     </row>
     <row r="17">
@@ -6793,10 +6793,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>39.12837497755943</v>
+        <v>39.12837497755944</v>
       </c>
       <c r="C17" t="n">
-        <v>39.12105721249612</v>
+        <v>39.12105721249613</v>
       </c>
       <c r="D17" t="n">
         <v>39.10615884760433</v>
@@ -6805,10 +6805,10 @@
         <v>39.09102512735672</v>
       </c>
       <c r="F17" t="n">
-        <v>39.0833555144978</v>
+        <v>39.08335551449779</v>
       </c>
       <c r="G17" t="n">
-        <v>39.0833555144978</v>
+        <v>39.08335551449779</v>
       </c>
       <c r="H17" t="n">
         <v>39.06806829779364</v>
@@ -6817,55 +6817,55 @@
         <v>39.03736689137853</v>
       </c>
       <c r="J17" t="n">
-        <v>39.00657230979381</v>
+        <v>39.00657230979382</v>
       </c>
       <c r="K17" t="n">
-        <v>38.99115135602682</v>
+        <v>38.99115135602683</v>
       </c>
       <c r="L17" t="n">
-        <v>39.0833555144978</v>
+        <v>39.08335551449779</v>
       </c>
       <c r="M17" t="n">
         <v>39.0771828268517</v>
       </c>
       <c r="N17" t="n">
-        <v>39.06481456671348</v>
+        <v>39.06481456671347</v>
       </c>
       <c r="O17" t="n">
-        <v>39.05242444939671</v>
+        <v>39.0524244493967</v>
       </c>
       <c r="P17" t="n">
         <v>39.04621995034832</v>
       </c>
       <c r="Q17" t="n">
-        <v>39.71491123820066</v>
+        <v>39.71491123808867</v>
       </c>
       <c r="R17" t="n">
-        <v>39.60035492245441</v>
+        <v>39.60035492242223</v>
       </c>
       <c r="S17" t="n">
-        <v>39.36325137592813</v>
+        <v>39.36325137592731</v>
       </c>
       <c r="T17" t="n">
-        <v>39.12026871601697</v>
+        <v>39.12026871601773</v>
       </c>
       <c r="U17" t="n">
-        <v>38.99724835001454</v>
+        <v>38.99724835001503</v>
       </c>
       <c r="V17" t="n">
-        <v>38.99724835001454</v>
+        <v>38.99724835001503</v>
       </c>
       <c r="W17" t="n">
-        <v>38.99623427729139</v>
+        <v>38.99623427729188</v>
       </c>
       <c r="X17" t="n">
-        <v>38.99420137109017</v>
+        <v>38.99420137109064</v>
       </c>
       <c r="Y17" t="n">
-        <v>38.9921655425656</v>
+        <v>38.99216554256606</v>
       </c>
       <c r="Z17" t="n">
-        <v>38.99114711136058</v>
+        <v>38.99114711136104</v>
       </c>
     </row>
     <row r="18">
@@ -6876,76 +6876,76 @@
         <v>39.08463320130166</v>
       </c>
       <c r="C18" t="n">
-        <v>39.07964572949705</v>
+        <v>39.07964572949704</v>
       </c>
       <c r="D18" t="n">
         <v>39.06949385934568</v>
       </c>
       <c r="E18" t="n">
-        <v>39.05918251218583</v>
+        <v>39.05918251218581</v>
       </c>
       <c r="F18" t="n">
-        <v>39.05395686630028</v>
+        <v>39.05395686630027</v>
       </c>
       <c r="G18" t="n">
-        <v>39.05395686630028</v>
+        <v>39.05395686630027</v>
       </c>
       <c r="H18" t="n">
-        <v>39.04354346384926</v>
+        <v>39.04354346384925</v>
       </c>
       <c r="I18" t="n">
-        <v>39.02263181055864</v>
+        <v>39.02263181055863</v>
       </c>
       <c r="J18" t="n">
-        <v>39.0016612194906</v>
+        <v>39.00166121949059</v>
       </c>
       <c r="K18" t="n">
-        <v>38.99116232536092</v>
+        <v>38.99116232536091</v>
       </c>
       <c r="L18" t="n">
-        <v>39.05395686630028</v>
+        <v>39.05395686630027</v>
       </c>
       <c r="M18" t="n">
-        <v>39.04975191732103</v>
+        <v>39.04975191732101</v>
       </c>
       <c r="N18" t="n">
-        <v>39.04132671511785</v>
+        <v>39.04132671511783</v>
       </c>
       <c r="O18" t="n">
-        <v>39.03288735441907</v>
+        <v>39.03288735441906</v>
       </c>
       <c r="P18" t="n">
-        <v>39.0286616250173</v>
+        <v>39.02866162501729</v>
       </c>
       <c r="Q18" t="n">
-        <v>39.48573310303048</v>
+        <v>39.48573310303046</v>
       </c>
       <c r="R18" t="n">
-        <v>39.4072422506236</v>
+        <v>39.40724225062326</v>
       </c>
       <c r="S18" t="n">
-        <v>39.2450661519758</v>
+        <v>39.24506615197561</v>
       </c>
       <c r="T18" t="n">
-        <v>39.07918307989159</v>
+        <v>39.07918307989158</v>
       </c>
       <c r="U18" t="n">
-        <v>38.9953561397509</v>
+        <v>38.99535613975095</v>
       </c>
       <c r="V18" t="n">
-        <v>38.9953561397509</v>
+        <v>38.99535613975095</v>
       </c>
       <c r="W18" t="n">
-        <v>38.99466406354185</v>
+        <v>38.9946640635419</v>
       </c>
       <c r="X18" t="n">
-        <v>38.99327671880701</v>
+        <v>38.99327671880707</v>
       </c>
       <c r="Y18" t="n">
-        <v>38.99188745809681</v>
+        <v>38.99188745809685</v>
       </c>
       <c r="Z18" t="n">
-        <v>38.99119252244568</v>
+        <v>38.99119252244573</v>
       </c>
     </row>
     <row r="19">
@@ -6959,16 +6959,16 @@
         <v>39.08033042569596</v>
       </c>
       <c r="D19" t="n">
-        <v>39.06984325879952</v>
+        <v>39.06984325879953</v>
       </c>
       <c r="E19" t="n">
-        <v>39.05935479524497</v>
+        <v>39.05935479524498</v>
       </c>
       <c r="F19" t="n">
-        <v>39.0541095309424</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="G19" t="n">
-        <v>39.0541095309424</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="H19" t="n">
         <v>39.0436245601332</v>
@@ -6983,49 +6983,49 @@
         <v>38.9911638509007</v>
       </c>
       <c r="L19" t="n">
-        <v>39.0541095309424</v>
+        <v>39.05410953094241</v>
       </c>
       <c r="M19" t="n">
         <v>39.04988600439014</v>
       </c>
       <c r="N19" t="n">
-        <v>39.04143810910998</v>
+        <v>39.04143810910999</v>
       </c>
       <c r="O19" t="n">
-        <v>39.03298844628532</v>
+        <v>39.03298844628533</v>
       </c>
       <c r="P19" t="n">
         <v>39.02876272781678</v>
       </c>
       <c r="Q19" t="n">
-        <v>39.49877863180093</v>
+        <v>39.49877863180105</v>
       </c>
       <c r="R19" t="n">
-        <v>39.41532198056899</v>
+        <v>39.4153219805691</v>
       </c>
       <c r="S19" t="n">
-        <v>39.24826428376232</v>
+        <v>39.2482642837624</v>
       </c>
       <c r="T19" t="n">
-        <v>39.0805787138757</v>
+        <v>39.08057871387578</v>
       </c>
       <c r="U19" t="n">
-        <v>38.99639445855779</v>
+        <v>38.99639445855786</v>
       </c>
       <c r="V19" t="n">
-        <v>38.99639445855779</v>
+        <v>38.99639445855786</v>
       </c>
       <c r="W19" t="n">
-        <v>38.99569648525861</v>
+        <v>38.99569648525868</v>
       </c>
       <c r="X19" t="n">
-        <v>38.99430260402571</v>
+        <v>38.99430260402578</v>
       </c>
       <c r="Y19" t="n">
-        <v>38.992910748996</v>
+        <v>38.99291074899607</v>
       </c>
       <c r="Z19" t="n">
-        <v>38.99221583129302</v>
+        <v>38.9922158312931</v>
       </c>
     </row>
     <row r="20">
@@ -7045,31 +7045,31 @@
         <v>39.09148126276158</v>
       </c>
       <c r="F20" t="n">
-        <v>39.08375946916552</v>
+        <v>39.08375946916551</v>
       </c>
       <c r="G20" t="n">
-        <v>39.08375946916552</v>
+        <v>39.08375946916551</v>
       </c>
       <c r="H20" t="n">
-        <v>39.06828182802153</v>
+        <v>39.06828182802152</v>
       </c>
       <c r="I20" t="n">
-        <v>39.03741130519171</v>
+        <v>39.0374113051917</v>
       </c>
       <c r="J20" t="n">
         <v>39.00657444152696</v>
       </c>
       <c r="K20" t="n">
-        <v>38.99115348860217</v>
+        <v>38.99115348860216</v>
       </c>
       <c r="L20" t="n">
-        <v>39.08375946916552</v>
+        <v>39.08375946916551</v>
       </c>
       <c r="M20" t="n">
         <v>39.07753730406834</v>
       </c>
       <c r="N20" t="n">
-        <v>39.06510863251498</v>
+        <v>39.06510863251497</v>
       </c>
       <c r="O20" t="n">
         <v>39.05269110373037</v>
@@ -7078,34 +7078,34 @@
         <v>39.0464866470176</v>
       </c>
       <c r="Q20" t="n">
-        <v>39.74417654596289</v>
+        <v>39.7441765460131</v>
       </c>
       <c r="R20" t="n">
-        <v>39.61697870367352</v>
+        <v>39.61697870371778</v>
       </c>
       <c r="S20" t="n">
-        <v>39.36815283832836</v>
+        <v>39.36815283836221</v>
       </c>
       <c r="T20" t="n">
-        <v>39.12153680886416</v>
+        <v>39.1215368088886</v>
       </c>
       <c r="U20" t="n">
-        <v>38.99809844419298</v>
+        <v>38.99809844421306</v>
       </c>
       <c r="V20" t="n">
-        <v>38.99809844419298</v>
+        <v>38.99809844421306</v>
       </c>
       <c r="W20" t="n">
-        <v>38.99707746039464</v>
+        <v>38.99707746041465</v>
       </c>
       <c r="X20" t="n">
-        <v>38.9950388250394</v>
+        <v>38.99503882505931</v>
       </c>
       <c r="Y20" t="n">
-        <v>38.99300188786713</v>
+        <v>38.993001887887</v>
       </c>
       <c r="Z20" t="n">
-        <v>38.9919834782692</v>
+        <v>38.99198347828906</v>
       </c>
     </row>
     <row r="21">
@@ -7113,7 +7113,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>39.18391652813911</v>
+        <v>39.1839165281391</v>
       </c>
       <c r="C21" t="n">
         <v>39.1728715289199</v>
@@ -7122,13 +7122,13 @@
         <v>39.15108807004184</v>
       </c>
       <c r="E21" t="n">
-        <v>39.12956611695903</v>
+        <v>39.12956611695902</v>
       </c>
       <c r="F21" t="n">
-        <v>39.11891700914099</v>
+        <v>39.11891700914098</v>
       </c>
       <c r="G21" t="n">
-        <v>39.11891700914099</v>
+        <v>39.11891700914098</v>
       </c>
       <c r="H21" t="n">
         <v>39.09756795798147</v>
@@ -7143,10 +7143,10 @@
         <v>38.9911451281142</v>
       </c>
       <c r="L21" t="n">
-        <v>39.11891700914099</v>
+        <v>39.11891700914098</v>
       </c>
       <c r="M21" t="n">
-        <v>39.11033476193541</v>
+        <v>39.11033476193539</v>
       </c>
       <c r="N21" t="n">
         <v>39.09319106533937</v>
@@ -7158,34 +7158,34 @@
         <v>39.06750078375973</v>
       </c>
       <c r="Q21" t="n">
-        <v>40.0240361746249</v>
+        <v>40.02403617458675</v>
       </c>
       <c r="R21" t="n">
-        <v>39.84987657647308</v>
+        <v>39.84987657644293</v>
       </c>
       <c r="S21" t="n">
-        <v>39.50864671321603</v>
+        <v>39.50864671319904</v>
       </c>
       <c r="T21" t="n">
-        <v>39.16965737966944</v>
+        <v>39.16965737966387</v>
       </c>
       <c r="U21" t="n">
-        <v>38.99958749854603</v>
+        <v>38.9995874985457</v>
       </c>
       <c r="V21" t="n">
-        <v>38.99958749854603</v>
+        <v>38.9995874985457</v>
       </c>
       <c r="W21" t="n">
-        <v>38.99818234455978</v>
+        <v>38.99818234455954</v>
       </c>
       <c r="X21" t="n">
-        <v>38.99537511615702</v>
+        <v>38.9953751161569</v>
       </c>
       <c r="Y21" t="n">
-        <v>38.99256865486755</v>
+        <v>38.9925686548675</v>
       </c>
       <c r="Z21" t="n">
-        <v>38.99116470069126</v>
+        <v>38.99116470069121</v>
       </c>
     </row>
     <row r="22">
@@ -7193,79 +7193,79 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>39.1822913410094</v>
+        <v>39.18229134100939</v>
       </c>
       <c r="C22" t="n">
         <v>39.17169629324966</v>
       </c>
       <c r="D22" t="n">
-        <v>39.15049324298907</v>
+        <v>39.15049324298906</v>
       </c>
       <c r="E22" t="n">
-        <v>39.12927505883827</v>
+        <v>39.12927505883825</v>
       </c>
       <c r="F22" t="n">
-        <v>39.11865932276825</v>
+        <v>39.11865932276823</v>
       </c>
       <c r="G22" t="n">
-        <v>39.11865932276825</v>
+        <v>39.11865932276823</v>
       </c>
       <c r="H22" t="n">
-        <v>39.09743212583644</v>
+        <v>39.09743212583643</v>
       </c>
       <c r="I22" t="n">
-        <v>39.05495406746989</v>
+        <v>39.05495406746986</v>
       </c>
       <c r="J22" t="n">
-        <v>39.01242970273287</v>
+        <v>39.01242970273286</v>
       </c>
       <c r="K22" t="n">
-        <v>38.9911443538781</v>
+        <v>38.99114435387809</v>
       </c>
       <c r="L22" t="n">
-        <v>39.11865932276825</v>
+        <v>39.11865932276823</v>
       </c>
       <c r="M22" t="n">
-        <v>39.11010876048072</v>
+        <v>39.1101087604807</v>
       </c>
       <c r="N22" t="n">
-        <v>39.09300372998416</v>
+        <v>39.09300372998415</v>
       </c>
       <c r="O22" t="n">
-        <v>39.07589107881315</v>
+        <v>39.07589107881314</v>
       </c>
       <c r="P22" t="n">
-        <v>39.06733094444637</v>
+        <v>39.06733094444635</v>
       </c>
       <c r="Q22" t="n">
-        <v>40.00694835879139</v>
+        <v>40.00694835879359</v>
       </c>
       <c r="R22" t="n">
-        <v>39.84073450333117</v>
+        <v>39.84073450333235</v>
       </c>
       <c r="S22" t="n">
-        <v>39.50658772470074</v>
+        <v>39.50658772470103</v>
       </c>
       <c r="T22" t="n">
-        <v>39.16953958266069</v>
+        <v>39.16953958266072</v>
       </c>
       <c r="U22" t="n">
-        <v>38.99956339170379</v>
+        <v>38.99956339170378</v>
       </c>
       <c r="V22" t="n">
-        <v>38.99956339170379</v>
+        <v>38.99956339170378</v>
       </c>
       <c r="W22" t="n">
         <v>38.99815978684023</v>
       </c>
       <c r="X22" t="n">
-        <v>38.99535241195022</v>
+        <v>38.99535241195021</v>
       </c>
       <c r="Y22" t="n">
         <v>38.99254477119884</v>
       </c>
       <c r="Z22" t="n">
-        <v>38.99114081616939</v>
+        <v>38.99114081616938</v>
       </c>
     </row>
     <row r="23">
@@ -7273,7 +7273,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>39.12837497755943</v>
+        <v>39.12837497755944</v>
       </c>
       <c r="C23" t="n">
         <v>39.12105721249613</v>
@@ -7291,7 +7291,7 @@
         <v>39.0833555144978</v>
       </c>
       <c r="H23" t="n">
-        <v>39.06806829779364</v>
+        <v>39.06806829779365</v>
       </c>
       <c r="I23" t="n">
         <v>39.03736689137853</v>
@@ -7318,34 +7318,34 @@
         <v>39.04621995034832</v>
       </c>
       <c r="Q23" t="n">
-        <v>39.71491123820027</v>
+        <v>39.71491123820149</v>
       </c>
       <c r="R23" t="n">
-        <v>39.60035492245407</v>
+        <v>39.60035492245517</v>
       </c>
       <c r="S23" t="n">
-        <v>39.36325137592787</v>
+        <v>39.36325137592871</v>
       </c>
       <c r="T23" t="n">
-        <v>39.12026871601678</v>
+        <v>39.1202687160174</v>
       </c>
       <c r="U23" t="n">
-        <v>38.9972483500144</v>
+        <v>38.99724835001489</v>
       </c>
       <c r="V23" t="n">
-        <v>38.9972483500144</v>
+        <v>38.99724835001489</v>
       </c>
       <c r="W23" t="n">
-        <v>38.99623427729124</v>
+        <v>38.99623427729175</v>
       </c>
       <c r="X23" t="n">
-        <v>38.99420137109002</v>
+        <v>38.99420137109051</v>
       </c>
       <c r="Y23" t="n">
-        <v>38.99216554256545</v>
+        <v>38.99216554256595</v>
       </c>
       <c r="Z23" t="n">
-        <v>38.99114711136043</v>
+        <v>38.99114711136092</v>
       </c>
     </row>
     <row r="24">
@@ -7353,79 +7353,79 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>39.08463320130167</v>
+        <v>39.08463320130166</v>
       </c>
       <c r="C24" t="n">
         <v>39.07964572949705</v>
       </c>
       <c r="D24" t="n">
-        <v>39.06949385934567</v>
+        <v>39.06949385934568</v>
       </c>
       <c r="E24" t="n">
-        <v>39.05918251218583</v>
+        <v>39.05918251218582</v>
       </c>
       <c r="F24" t="n">
-        <v>39.05395686630028</v>
+        <v>39.05395686630027</v>
       </c>
       <c r="G24" t="n">
-        <v>39.05395686630028</v>
+        <v>39.05395686630027</v>
       </c>
       <c r="H24" t="n">
-        <v>39.04354346384926</v>
+        <v>39.04354346384925</v>
       </c>
       <c r="I24" t="n">
         <v>39.02263181055864</v>
       </c>
       <c r="J24" t="n">
-        <v>39.0016612194906</v>
+        <v>39.00166121949059</v>
       </c>
       <c r="K24" t="n">
         <v>38.99116232536092</v>
       </c>
       <c r="L24" t="n">
-        <v>39.05395686630028</v>
+        <v>39.05395686630027</v>
       </c>
       <c r="M24" t="n">
-        <v>39.04975191732103</v>
+        <v>39.04975191732102</v>
       </c>
       <c r="N24" t="n">
-        <v>39.04132671511785</v>
+        <v>39.04132671511784</v>
       </c>
       <c r="O24" t="n">
         <v>39.03288735441907</v>
       </c>
       <c r="P24" t="n">
-        <v>39.02866162501731</v>
+        <v>39.02866162501729</v>
       </c>
       <c r="Q24" t="n">
-        <v>39.48573310303056</v>
+        <v>39.48573310303004</v>
       </c>
       <c r="R24" t="n">
-        <v>39.40724225062366</v>
+        <v>39.40724225062326</v>
       </c>
       <c r="S24" t="n">
-        <v>39.24506615197581</v>
+        <v>39.24506615197561</v>
       </c>
       <c r="T24" t="n">
-        <v>39.07918307989156</v>
+        <v>39.07918307989155</v>
       </c>
       <c r="U24" t="n">
-        <v>38.99535613975084</v>
+        <v>38.99535613975091</v>
       </c>
       <c r="V24" t="n">
-        <v>38.99535613975084</v>
+        <v>38.99535613975091</v>
       </c>
       <c r="W24" t="n">
-        <v>38.99466406354178</v>
+        <v>38.99466406354186</v>
       </c>
       <c r="X24" t="n">
-        <v>38.99327671880695</v>
+        <v>38.99327671880702</v>
       </c>
       <c r="Y24" t="n">
-        <v>38.99188745809674</v>
+        <v>38.99188745809681</v>
       </c>
       <c r="Z24" t="n">
-        <v>38.99119252244562</v>
+        <v>38.99119252244569</v>
       </c>
     </row>
     <row r="25">
@@ -7439,10 +7439,10 @@
         <v>39.08033042569596</v>
       </c>
       <c r="D25" t="n">
-        <v>39.06984325879953</v>
+        <v>39.06984325879952</v>
       </c>
       <c r="E25" t="n">
-        <v>39.05935479524498</v>
+        <v>39.05935479524497</v>
       </c>
       <c r="F25" t="n">
         <v>39.05410953094241</v>
@@ -7472,40 +7472,40 @@
         <v>39.04143810910998</v>
       </c>
       <c r="O25" t="n">
-        <v>39.03298844628533</v>
+        <v>39.03298844628532</v>
       </c>
       <c r="P25" t="n">
         <v>39.02876272781678</v>
       </c>
       <c r="Q25" t="n">
-        <v>39.49877863180117</v>
+        <v>39.49877863180131</v>
       </c>
       <c r="R25" t="n">
-        <v>39.41532198056919</v>
+        <v>39.41532198056932</v>
       </c>
       <c r="S25" t="n">
-        <v>39.24826428376247</v>
+        <v>39.24826428376258</v>
       </c>
       <c r="T25" t="n">
-        <v>39.08057871387582</v>
+        <v>39.08057871387591</v>
       </c>
       <c r="U25" t="n">
-        <v>38.99639445855787</v>
+        <v>38.99639445855796</v>
       </c>
       <c r="V25" t="n">
-        <v>38.99639445855787</v>
+        <v>38.99639445855796</v>
       </c>
       <c r="W25" t="n">
-        <v>38.99569648525868</v>
+        <v>38.99569648525878</v>
       </c>
       <c r="X25" t="n">
-        <v>38.99430260402578</v>
+        <v>38.99430260402588</v>
       </c>
       <c r="Y25" t="n">
-        <v>38.99291074899607</v>
+        <v>38.99291074899617</v>
       </c>
       <c r="Z25" t="n">
-        <v>38.99221583129309</v>
+        <v>38.9922158312932</v>
       </c>
     </row>
     <row r="26">
@@ -7513,79 +7513,79 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>39.13089607071609</v>
+        <v>39.13089607071608</v>
       </c>
       <c r="C26" t="n">
-        <v>39.12288548007054</v>
+        <v>39.12288548007052</v>
       </c>
       <c r="D26" t="n">
-        <v>39.1070878997859</v>
+        <v>39.10708789978589</v>
       </c>
       <c r="E26" t="n">
         <v>39.09148126276158</v>
       </c>
       <c r="F26" t="n">
-        <v>39.08375946916552</v>
+        <v>39.08375946916551</v>
       </c>
       <c r="G26" t="n">
-        <v>39.08375946916552</v>
+        <v>39.08375946916551</v>
       </c>
       <c r="H26" t="n">
-        <v>39.06828182802153</v>
+        <v>39.06828182802152</v>
       </c>
       <c r="I26" t="n">
-        <v>39.03741130519171</v>
+        <v>39.0374113051917</v>
       </c>
       <c r="J26" t="n">
-        <v>39.00657444152697</v>
+        <v>39.00657444152696</v>
       </c>
       <c r="K26" t="n">
-        <v>38.99115348860216</v>
+        <v>38.99115348860215</v>
       </c>
       <c r="L26" t="n">
-        <v>39.08375946916552</v>
+        <v>39.08375946916551</v>
       </c>
       <c r="M26" t="n">
         <v>39.07753730406834</v>
       </c>
       <c r="N26" t="n">
-        <v>39.06510863251498</v>
+        <v>39.06510863251496</v>
       </c>
       <c r="O26" t="n">
         <v>39.05269110373037</v>
       </c>
       <c r="P26" t="n">
-        <v>39.04648664701762</v>
+        <v>39.0464866470176</v>
       </c>
       <c r="Q26" t="n">
-        <v>39.74417654597011</v>
+        <v>39.74417654603524</v>
       </c>
       <c r="R26" t="n">
-        <v>39.61697870367988</v>
+        <v>39.61697870373732</v>
       </c>
       <c r="S26" t="n">
-        <v>39.36815283833325</v>
+        <v>39.36815283837717</v>
       </c>
       <c r="T26" t="n">
-        <v>39.1215368088677</v>
+        <v>39.12153680889942</v>
       </c>
       <c r="U26" t="n">
-        <v>38.9980984441959</v>
+        <v>38.99809844422197</v>
       </c>
       <c r="V26" t="n">
-        <v>38.9980984441959</v>
+        <v>38.99809844422197</v>
       </c>
       <c r="W26" t="n">
-        <v>38.99707746039756</v>
+        <v>38.99707746042352</v>
       </c>
       <c r="X26" t="n">
-        <v>38.9950388250423</v>
+        <v>38.99503882506814</v>
       </c>
       <c r="Y26" t="n">
-        <v>38.99300188787003</v>
+        <v>38.99300188789582</v>
       </c>
       <c r="Z26" t="n">
-        <v>38.9919834782721</v>
+        <v>38.99198347829788</v>
       </c>
     </row>
   </sheetData>
